--- a/BOMs/BOM_ORDER.xlsx
+++ b/BOMs/BOM_ORDER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon\Documents\KiCad\desings\4_DMX node\BOMs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A084D5-3EE1-4013-BE20-FA73546B60A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05D89962-65B0-4B14-ACEA-DC485BF0AB54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{9B84EF14-36DD-40E4-AAD2-543AD15C4A8A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{9B84EF14-36DD-40E4-AAD2-543AD15C4A8A}"/>
   </bookViews>
   <sheets>
     <sheet name="ORDER" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2042" uniqueCount="651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2047" uniqueCount="655">
   <si>
     <t>Id</t>
   </si>
@@ -1887,9 +1887,6 @@
     <t>Ext.Price(USD)</t>
   </si>
   <si>
-    <t>LCSC#</t>
-  </si>
-  <si>
     <t>Package</t>
   </si>
   <si>
@@ -2023,6 +2020,21 @@
   </si>
   <si>
     <t>https://www.lcsc.com/product-detail/C109318.html</t>
+  </si>
+  <si>
+    <t>PKCELL Li-Po Battery 3.7V 2000mAh</t>
+  </si>
+  <si>
+    <t>PKCELL</t>
+  </si>
+  <si>
+    <t>Li-Po Battery 3.7V 2000mAh - JST-PH - LP803860</t>
+  </si>
+  <si>
+    <t>LCSC#/MOUSER</t>
+  </si>
+  <si>
+    <t>https://www.tinytronics.nl/en/power/batteries/li-po/pkcell-li-po-battery-3.7v-2000mah-jst-ph-lp803860</t>
   </si>
 </sst>
 </file>
@@ -2032,7 +2044,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2073,22 +2085,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color indexed="12"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2138,16 +2134,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2157,26 +2152,19 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2186,66 +2174,52 @@
     <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="4">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
-    <cellStyle name="Hyperlink" xfId="4" builtinId="8"/>
     <cellStyle name="Hyperlink 2" xfId="3" xr:uid="{4E5B0147-6CFE-4E54-ACBB-AF608E19D3A6}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{B5D1B2ED-513F-44B5-BB21-F052053D13F4}"/>
   </cellStyles>
-  <dxfs count="125">
+  <dxfs count="128">
     <dxf>
       <font>
-        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
+        <u/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <color indexed="12"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2263,18 +2237,19 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
+        <u/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <color indexed="12"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2292,18 +2267,19 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
+        <u/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <color indexed="12"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2320,395 +2296,129 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
@@ -2917,11 +2627,229 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-      <border outline="0">
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -2930,48 +2858,6 @@
           <color indexed="64"/>
         </right>
       </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -3004,97 +2890,208 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <border outline="0">
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -3319,25 +3316,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{17788B69-A5A2-442D-970D-4F3F58D2C1D1}">
-      <tableStyleElement type="wholeTable" dxfId="124"/>
-      <tableStyleElement type="headerRow" dxfId="123"/>
-      <tableStyleElement type="totalRow" dxfId="122"/>
-      <tableStyleElement type="firstColumn" dxfId="121"/>
-      <tableStyleElement type="lastColumn" dxfId="120"/>
-      <tableStyleElement type="firstRowStripe" dxfId="119"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="118"/>
+      <tableStyleElement type="wholeTable" dxfId="127"/>
+      <tableStyleElement type="headerRow" dxfId="126"/>
+      <tableStyleElement type="totalRow" dxfId="125"/>
+      <tableStyleElement type="firstColumn" dxfId="124"/>
+      <tableStyleElement type="lastColumn" dxfId="123"/>
+      <tableStyleElement type="firstRowStripe" dxfId="122"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="121"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{49D30C32-15C7-40F8-9F26-4D109DA1EB3E}">
-      <tableStyleElement type="headerRow" dxfId="117"/>
-      <tableStyleElement type="totalRow" dxfId="116"/>
-      <tableStyleElement type="firstRowStripe" dxfId="115"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="114"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="113"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="112"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="111"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="110"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="109"/>
-      <tableStyleElement type="pageFieldValues" dxfId="108"/>
+      <tableStyleElement type="headerRow" dxfId="120"/>
+      <tableStyleElement type="totalRow" dxfId="119"/>
+      <tableStyleElement type="firstRowStripe" dxfId="118"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="117"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="116"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="115"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="114"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="113"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="112"/>
+      <tableStyleElement type="pageFieldValues" dxfId="111"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -3527,36 +3524,36 @@
   </sortState>
   <tableColumns count="29">
     <tableColumn id="1" xr3:uid="{193D4942-D9C7-4808-9664-ED233B7BC77F}" uniqueName="1" name="Id" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{EBE99961-81FC-436F-B8F4-C920E55866B1}" uniqueName="2" name="Designator" queryTableFieldId="2" dataDxfId="66"/>
-    <tableColumn id="3" xr3:uid="{68D5AD26-CBA6-4EC2-A9F1-D603B2F6AF06}" uniqueName="3" name="Footprint" queryTableFieldId="3" dataDxfId="65"/>
+    <tableColumn id="2" xr3:uid="{EBE99961-81FC-436F-B8F4-C920E55866B1}" uniqueName="2" name="Designator" queryTableFieldId="2" dataDxfId="110"/>
+    <tableColumn id="3" xr3:uid="{68D5AD26-CBA6-4EC2-A9F1-D603B2F6AF06}" uniqueName="3" name="Footprint" queryTableFieldId="3" dataDxfId="109"/>
     <tableColumn id="4" xr3:uid="{C69663E0-3934-402E-A217-B04C029903F9}" uniqueName="4" name="Quantity" queryTableFieldId="4"/>
-    <tableColumn id="5" xr3:uid="{EFC1BF42-A0F8-4167-A78B-971913DD5EC6}" uniqueName="5" name="Designation" queryTableFieldId="5" dataDxfId="64"/>
-    <tableColumn id="6" xr3:uid="{ADFEF14D-AB5A-4337-BFD4-9F22C06A037A}" uniqueName="6" name="Supplier and ref" queryTableFieldId="6" dataDxfId="63"/>
-    <tableColumn id="7" xr3:uid="{5FF69B16-46E7-4D4B-92E4-918E69492B30}" uniqueName="7" name="Column1" queryTableFieldId="7" dataDxfId="62"/>
-    <tableColumn id="10" xr3:uid="{7ECCF4D2-A4BB-4FB1-AB47-D80526DE1596}" uniqueName="10" name="Needed quantity" queryTableFieldId="9" dataDxfId="61">
+    <tableColumn id="5" xr3:uid="{EFC1BF42-A0F8-4167-A78B-971913DD5EC6}" uniqueName="5" name="Designation" queryTableFieldId="5" dataDxfId="108"/>
+    <tableColumn id="6" xr3:uid="{ADFEF14D-AB5A-4337-BFD4-9F22C06A037A}" uniqueName="6" name="Supplier and ref" queryTableFieldId="6" dataDxfId="107"/>
+    <tableColumn id="7" xr3:uid="{5FF69B16-46E7-4D4B-92E4-918E69492B30}" uniqueName="7" name="Column1" queryTableFieldId="7" dataDxfId="106"/>
+    <tableColumn id="10" xr3:uid="{7ECCF4D2-A4BB-4FB1-AB47-D80526DE1596}" uniqueName="10" name="Needed quantity" queryTableFieldId="9" dataDxfId="105">
       <calculatedColumnFormula>2*Artnet_DMX_Converter5[[#This Row],[Quantity]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B90649C3-9530-44F6-9F83-0F46EA369F24}" uniqueName="8" name="-" queryTableFieldId="8" dataDxfId="60"/>
-    <tableColumn id="11" xr3:uid="{8BB3B2CB-709B-40DE-91FE-851022C724E2}" uniqueName="11" name="LCSC" queryTableFieldId="10" dataDxfId="59"/>
-    <tableColumn id="12" xr3:uid="{5B21BDC3-D99E-43DA-A2E4-B05F14DDA14D}" uniqueName="12" name="MOUSER" queryTableFieldId="11" dataDxfId="58"/>
-    <tableColumn id="13" xr3:uid="{B0CDCEBA-8AC4-4942-9413-2D530A7F2761}" uniqueName="13" name="Already in another pcb" queryTableFieldId="12" dataDxfId="57"/>
-    <tableColumn id="14" xr3:uid="{8340A12D-F318-4D9C-969B-3117A5EADB1A}" uniqueName="14" name="Enough?" queryTableFieldId="13" dataDxfId="50"/>
-    <tableColumn id="15" xr3:uid="{1ED5A8A2-1611-49FA-A788-90397B1162E3}" uniqueName="15" name="Mrf#" queryTableFieldId="14" dataDxfId="47"/>
-    <tableColumn id="16" xr3:uid="{07C56306-EF8D-45EF-BC0C-FA7F2A15FEF3}" uniqueName="16" name="Mfr." queryTableFieldId="15" dataDxfId="46"/>
-    <tableColumn id="17" xr3:uid="{19635C0F-7BD1-4660-98C6-93346F766B86}" uniqueName="17" name="Order Qty." queryTableFieldId="16" dataDxfId="45" dataCellStyle="Currency"/>
-    <tableColumn id="18" xr3:uid="{A46DB81F-05A4-4B42-8CA7-8DD56227E5E7}" uniqueName="18" name="Unit Price(USD)" queryTableFieldId="17" dataDxfId="44" dataCellStyle="Currency"/>
-    <tableColumn id="19" xr3:uid="{570EBF30-7625-4C4F-A1A9-5A6C29E3344C}" uniqueName="19" name="Ext.Price(USD)" queryTableFieldId="18" dataDxfId="43" dataCellStyle="Currency"/>
-    <tableColumn id="20" xr3:uid="{1210C2A8-B78E-4F49-8D59-4D7358DDF469}" uniqueName="20" name="LCSC#" queryTableFieldId="19" dataDxfId="42"/>
-    <tableColumn id="21" xr3:uid="{DCDFBA0B-E1DF-4891-B6DE-50DD37843C8F}" uniqueName="21" name="Package" queryTableFieldId="20" dataDxfId="41"/>
-    <tableColumn id="22" xr3:uid="{EE553BAA-235A-4ADE-BF21-5A6D487E525F}" uniqueName="22" name="Min" queryTableFieldId="21" dataDxfId="40"/>
-    <tableColumn id="23" xr3:uid="{EF5D702D-6003-4207-8949-2FAAAEA59C21}" uniqueName="23" name="Mult" queryTableFieldId="22" dataDxfId="39"/>
-    <tableColumn id="24" xr3:uid="{FC548331-4E82-4F18-8F1B-96AD5CFD679F}" uniqueName="24" name="SPQ" queryTableFieldId="23" dataDxfId="38"/>
-    <tableColumn id="25" xr3:uid="{4CE5E4B3-AC89-4D44-992B-1F594AE2EC4A}" uniqueName="25" name="Availability" queryTableFieldId="24" dataDxfId="37"/>
-    <tableColumn id="26" xr3:uid="{8719B838-3310-4B06-B6C2-7223B1B40BC9}" uniqueName="26" name="Stock Status" queryTableFieldId="25" dataDxfId="36"/>
-    <tableColumn id="27" xr3:uid="{2577FF1C-2965-441F-B3FF-7C6FD0944441}" uniqueName="27" name="Customer Notes" queryTableFieldId="26" dataDxfId="35"/>
-    <tableColumn id="28" xr3:uid="{5613E865-76FA-42C7-807E-255777292765}" uniqueName="28" name="Description" queryTableFieldId="27" dataDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{B90649C3-9530-44F6-9F83-0F46EA369F24}" uniqueName="8" name="-" queryTableFieldId="8" dataDxfId="104"/>
+    <tableColumn id="11" xr3:uid="{8BB3B2CB-709B-40DE-91FE-851022C724E2}" uniqueName="11" name="LCSC" queryTableFieldId="10" dataDxfId="103"/>
+    <tableColumn id="12" xr3:uid="{5B21BDC3-D99E-43DA-A2E4-B05F14DDA14D}" uniqueName="12" name="MOUSER" queryTableFieldId="11" dataDxfId="102"/>
+    <tableColumn id="13" xr3:uid="{B0CDCEBA-8AC4-4942-9413-2D530A7F2761}" uniqueName="13" name="Already in another pcb" queryTableFieldId="12" dataDxfId="101"/>
+    <tableColumn id="14" xr3:uid="{8340A12D-F318-4D9C-969B-3117A5EADB1A}" uniqueName="14" name="Enough?" queryTableFieldId="13" dataDxfId="100"/>
+    <tableColumn id="15" xr3:uid="{1ED5A8A2-1611-49FA-A788-90397B1162E3}" uniqueName="15" name="Mrf#" queryTableFieldId="14" dataDxfId="99"/>
+    <tableColumn id="16" xr3:uid="{07C56306-EF8D-45EF-BC0C-FA7F2A15FEF3}" uniqueName="16" name="Mfr." queryTableFieldId="15" dataDxfId="98"/>
+    <tableColumn id="17" xr3:uid="{19635C0F-7BD1-4660-98C6-93346F766B86}" uniqueName="17" name="Order Qty." queryTableFieldId="16" dataDxfId="97" dataCellStyle="Currency"/>
+    <tableColumn id="18" xr3:uid="{A46DB81F-05A4-4B42-8CA7-8DD56227E5E7}" uniqueName="18" name="Unit Price(USD)" queryTableFieldId="17" dataDxfId="96" dataCellStyle="Currency"/>
+    <tableColumn id="19" xr3:uid="{570EBF30-7625-4C4F-A1A9-5A6C29E3344C}" uniqueName="19" name="Ext.Price(USD)" queryTableFieldId="18" dataDxfId="95" dataCellStyle="Currency"/>
+    <tableColumn id="20" xr3:uid="{1210C2A8-B78E-4F49-8D59-4D7358DDF469}" uniqueName="20" name="LCSC#/MOUSER" queryTableFieldId="19" dataDxfId="94"/>
+    <tableColumn id="21" xr3:uid="{DCDFBA0B-E1DF-4891-B6DE-50DD37843C8F}" uniqueName="21" name="Package" queryTableFieldId="20" dataDxfId="93"/>
+    <tableColumn id="22" xr3:uid="{EE553BAA-235A-4ADE-BF21-5A6D487E525F}" uniqueName="22" name="Min" queryTableFieldId="21" dataDxfId="92"/>
+    <tableColumn id="23" xr3:uid="{EF5D702D-6003-4207-8949-2FAAAEA59C21}" uniqueName="23" name="Mult" queryTableFieldId="22" dataDxfId="91"/>
+    <tableColumn id="24" xr3:uid="{FC548331-4E82-4F18-8F1B-96AD5CFD679F}" uniqueName="24" name="SPQ" queryTableFieldId="23" dataDxfId="90"/>
+    <tableColumn id="25" xr3:uid="{4CE5E4B3-AC89-4D44-992B-1F594AE2EC4A}" uniqueName="25" name="Availability" queryTableFieldId="24" dataDxfId="89"/>
+    <tableColumn id="26" xr3:uid="{8719B838-3310-4B06-B6C2-7223B1B40BC9}" uniqueName="26" name="Stock Status" queryTableFieldId="25" dataDxfId="88"/>
+    <tableColumn id="27" xr3:uid="{2577FF1C-2965-441F-B3FF-7C6FD0944441}" uniqueName="27" name="Customer Notes" queryTableFieldId="26" dataDxfId="87"/>
+    <tableColumn id="28" xr3:uid="{5613E865-76FA-42C7-807E-255777292765}" uniqueName="28" name="Description" queryTableFieldId="27" dataDxfId="86"/>
     <tableColumn id="29" xr3:uid="{DC4F61A6-52E4-4ABC-BD2A-0891230BC00B}" uniqueName="29" name="Matched status" queryTableFieldId="28" dataDxfId="5"/>
-    <tableColumn id="30" xr3:uid="{F1A13F5D-E76A-4CC6-B004-7EA2E6343DD2}" uniqueName="30" name="Product Link" queryTableFieldId="29" dataDxfId="4"/>
+    <tableColumn id="30" xr3:uid="{F1A13F5D-E76A-4CC6-B004-7EA2E6343DD2}" uniqueName="30" name="Product Link" queryTableFieldId="29" dataDxfId="4" dataCellStyle="Hyperlink 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3570,36 +3567,36 @@
   </sortState>
   <tableColumns count="29">
     <tableColumn id="1" xr3:uid="{497A9602-423A-4EE5-A4C3-05DBCE27F0C5}" uniqueName="1" name="Id" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{248C9EEE-C317-4CF2-8FF9-EBC3B367C080}" uniqueName="2" name="Designator" queryTableFieldId="2" dataDxfId="86"/>
-    <tableColumn id="3" xr3:uid="{36AFF123-E529-4AD9-B586-671130A051FA}" uniqueName="3" name="Footprint" queryTableFieldId="3" dataDxfId="85"/>
+    <tableColumn id="2" xr3:uid="{248C9EEE-C317-4CF2-8FF9-EBC3B367C080}" uniqueName="2" name="Designator" queryTableFieldId="2" dataDxfId="85"/>
+    <tableColumn id="3" xr3:uid="{36AFF123-E529-4AD9-B586-671130A051FA}" uniqueName="3" name="Footprint" queryTableFieldId="3" dataDxfId="84"/>
     <tableColumn id="4" xr3:uid="{3676B207-F980-400C-B584-7AEC2C881662}" uniqueName="4" name="Quantity" queryTableFieldId="4"/>
-    <tableColumn id="5" xr3:uid="{5E97CF41-ABB3-47AE-A0AC-B0E7E29D04F2}" uniqueName="5" name="Designation" queryTableFieldId="5" dataDxfId="84"/>
-    <tableColumn id="6" xr3:uid="{9E4029D5-EC40-4FD8-A618-F86B9AC55CCF}" uniqueName="6" name="Supplier and ref" queryTableFieldId="6" dataDxfId="83"/>
-    <tableColumn id="7" xr3:uid="{AD3BD5D5-70CF-457B-9E36-2BF3A5A4569F}" uniqueName="7" name="Column1" queryTableFieldId="7" dataDxfId="82"/>
-    <tableColumn id="8" xr3:uid="{312509E5-FBDF-4828-AE6F-FA834B68DF72}" uniqueName="8" name="Needed quantity" queryTableFieldId="8" dataDxfId="81">
+    <tableColumn id="5" xr3:uid="{5E97CF41-ABB3-47AE-A0AC-B0E7E29D04F2}" uniqueName="5" name="Designation" queryTableFieldId="5" dataDxfId="83"/>
+    <tableColumn id="6" xr3:uid="{9E4029D5-EC40-4FD8-A618-F86B9AC55CCF}" uniqueName="6" name="Supplier and ref" queryTableFieldId="6" dataDxfId="82"/>
+    <tableColumn id="7" xr3:uid="{AD3BD5D5-70CF-457B-9E36-2BF3A5A4569F}" uniqueName="7" name="Column1" queryTableFieldId="7" dataDxfId="81"/>
+    <tableColumn id="8" xr3:uid="{312509E5-FBDF-4828-AE6F-FA834B68DF72}" uniqueName="8" name="Needed quantity" queryTableFieldId="8" dataDxfId="80">
       <calculatedColumnFormula>2*Display_panel7[[#This Row],[Quantity]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{466BF7CA-A66E-4E93-A410-26712E4A088D}" uniqueName="9" name="-" queryTableFieldId="9" dataDxfId="80"/>
-    <tableColumn id="10" xr3:uid="{EF9CED38-6BA4-4B5E-A768-E8F7877DA34C}" uniqueName="10" name="LCSC" queryTableFieldId="10" dataDxfId="79"/>
-    <tableColumn id="11" xr3:uid="{B8AF37A0-7622-4CE8-B4F8-07F8A264DAFC}" uniqueName="11" name="MOUSER" queryTableFieldId="11" dataDxfId="78"/>
-    <tableColumn id="12" xr3:uid="{3CC847EE-DB6C-4D10-A4FE-5AF7D6DAC000}" uniqueName="12" name="Already in another pcb" queryTableFieldId="12" dataDxfId="77"/>
-    <tableColumn id="13" xr3:uid="{4209E125-D2D4-4118-AAF7-2424A4EE1570}" uniqueName="13" name="--" queryTableFieldId="13" dataDxfId="49"/>
-    <tableColumn id="14" xr3:uid="{F77F0236-F98A-4965-9182-ADC25F4B7E38}" uniqueName="14" name="Mrf#" queryTableFieldId="14" dataDxfId="33"/>
-    <tableColumn id="15" xr3:uid="{35B8A93E-B4A7-4A83-9024-CC101868A70A}" uniqueName="15" name="Mfr." queryTableFieldId="15" dataDxfId="32"/>
-    <tableColumn id="16" xr3:uid="{E562ACF4-D8CD-4985-8EC9-26D45054BB92}" uniqueName="16" name="Order Qty." queryTableFieldId="16" dataDxfId="31" dataCellStyle="Currency"/>
-    <tableColumn id="17" xr3:uid="{4B8A9EA3-8B9F-48DB-B5CE-DD5C61A296C3}" uniqueName="17" name="Unit Price(USD)" queryTableFieldId="17" dataDxfId="30" dataCellStyle="Currency"/>
-    <tableColumn id="18" xr3:uid="{681F7274-0403-4F56-A317-DD049A8A07BF}" uniqueName="18" name="Ext.Price(USD)" queryTableFieldId="18" dataDxfId="29" dataCellStyle="Currency"/>
-    <tableColumn id="19" xr3:uid="{6073EC40-E9B7-4260-A82D-A28FAFFCC35E}" uniqueName="19" name="LCSC#" queryTableFieldId="19" dataDxfId="28"/>
-    <tableColumn id="20" xr3:uid="{EEC6C7E9-C4FE-4094-B250-BB6B33BB8464}" uniqueName="20" name="Package" queryTableFieldId="20" dataDxfId="27"/>
-    <tableColumn id="21" xr3:uid="{81D33918-2986-4E3F-BD4D-051917441601}" uniqueName="21" name="Min" queryTableFieldId="21" dataDxfId="26"/>
-    <tableColumn id="22" xr3:uid="{F26EC7E1-D7C6-4ECE-B10B-99623AAEFE95}" uniqueName="22" name="Mult" queryTableFieldId="22" dataDxfId="25"/>
-    <tableColumn id="23" xr3:uid="{7AC43392-CA85-4105-977C-51ED085E626D}" uniqueName="23" name="SPQ" queryTableFieldId="23" dataDxfId="24"/>
-    <tableColumn id="24" xr3:uid="{054AEE52-D1A0-4011-B23F-BB94CFAE1142}" uniqueName="24" name="Availability" queryTableFieldId="24" dataDxfId="23"/>
-    <tableColumn id="25" xr3:uid="{0AA1D208-8245-459D-94F6-604BED0B7234}" uniqueName="25" name="Stock Status" queryTableFieldId="25" dataDxfId="22"/>
-    <tableColumn id="26" xr3:uid="{C5ABA018-08A0-4C05-B2A8-0C9FFA3C4F07}" uniqueName="26" name="Customer Notes" queryTableFieldId="26" dataDxfId="21"/>
-    <tableColumn id="27" xr3:uid="{95403B65-8FFF-446B-907D-9606ACF3E1AB}" uniqueName="27" name="Description" queryTableFieldId="27" dataDxfId="20"/>
+    <tableColumn id="9" xr3:uid="{466BF7CA-A66E-4E93-A410-26712E4A088D}" uniqueName="9" name="-" queryTableFieldId="9" dataDxfId="79"/>
+    <tableColumn id="10" xr3:uid="{EF9CED38-6BA4-4B5E-A768-E8F7877DA34C}" uniqueName="10" name="LCSC" queryTableFieldId="10" dataDxfId="78"/>
+    <tableColumn id="11" xr3:uid="{B8AF37A0-7622-4CE8-B4F8-07F8A264DAFC}" uniqueName="11" name="MOUSER" queryTableFieldId="11" dataDxfId="77"/>
+    <tableColumn id="12" xr3:uid="{3CC847EE-DB6C-4D10-A4FE-5AF7D6DAC000}" uniqueName="12" name="Already in another pcb" queryTableFieldId="12" dataDxfId="76"/>
+    <tableColumn id="13" xr3:uid="{4209E125-D2D4-4118-AAF7-2424A4EE1570}" uniqueName="13" name="--" queryTableFieldId="13" dataDxfId="75"/>
+    <tableColumn id="14" xr3:uid="{F77F0236-F98A-4965-9182-ADC25F4B7E38}" uniqueName="14" name="Mrf#" queryTableFieldId="14" dataDxfId="74"/>
+    <tableColumn id="15" xr3:uid="{35B8A93E-B4A7-4A83-9024-CC101868A70A}" uniqueName="15" name="Mfr." queryTableFieldId="15" dataDxfId="73"/>
+    <tableColumn id="16" xr3:uid="{E562ACF4-D8CD-4985-8EC9-26D45054BB92}" uniqueName="16" name="Order Qty." queryTableFieldId="16" dataDxfId="72" dataCellStyle="Currency"/>
+    <tableColumn id="17" xr3:uid="{4B8A9EA3-8B9F-48DB-B5CE-DD5C61A296C3}" uniqueName="17" name="Unit Price(USD)" queryTableFieldId="17" dataDxfId="71" dataCellStyle="Currency"/>
+    <tableColumn id="18" xr3:uid="{681F7274-0403-4F56-A317-DD049A8A07BF}" uniqueName="18" name="Ext.Price(USD)" queryTableFieldId="18" dataDxfId="70" dataCellStyle="Currency"/>
+    <tableColumn id="19" xr3:uid="{6073EC40-E9B7-4260-A82D-A28FAFFCC35E}" uniqueName="19" name="LCSC#/MOUSER" queryTableFieldId="19" dataDxfId="69"/>
+    <tableColumn id="20" xr3:uid="{EEC6C7E9-C4FE-4094-B250-BB6B33BB8464}" uniqueName="20" name="Package" queryTableFieldId="20" dataDxfId="68"/>
+    <tableColumn id="21" xr3:uid="{81D33918-2986-4E3F-BD4D-051917441601}" uniqueName="21" name="Min" queryTableFieldId="21" dataDxfId="67"/>
+    <tableColumn id="22" xr3:uid="{F26EC7E1-D7C6-4ECE-B10B-99623AAEFE95}" uniqueName="22" name="Mult" queryTableFieldId="22" dataDxfId="66"/>
+    <tableColumn id="23" xr3:uid="{7AC43392-CA85-4105-977C-51ED085E626D}" uniqueName="23" name="SPQ" queryTableFieldId="23" dataDxfId="65"/>
+    <tableColumn id="24" xr3:uid="{054AEE52-D1A0-4011-B23F-BB94CFAE1142}" uniqueName="24" name="Availability" queryTableFieldId="24" dataDxfId="64"/>
+    <tableColumn id="25" xr3:uid="{0AA1D208-8245-459D-94F6-604BED0B7234}" uniqueName="25" name="Stock Status" queryTableFieldId="25" dataDxfId="63"/>
+    <tableColumn id="26" xr3:uid="{C5ABA018-08A0-4C05-B2A8-0C9FFA3C4F07}" uniqueName="26" name="Customer Notes" queryTableFieldId="26" dataDxfId="62"/>
+    <tableColumn id="27" xr3:uid="{95403B65-8FFF-446B-907D-9606ACF3E1AB}" uniqueName="27" name="Description" queryTableFieldId="27" dataDxfId="61"/>
     <tableColumn id="28" xr3:uid="{C1157F66-0BE1-48D4-BF0E-A795DED00553}" uniqueName="28" name="Matched status" queryTableFieldId="28" dataDxfId="3"/>
-    <tableColumn id="29" xr3:uid="{B225C4F7-C17C-4475-85AA-F874BA501B03}" uniqueName="29" name="Product Link" queryTableFieldId="29" dataDxfId="2"/>
+    <tableColumn id="29" xr3:uid="{B225C4F7-C17C-4475-85AA-F874BA501B03}" uniqueName="29" name="Product Link" queryTableFieldId="29" dataDxfId="2" dataCellStyle="Hyperlink 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3613,34 +3610,34 @@
   </sortState>
   <tableColumns count="29">
     <tableColumn id="1" xr3:uid="{0E63F159-3CED-4B29-86B6-632E7C1C742B}" uniqueName="1" name="Id" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{D1DE625A-59DE-459D-A45A-536F2DCFBF7F}" uniqueName="2" name="Designator" queryTableFieldId="2" dataDxfId="76"/>
-    <tableColumn id="3" xr3:uid="{873A6810-3388-41FB-952D-50FC4CA27EDB}" uniqueName="3" name="Footprint" queryTableFieldId="3" dataDxfId="75"/>
+    <tableColumn id="2" xr3:uid="{D1DE625A-59DE-459D-A45A-536F2DCFBF7F}" uniqueName="2" name="Designator" queryTableFieldId="2" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{873A6810-3388-41FB-952D-50FC4CA27EDB}" uniqueName="3" name="Footprint" queryTableFieldId="3" dataDxfId="59"/>
     <tableColumn id="4" xr3:uid="{44B2CDFF-B5E8-4E2D-AB83-7100F24D4468}" uniqueName="4" name="Quantity" queryTableFieldId="4"/>
-    <tableColumn id="5" xr3:uid="{22FA568B-01D6-4A0C-9ECE-923A51F41F44}" uniqueName="5" name="Designation" queryTableFieldId="5" dataDxfId="74"/>
-    <tableColumn id="6" xr3:uid="{78CCE0AA-C426-48A2-9C9F-C7FD9E916E42}" uniqueName="6" name="Supplier and ref" queryTableFieldId="6" dataDxfId="73"/>
-    <tableColumn id="7" xr3:uid="{97C1A426-B683-4782-81E7-54C43CABE5DE}" uniqueName="7" name="Column1" queryTableFieldId="7" dataDxfId="72"/>
-    <tableColumn id="8" xr3:uid="{416DEE51-9BEE-4225-8B54-F5BF6C08F6B9}" uniqueName="8" name="Needed quantity" queryTableFieldId="8" dataDxfId="71"/>
-    <tableColumn id="9" xr3:uid="{32E30C7A-53F3-408B-8293-6A9B9B9AC1DF}" uniqueName="9" name="-" queryTableFieldId="9" dataDxfId="70"/>
-    <tableColumn id="10" xr3:uid="{D6C8BC49-3D09-492D-B4A4-089F31B50C42}" uniqueName="10" name="LCSC" queryTableFieldId="10" dataDxfId="69"/>
-    <tableColumn id="11" xr3:uid="{CC107E5C-29C8-4CCE-8483-88216043072D}" uniqueName="11" name="MOUSER" queryTableFieldId="11" dataDxfId="68"/>
-    <tableColumn id="12" xr3:uid="{E7EC2C75-44FB-4D79-B6F6-F9B011D6211F}" uniqueName="12" name="Already in another pcb" queryTableFieldId="12" dataDxfId="67"/>
-    <tableColumn id="13" xr3:uid="{0C385EB9-878B-4C2B-96C7-A160EB6C8B7B}" uniqueName="13" name="--" queryTableFieldId="13" dataDxfId="48"/>
-    <tableColumn id="14" xr3:uid="{D8B5CD8B-44BF-4725-BCDE-21E44EEBF205}" uniqueName="14" name="Mrf#" queryTableFieldId="14" dataDxfId="19"/>
-    <tableColumn id="15" xr3:uid="{3EF7D800-5FBD-4B86-AE11-67617320382F}" uniqueName="15" name="Mfr." queryTableFieldId="15" dataDxfId="18"/>
-    <tableColumn id="16" xr3:uid="{6D0D8B28-79C8-4C77-9563-E1F5D6B87774}" uniqueName="16" name="Order Qty." queryTableFieldId="16" dataDxfId="17" dataCellStyle="Currency"/>
-    <tableColumn id="17" xr3:uid="{4CE14486-CC74-4467-B9AD-79C240E52F93}" uniqueName="17" name="Unit Price(USD)" queryTableFieldId="17" dataDxfId="16" dataCellStyle="Currency"/>
-    <tableColumn id="18" xr3:uid="{2F6A5361-9124-455F-B3F1-383018915EB3}" uniqueName="18" name="Ext.Price(USD)" queryTableFieldId="18" dataDxfId="15" dataCellStyle="Currency"/>
-    <tableColumn id="19" xr3:uid="{78F98052-EB98-43FF-8EE5-602D557FB4D3}" uniqueName="19" name="LCSC#" queryTableFieldId="19" dataDxfId="14"/>
-    <tableColumn id="20" xr3:uid="{4F449396-32DC-4534-BFE5-AA61E6C0DC5A}" uniqueName="20" name="Package" queryTableFieldId="20" dataDxfId="13"/>
-    <tableColumn id="21" xr3:uid="{26D2A300-326B-49F5-84C9-02EB05291F90}" uniqueName="21" name="Min" queryTableFieldId="21" dataDxfId="12"/>
-    <tableColumn id="22" xr3:uid="{5CAF8612-E695-4A48-836A-F8A9EDFB3CB8}" uniqueName="22" name="Mult" queryTableFieldId="22" dataDxfId="11"/>
-    <tableColumn id="23" xr3:uid="{9A05AEF9-585A-4855-B11C-CAE738DD58FA}" uniqueName="23" name="SPQ" queryTableFieldId="23" dataDxfId="10"/>
-    <tableColumn id="24" xr3:uid="{3D7F11A3-37D2-4805-AEBA-B9E26E5E28E9}" uniqueName="24" name="Availability" queryTableFieldId="24" dataDxfId="9"/>
-    <tableColumn id="25" xr3:uid="{933DBD96-9E4F-43F7-A800-CD83B0A44E24}" uniqueName="25" name="Stock Status" queryTableFieldId="25" dataDxfId="8"/>
-    <tableColumn id="26" xr3:uid="{32899468-D5AC-4CCC-BF0C-B9A3CB2B5492}" uniqueName="26" name="Customer Notes" queryTableFieldId="26" dataDxfId="7"/>
-    <tableColumn id="27" xr3:uid="{8CDB5DD7-778C-4CF7-A3C5-BE2C00EB1D37}" uniqueName="27" name="Description" queryTableFieldId="27" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{22FA568B-01D6-4A0C-9ECE-923A51F41F44}" uniqueName="5" name="Designation" queryTableFieldId="5" dataDxfId="58"/>
+    <tableColumn id="6" xr3:uid="{78CCE0AA-C426-48A2-9C9F-C7FD9E916E42}" uniqueName="6" name="Supplier and ref" queryTableFieldId="6" dataDxfId="57"/>
+    <tableColumn id="7" xr3:uid="{97C1A426-B683-4782-81E7-54C43CABE5DE}" uniqueName="7" name="Column1" queryTableFieldId="7" dataDxfId="56"/>
+    <tableColumn id="8" xr3:uid="{416DEE51-9BEE-4225-8B54-F5BF6C08F6B9}" uniqueName="8" name="Needed quantity" queryTableFieldId="8" dataDxfId="55"/>
+    <tableColumn id="9" xr3:uid="{32E30C7A-53F3-408B-8293-6A9B9B9AC1DF}" uniqueName="9" name="-" queryTableFieldId="9" dataDxfId="54"/>
+    <tableColumn id="10" xr3:uid="{D6C8BC49-3D09-492D-B4A4-089F31B50C42}" uniqueName="10" name="LCSC" queryTableFieldId="10" dataDxfId="53"/>
+    <tableColumn id="11" xr3:uid="{CC107E5C-29C8-4CCE-8483-88216043072D}" uniqueName="11" name="MOUSER" queryTableFieldId="11" dataDxfId="52"/>
+    <tableColumn id="12" xr3:uid="{E7EC2C75-44FB-4D79-B6F6-F9B011D6211F}" uniqueName="12" name="Already in another pcb" queryTableFieldId="12" dataDxfId="51"/>
+    <tableColumn id="13" xr3:uid="{0C385EB9-878B-4C2B-96C7-A160EB6C8B7B}" uniqueName="13" name="--" queryTableFieldId="13" dataDxfId="50"/>
+    <tableColumn id="14" xr3:uid="{D8B5CD8B-44BF-4725-BCDE-21E44EEBF205}" uniqueName="14" name="Mrf#" queryTableFieldId="14" dataDxfId="49"/>
+    <tableColumn id="15" xr3:uid="{3EF7D800-5FBD-4B86-AE11-67617320382F}" uniqueName="15" name="Mfr." queryTableFieldId="15" dataDxfId="48"/>
+    <tableColumn id="16" xr3:uid="{6D0D8B28-79C8-4C77-9563-E1F5D6B87774}" uniqueName="16" name="Order Qty." queryTableFieldId="16" dataDxfId="47" dataCellStyle="Currency"/>
+    <tableColumn id="17" xr3:uid="{4CE14486-CC74-4467-B9AD-79C240E52F93}" uniqueName="17" name="Unit Price(USD)" queryTableFieldId="17" dataDxfId="46" dataCellStyle="Currency"/>
+    <tableColumn id="18" xr3:uid="{2F6A5361-9124-455F-B3F1-383018915EB3}" uniqueName="18" name="Ext.Price(USD)" queryTableFieldId="18" dataDxfId="45" dataCellStyle="Currency"/>
+    <tableColumn id="19" xr3:uid="{78F98052-EB98-43FF-8EE5-602D557FB4D3}" uniqueName="19" name="LCSC#/MOUSER" queryTableFieldId="19" dataDxfId="44"/>
+    <tableColumn id="20" xr3:uid="{4F449396-32DC-4534-BFE5-AA61E6C0DC5A}" uniqueName="20" name="Package" queryTableFieldId="20" dataDxfId="43"/>
+    <tableColumn id="21" xr3:uid="{26D2A300-326B-49F5-84C9-02EB05291F90}" uniqueName="21" name="Min" queryTableFieldId="21" dataDxfId="42"/>
+    <tableColumn id="22" xr3:uid="{5CAF8612-E695-4A48-836A-F8A9EDFB3CB8}" uniqueName="22" name="Mult" queryTableFieldId="22" dataDxfId="41"/>
+    <tableColumn id="23" xr3:uid="{9A05AEF9-585A-4855-B11C-CAE738DD58FA}" uniqueName="23" name="SPQ" queryTableFieldId="23" dataDxfId="40"/>
+    <tableColumn id="24" xr3:uid="{3D7F11A3-37D2-4805-AEBA-B9E26E5E28E9}" uniqueName="24" name="Availability" queryTableFieldId="24" dataDxfId="39"/>
+    <tableColumn id="25" xr3:uid="{933DBD96-9E4F-43F7-A800-CD83B0A44E24}" uniqueName="25" name="Stock Status" queryTableFieldId="25" dataDxfId="38"/>
+    <tableColumn id="26" xr3:uid="{32899468-D5AC-4CCC-BF0C-B9A3CB2B5492}" uniqueName="26" name="Customer Notes" queryTableFieldId="26" dataDxfId="37"/>
+    <tableColumn id="27" xr3:uid="{8CDB5DD7-778C-4CF7-A3C5-BE2C00EB1D37}" uniqueName="27" name="Description" queryTableFieldId="27" dataDxfId="36"/>
     <tableColumn id="28" xr3:uid="{F1DA22D8-5468-4D00-B4F4-CB4FD27BE53B}" uniqueName="28" name="Matched status" queryTableFieldId="28" dataDxfId="1"/>
-    <tableColumn id="29" xr3:uid="{687D4C7B-94A2-47A4-BECA-516084FF4352}" uniqueName="29" name="Product Link" queryTableFieldId="29" dataDxfId="0"/>
+    <tableColumn id="29" xr3:uid="{687D4C7B-94A2-47A4-BECA-516084FF4352}" uniqueName="29" name="Product Link" queryTableFieldId="29" dataDxfId="0" dataCellStyle="Hyperlink 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3651,12 +3648,12 @@
   <autoFilter ref="A1:G10" xr:uid="{358C07D9-C534-4C2D-B737-344400F670C4}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{0F19A646-43F4-4862-8B93-9080417C7268}" uniqueName="1" name="Id" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{7198E0C1-4967-4BBD-9D55-A70B2A61C192}" uniqueName="2" name="Designator" queryTableFieldId="2" dataDxfId="107"/>
-    <tableColumn id="3" xr3:uid="{C2A2451A-0F59-404F-AA66-0DD98A96CB6B}" uniqueName="3" name="Footprint" queryTableFieldId="3" dataDxfId="106"/>
+    <tableColumn id="2" xr3:uid="{7198E0C1-4967-4BBD-9D55-A70B2A61C192}" uniqueName="2" name="Designator" queryTableFieldId="2" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{C2A2451A-0F59-404F-AA66-0DD98A96CB6B}" uniqueName="3" name="Footprint" queryTableFieldId="3" dataDxfId="34"/>
     <tableColumn id="4" xr3:uid="{57EDD4F3-19D9-42B5-A4D4-17B50797C919}" uniqueName="4" name="Quantity" queryTableFieldId="4"/>
-    <tableColumn id="5" xr3:uid="{AC6AFA26-0E57-46AC-BB98-3942162B3F06}" uniqueName="5" name="Designation" queryTableFieldId="5" dataDxfId="105"/>
-    <tableColumn id="6" xr3:uid="{3285DEC9-31B3-4F44-B1AD-0B3851AF39BA}" uniqueName="6" name="Supplier and ref" queryTableFieldId="6" dataDxfId="104"/>
-    <tableColumn id="7" xr3:uid="{AA28C35C-D1F9-457B-A91B-14B4A9A05C17}" uniqueName="7" name="Column1" queryTableFieldId="7" dataDxfId="103"/>
+    <tableColumn id="5" xr3:uid="{AC6AFA26-0E57-46AC-BB98-3942162B3F06}" uniqueName="5" name="Designation" queryTableFieldId="5" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{3285DEC9-31B3-4F44-B1AD-0B3851AF39BA}" uniqueName="6" name="Supplier and ref" queryTableFieldId="6" dataDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{AA28C35C-D1F9-457B-A91B-14B4A9A05C17}" uniqueName="7" name="Column1" queryTableFieldId="7" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3670,19 +3667,19 @@
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{ADE8F525-CFD6-41FB-A869-878D887125F2}" uniqueName="1" name="Id" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{06802B0A-38DB-4939-98FE-D825FBBCF621}" uniqueName="2" name="Designator" queryTableFieldId="2" dataDxfId="102"/>
-    <tableColumn id="3" xr3:uid="{A0E49D32-4602-4A36-A99A-61255BE52689}" uniqueName="3" name="Footprint" queryTableFieldId="3" dataDxfId="101"/>
+    <tableColumn id="2" xr3:uid="{06802B0A-38DB-4939-98FE-D825FBBCF621}" uniqueName="2" name="Designator" queryTableFieldId="2" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{A0E49D32-4602-4A36-A99A-61255BE52689}" uniqueName="3" name="Footprint" queryTableFieldId="3" dataDxfId="29"/>
     <tableColumn id="4" xr3:uid="{2639D562-1AB7-4369-9C38-6DE58E9DE4E0}" uniqueName="4" name="Quantity" queryTableFieldId="4"/>
-    <tableColumn id="5" xr3:uid="{E918130A-210D-4D0D-B354-0424657F3D8A}" uniqueName="5" name="Designation" queryTableFieldId="5" dataDxfId="100"/>
-    <tableColumn id="6" xr3:uid="{2852533A-8BB7-4324-9C65-B20AD7F9634F}" uniqueName="6" name="Supplier and ref" queryTableFieldId="6" dataDxfId="99"/>
-    <tableColumn id="7" xr3:uid="{FCD08B98-7123-4ED3-95E6-F7165F6496EF}" uniqueName="7" name="Column1" queryTableFieldId="7" dataDxfId="98"/>
-    <tableColumn id="10" xr3:uid="{D704FAE8-15F6-48B1-9F78-ECE42633C6A6}" uniqueName="10" name="Needed quantity" queryTableFieldId="9" dataDxfId="97">
+    <tableColumn id="5" xr3:uid="{E918130A-210D-4D0D-B354-0424657F3D8A}" uniqueName="5" name="Designation" queryTableFieldId="5" dataDxfId="28"/>
+    <tableColumn id="6" xr3:uid="{2852533A-8BB7-4324-9C65-B20AD7F9634F}" uniqueName="6" name="Supplier and ref" queryTableFieldId="6" dataDxfId="27"/>
+    <tableColumn id="7" xr3:uid="{FCD08B98-7123-4ED3-95E6-F7165F6496EF}" uniqueName="7" name="Column1" queryTableFieldId="7" dataDxfId="26"/>
+    <tableColumn id="10" xr3:uid="{D704FAE8-15F6-48B1-9F78-ECE42633C6A6}" uniqueName="10" name="Needed quantity" queryTableFieldId="9" dataDxfId="25">
       <calculatedColumnFormula>2*Artnet_DMX_Converter[[#This Row],[Quantity]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{912033B7-820A-4CB4-A444-84EA4F66B927}" uniqueName="8" name="_1" queryTableFieldId="8" dataDxfId="96"/>
-    <tableColumn id="11" xr3:uid="{D185F272-ECD8-4D0C-A8C0-5C517F5CB2C3}" uniqueName="11" name="Column12" queryTableFieldId="10" dataDxfId="95"/>
-    <tableColumn id="12" xr3:uid="{8235DE14-4219-4B94-81A0-74DA669B2200}" uniqueName="12" name="Column13" queryTableFieldId="11" dataDxfId="94"/>
-    <tableColumn id="13" xr3:uid="{0CB54720-3FD3-41A1-B176-167D3F8B9C1F}" uniqueName="13" name="Column14" queryTableFieldId="12" dataDxfId="93"/>
+    <tableColumn id="8" xr3:uid="{912033B7-820A-4CB4-A444-84EA4F66B927}" uniqueName="8" name="_1" queryTableFieldId="8" dataDxfId="24"/>
+    <tableColumn id="11" xr3:uid="{D185F272-ECD8-4D0C-A8C0-5C517F5CB2C3}" uniqueName="11" name="Column12" queryTableFieldId="10" dataDxfId="23"/>
+    <tableColumn id="12" xr3:uid="{8235DE14-4219-4B94-81A0-74DA669B2200}" uniqueName="12" name="Column13" queryTableFieldId="11" dataDxfId="22"/>
+    <tableColumn id="13" xr3:uid="{0CB54720-3FD3-41A1-B176-167D3F8B9C1F}" uniqueName="13" name="Column14" queryTableFieldId="12" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3693,13 +3690,13 @@
   <autoFilter ref="A1:H12" xr:uid="{7769F78E-5E6C-4F2E-A421-D9864D32DBFF}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{BEBDD4F5-047E-42EE-AF7A-AEC96CC412EB}" uniqueName="1" name="Id" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{70C04B8F-9B5D-4AE8-811E-7A325F5B3B32}" uniqueName="2" name="Designator" queryTableFieldId="2" dataDxfId="92"/>
-    <tableColumn id="3" xr3:uid="{5D3B3C5B-89C3-4145-BEFA-49CD552602EC}" uniqueName="3" name="Footprint" queryTableFieldId="3" dataDxfId="91"/>
+    <tableColumn id="2" xr3:uid="{70C04B8F-9B5D-4AE8-811E-7A325F5B3B32}" uniqueName="2" name="Designator" queryTableFieldId="2" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{5D3B3C5B-89C3-4145-BEFA-49CD552602EC}" uniqueName="3" name="Footprint" queryTableFieldId="3" dataDxfId="19"/>
     <tableColumn id="4" xr3:uid="{C6D2277C-C53C-42BD-B1B1-3F5BD927522F}" uniqueName="4" name="Quantity" queryTableFieldId="4"/>
-    <tableColumn id="5" xr3:uid="{50C12BFC-08EC-4014-8DE1-7360FE30FFEE}" uniqueName="5" name="Designation" queryTableFieldId="5" dataDxfId="90"/>
-    <tableColumn id="6" xr3:uid="{5E872B7B-44C6-474C-8EE6-2996F8257863}" uniqueName="6" name="Supplier and ref" queryTableFieldId="6" dataDxfId="89"/>
-    <tableColumn id="7" xr3:uid="{8616BBA3-0AE5-4D84-BE4F-A09C69812E1F}" uniqueName="7" name="Column1" queryTableFieldId="7" dataDxfId="88"/>
-    <tableColumn id="8" xr3:uid="{83C5AA2C-C2E2-4E7E-82D8-7C221C32DC65}" uniqueName="8" name="_1" queryTableFieldId="8" dataDxfId="87"/>
+    <tableColumn id="5" xr3:uid="{50C12BFC-08EC-4014-8DE1-7360FE30FFEE}" uniqueName="5" name="Designation" queryTableFieldId="5" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{5E872B7B-44C6-474C-8EE6-2996F8257863}" uniqueName="6" name="Supplier and ref" queryTableFieldId="6" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{8616BBA3-0AE5-4D84-BE4F-A09C69812E1F}" uniqueName="7" name="Column1" queryTableFieldId="7" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{83C5AA2C-C2E2-4E7E-82D8-7C221C32DC65}" uniqueName="8" name="_1" queryTableFieldId="8" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4027,22 +4024,22 @@
   <cols>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="43" customWidth="1"/>
-    <col min="5" max="5" width="27" customWidth="1"/>
+    <col min="5" max="5" width="31.140625" customWidth="1"/>
     <col min="10" max="10" width="10.7109375" customWidth="1"/>
     <col min="11" max="11" width="11.28515625" customWidth="1"/>
     <col min="12" max="12" width="24.28515625" customWidth="1"/>
-    <col min="14" max="14" width="19.85546875" style="18" customWidth="1"/>
-    <col min="15" max="15" width="9.140625" style="18"/>
-    <col min="16" max="16" width="9.140625" style="19"/>
-    <col min="17" max="18" width="9.140625" style="23" customWidth="1"/>
-    <col min="19" max="19" width="21" style="18" customWidth="1"/>
-    <col min="20" max="20" width="21.85546875" style="18" customWidth="1"/>
-    <col min="21" max="24" width="9.140625" style="18"/>
-    <col min="25" max="25" width="14" style="18" customWidth="1"/>
-    <col min="26" max="26" width="9.140625" style="18"/>
-    <col min="27" max="27" width="43.28515625" style="18" customWidth="1"/>
-    <col min="28" max="28" width="9.140625" style="18"/>
-    <col min="29" max="29" width="23.5703125" style="27" customWidth="1"/>
+    <col min="14" max="14" width="46.85546875" style="14" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="14"/>
+    <col min="16" max="16" width="9.140625" style="15"/>
+    <col min="17" max="18" width="9.140625" style="19" customWidth="1"/>
+    <col min="19" max="19" width="21" style="14" customWidth="1"/>
+    <col min="20" max="20" width="21.85546875" style="14" customWidth="1"/>
+    <col min="21" max="24" width="9.140625" style="14"/>
+    <col min="25" max="25" width="14" style="14" customWidth="1"/>
+    <col min="26" max="26" width="9.140625" style="14"/>
+    <col min="27" max="27" width="43.28515625" style="14" customWidth="1"/>
+    <col min="28" max="28" width="9.140625" style="14"/>
+    <col min="29" max="29" width="104.5703125" style="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="15" customHeight="1">
@@ -4080,58 +4077,58 @@
         <v>226</v>
       </c>
       <c r="L1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="N1" s="6" t="s">
+        <v>622</v>
+      </c>
+      <c r="N1" s="5" t="s">
         <v>600</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="5" t="s">
         <v>601</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="P1" s="10" t="s">
         <v>602</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="Q1" s="11" t="s">
         <v>603</v>
       </c>
-      <c r="R1" s="14" t="s">
+      <c r="R1" s="11" t="s">
         <v>604</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="S1" s="5" t="s">
+        <v>653</v>
+      </c>
+      <c r="T1" s="5" t="s">
         <v>605</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" s="5" t="s">
         <v>606</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="V1" s="5" t="s">
         <v>607</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="W1" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="Y1" s="5" t="s">
         <v>610</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Z1" s="5" t="s">
         <v>611</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="AA1" s="5" t="s">
         <v>612</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AB1" s="5" t="s">
         <v>613</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AC1" s="5" t="s">
         <v>614</v>
-      </c>
-      <c r="AC1" s="7" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="15" customHeight="1">
@@ -4166,52 +4163,52 @@
       <c r="J2" t="s">
         <v>186</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="N2" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="O2" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="P2" s="9">
+      <c r="P2" s="7">
         <v>10</v>
       </c>
-      <c r="Q2" s="15">
+      <c r="Q2" s="12">
         <v>5.0299999999999997E-2</v>
       </c>
-      <c r="R2" s="15">
+      <c r="R2" s="12">
         <v>0.5</v>
       </c>
-      <c r="S2" s="8" t="s">
+      <c r="S2" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="T2" s="8" t="s">
+      <c r="T2" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="U2" s="8">
+      <c r="U2" s="6">
         <v>10</v>
       </c>
-      <c r="V2" s="8">
+      <c r="V2" s="6">
         <v>10</v>
       </c>
-      <c r="W2" s="8">
+      <c r="W2" s="6">
         <v>1000</v>
       </c>
-      <c r="X2" s="8">
+      <c r="X2" s="6">
         <v>61980</v>
       </c>
-      <c r="Y2" s="8" t="s">
+      <c r="Y2" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z2" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA2" s="8" t="s">
+      <c r="Z2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA2" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="AB2" s="10" t="s">
+      <c r="AB2" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC2" s="16" t="s">
+      <c r="AC2" s="23" t="s">
         <v>236</v>
       </c>
     </row>
@@ -4247,50 +4244,50 @@
       <c r="J3" t="s">
         <v>186</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="P3" s="9">
+      <c r="P3" s="7">
         <v>100</v>
       </c>
-      <c r="Q3" s="15">
+      <c r="Q3" s="12">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="R3" s="15">
+      <c r="R3" s="12">
         <v>0.13</v>
       </c>
-      <c r="S3" s="8" t="s">
+      <c r="S3" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="T3" s="8">
+      <c r="T3" s="6">
         <v>402</v>
       </c>
-      <c r="U3" s="8">
+      <c r="U3" s="6">
         <v>100</v>
       </c>
-      <c r="V3" s="8">
+      <c r="V3" s="6">
         <v>100</v>
       </c>
-      <c r="W3" s="8">
+      <c r="W3" s="6">
         <v>10000</v>
       </c>
-      <c r="X3" s="8">
+      <c r="X3" s="6">
         <v>22016000</v>
       </c>
-      <c r="Y3" s="8" t="s">
+      <c r="Y3" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z3" s="8"/>
-      <c r="AA3" s="8" t="s">
+      <c r="Z3" s="6"/>
+      <c r="AA3" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="AB3" s="10" t="s">
+      <c r="AB3" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC3" s="16" t="s">
+      <c r="AC3" s="23" t="s">
         <v>241</v>
       </c>
     </row>
@@ -4326,50 +4323,50 @@
       <c r="J4" t="s">
         <v>186</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="N4" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="O4" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="P4" s="9">
+      <c r="P4" s="7">
         <v>100</v>
       </c>
-      <c r="Q4" s="15">
+      <c r="Q4" s="12">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="R4" s="15">
+      <c r="R4" s="12">
         <v>0.37</v>
       </c>
-      <c r="S4" s="8" t="s">
+      <c r="S4" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="T4" s="8">
+      <c r="T4" s="6">
         <v>402</v>
       </c>
-      <c r="U4" s="8">
+      <c r="U4" s="6">
         <v>100</v>
       </c>
-      <c r="V4" s="8">
+      <c r="V4" s="6">
         <v>100</v>
       </c>
-      <c r="W4" s="8">
+      <c r="W4" s="6">
         <v>10000</v>
       </c>
-      <c r="X4" s="8">
+      <c r="X4" s="6">
         <v>454800</v>
       </c>
-      <c r="Y4" s="8" t="s">
+      <c r="Y4" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z4" s="8"/>
-      <c r="AA4" s="8" t="s">
+      <c r="Z4" s="6"/>
+      <c r="AA4" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="AB4" s="10" t="s">
+      <c r="AB4" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC4" s="16" t="s">
+      <c r="AC4" s="23" t="s">
         <v>245</v>
       </c>
     </row>
@@ -4405,50 +4402,50 @@
       <c r="J5" t="s">
         <v>186</v>
       </c>
-      <c r="N5" s="8" t="s">
+      <c r="N5" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="O5" s="8" t="s">
+      <c r="O5" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="P5" s="9">
+      <c r="P5" s="7">
         <v>50</v>
       </c>
-      <c r="Q5" s="15">
+      <c r="Q5" s="12">
         <v>6.1999999999999998E-3</v>
       </c>
-      <c r="R5" s="15">
+      <c r="R5" s="12">
         <v>0.31</v>
       </c>
-      <c r="S5" s="8" t="s">
+      <c r="S5" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="T5" s="8">
+      <c r="T5" s="6">
         <v>402</v>
       </c>
-      <c r="U5" s="8">
+      <c r="U5" s="6">
         <v>50</v>
       </c>
-      <c r="V5" s="8">
+      <c r="V5" s="6">
         <v>50</v>
       </c>
-      <c r="W5" s="8">
+      <c r="W5" s="6">
         <v>10000</v>
       </c>
-      <c r="X5" s="8">
+      <c r="X5" s="6">
         <v>5001000</v>
       </c>
-      <c r="Y5" s="8" t="s">
+      <c r="Y5" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z5" s="8"/>
-      <c r="AA5" s="8" t="s">
+      <c r="Z5" s="6"/>
+      <c r="AA5" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="AB5" s="10" t="s">
+      <c r="AB5" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC5" s="16" t="s">
+      <c r="AC5" s="23" t="s">
         <v>249</v>
       </c>
     </row>
@@ -4484,50 +4481,50 @@
       <c r="J6" t="s">
         <v>186</v>
       </c>
-      <c r="N6" s="8" t="s">
+      <c r="N6" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="O6" s="8" t="s">
+      <c r="O6" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="P6" s="9">
+      <c r="P6" s="7">
         <v>100</v>
       </c>
-      <c r="Q6" s="15">
+      <c r="Q6" s="12">
         <v>6.1999999999999998E-3</v>
       </c>
-      <c r="R6" s="15">
+      <c r="R6" s="12">
         <v>0.62</v>
       </c>
-      <c r="S6" s="8" t="s">
+      <c r="S6" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="T6" s="8">
+      <c r="T6" s="6">
         <v>603</v>
       </c>
-      <c r="U6" s="8">
+      <c r="U6" s="6">
         <v>100</v>
       </c>
-      <c r="V6" s="8">
+      <c r="V6" s="6">
         <v>100</v>
       </c>
-      <c r="W6" s="8">
+      <c r="W6" s="6">
         <v>4000</v>
       </c>
-      <c r="X6" s="8">
+      <c r="X6" s="6">
         <v>18800</v>
       </c>
-      <c r="Y6" s="8" t="s">
+      <c r="Y6" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z6" s="8"/>
-      <c r="AA6" s="8" t="s">
+      <c r="Z6" s="6"/>
+      <c r="AA6" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="AB6" s="10" t="s">
+      <c r="AB6" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC6" s="16" t="s">
+      <c r="AC6" s="23" t="s">
         <v>306</v>
       </c>
     </row>
@@ -4563,50 +4560,50 @@
       <c r="J7" t="s">
         <v>186</v>
       </c>
-      <c r="N7" s="8" t="s">
+      <c r="N7" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="O7" s="8" t="s">
+      <c r="O7" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="P7" s="9">
+      <c r="P7" s="7">
         <v>50</v>
       </c>
-      <c r="Q7" s="15">
+      <c r="Q7" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="R7" s="15">
+      <c r="R7" s="12">
         <v>0.25</v>
       </c>
-      <c r="S7" s="8" t="s">
+      <c r="S7" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="T7" s="8">
+      <c r="T7" s="6">
         <v>603</v>
       </c>
-      <c r="U7" s="8">
+      <c r="U7" s="6">
         <v>50</v>
       </c>
-      <c r="V7" s="8">
+      <c r="V7" s="6">
         <v>50</v>
       </c>
-      <c r="W7" s="8">
+      <c r="W7" s="6">
         <v>4000</v>
       </c>
-      <c r="X7" s="8">
+      <c r="X7" s="6">
         <v>107650</v>
       </c>
-      <c r="Y7" s="8" t="s">
+      <c r="Y7" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z7" s="8"/>
-      <c r="AA7" s="8" t="s">
+      <c r="Z7" s="6"/>
+      <c r="AA7" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="AB7" s="10" t="s">
+      <c r="AB7" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC7" s="16" t="s">
+      <c r="AC7" s="23" t="s">
         <v>302</v>
       </c>
     </row>
@@ -4642,50 +4639,50 @@
       <c r="J8" t="s">
         <v>186</v>
       </c>
-      <c r="N8" s="8" t="s">
+      <c r="N8" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="O8" s="8" t="s">
+      <c r="O8" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="P8" s="9">
+      <c r="P8" s="7">
         <v>100</v>
       </c>
-      <c r="Q8" s="15">
+      <c r="Q8" s="12">
         <v>6.4999999999999997E-3</v>
       </c>
-      <c r="R8" s="15">
+      <c r="R8" s="12">
         <v>0.65</v>
       </c>
-      <c r="S8" s="8" t="s">
+      <c r="S8" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="T8" s="8">
+      <c r="T8" s="6">
         <v>603</v>
       </c>
-      <c r="U8" s="8">
+      <c r="U8" s="6">
         <v>50</v>
       </c>
-      <c r="V8" s="8">
+      <c r="V8" s="6">
         <v>50</v>
       </c>
-      <c r="W8" s="8">
+      <c r="W8" s="6">
         <v>4000</v>
       </c>
-      <c r="X8" s="8">
+      <c r="X8" s="6">
         <v>175750</v>
       </c>
-      <c r="Y8" s="8" t="s">
+      <c r="Y8" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z8" s="8"/>
-      <c r="AA8" s="8" t="s">
+      <c r="Z8" s="6"/>
+      <c r="AA8" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="AB8" s="10" t="s">
+      <c r="AB8" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC8" s="16" t="s">
+      <c r="AC8" s="23" t="s">
         <v>293</v>
       </c>
     </row>
@@ -4721,51 +4718,51 @@
       <c r="J9" t="s">
         <v>186</v>
       </c>
-      <c r="N9" s="8" t="s">
+      <c r="N9" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="O9" s="6" t="s">
         <v>616</v>
       </c>
-      <c r="O9" s="8" t="s">
+      <c r="P9" s="7">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="12">
+        <v>0.1812</v>
+      </c>
+      <c r="R9" s="12">
+        <v>0.91</v>
+      </c>
+      <c r="S9" s="6" t="s">
         <v>617</v>
       </c>
-      <c r="P9" s="9">
+      <c r="T9" s="6" t="s">
+        <v>618</v>
+      </c>
+      <c r="U9" s="6">
         <v>5</v>
       </c>
-      <c r="Q9" s="15">
-        <v>0.1812</v>
-      </c>
-      <c r="R9" s="15">
-        <v>0.91</v>
-      </c>
-      <c r="S9" s="8" t="s">
-        <v>618</v>
-      </c>
-      <c r="T9" s="8" t="s">
+      <c r="V9" s="6">
+        <v>5</v>
+      </c>
+      <c r="W9" s="6">
+        <v>2000</v>
+      </c>
+      <c r="X9" s="6">
+        <v>1980</v>
+      </c>
+      <c r="Y9" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z9" s="6"/>
+      <c r="AA9" s="6" t="s">
         <v>619</v>
       </c>
-      <c r="U9" s="8">
-        <v>5</v>
-      </c>
-      <c r="V9" s="8">
-        <v>5</v>
-      </c>
-      <c r="W9" s="8">
-        <v>2000</v>
-      </c>
-      <c r="X9" s="8">
-        <v>1980</v>
-      </c>
-      <c r="Y9" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="Z9" s="8"/>
-      <c r="AA9" s="8" t="s">
+      <c r="AB9" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="AC9" s="23" t="s">
         <v>620</v>
-      </c>
-      <c r="AB9" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="AC9" s="16" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="15" customHeight="1">
@@ -4800,50 +4797,50 @@
       <c r="J10" t="s">
         <v>186</v>
       </c>
-      <c r="N10" s="8" t="s">
+      <c r="N10" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="O10" s="8" t="s">
+      <c r="O10" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="P10" s="9">
+      <c r="P10" s="7">
         <v>100</v>
       </c>
-      <c r="Q10" s="15">
+      <c r="Q10" s="12">
         <v>6.7999999999999996E-3</v>
       </c>
-      <c r="R10" s="15">
+      <c r="R10" s="12">
         <v>0.68</v>
       </c>
-      <c r="S10" s="8" t="s">
+      <c r="S10" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="T10" s="8">
+      <c r="T10" s="6">
         <v>603</v>
       </c>
-      <c r="U10" s="8">
+      <c r="U10" s="6">
         <v>100</v>
       </c>
-      <c r="V10" s="8">
+      <c r="V10" s="6">
         <v>100</v>
       </c>
-      <c r="W10" s="8">
+      <c r="W10" s="6">
         <v>4000</v>
       </c>
-      <c r="X10" s="8">
+      <c r="X10" s="6">
         <v>5300</v>
       </c>
-      <c r="Y10" s="8" t="s">
+      <c r="Y10" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z10" s="8"/>
-      <c r="AA10" s="8" t="s">
+      <c r="Z10" s="6"/>
+      <c r="AA10" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="AB10" s="10" t="s">
+      <c r="AB10" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC10" s="16" t="s">
+      <c r="AC10" s="23" t="s">
         <v>253</v>
       </c>
     </row>
@@ -4879,50 +4876,50 @@
       <c r="J11" t="s">
         <v>186</v>
       </c>
-      <c r="N11" s="8" t="s">
+      <c r="N11" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="O11" s="8" t="s">
+      <c r="O11" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="P11" s="9">
+      <c r="P11" s="7">
         <v>100</v>
       </c>
-      <c r="Q11" s="15">
+      <c r="Q11" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="R11" s="15">
+      <c r="R11" s="12">
         <v>0.5</v>
       </c>
-      <c r="S11" s="8" t="s">
+      <c r="S11" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="T11" s="8">
+      <c r="T11" s="6">
         <v>603</v>
       </c>
-      <c r="U11" s="8">
+      <c r="U11" s="6">
         <v>100</v>
       </c>
-      <c r="V11" s="8">
+      <c r="V11" s="6">
         <v>100</v>
       </c>
-      <c r="W11" s="8">
+      <c r="W11" s="6">
         <v>4000</v>
       </c>
-      <c r="X11" s="8">
+      <c r="X11" s="6">
         <v>1498600</v>
       </c>
-      <c r="Y11" s="8" t="s">
+      <c r="Y11" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z11" s="8"/>
-      <c r="AA11" s="8" t="s">
+      <c r="Z11" s="6"/>
+      <c r="AA11" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="AB11" s="10" t="s">
+      <c r="AB11" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC11" s="16" t="s">
+      <c r="AC11" s="23" t="s">
         <v>257</v>
       </c>
     </row>
@@ -4958,50 +4955,50 @@
       <c r="J12" t="s">
         <v>186</v>
       </c>
-      <c r="N12" s="8" t="s">
+      <c r="N12" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="O12" s="8" t="s">
+      <c r="O12" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="P12" s="9">
+      <c r="P12" s="7">
         <v>10</v>
       </c>
-      <c r="Q12" s="15">
+      <c r="Q12" s="12">
         <v>0.1119</v>
       </c>
-      <c r="R12" s="15">
+      <c r="R12" s="12">
         <v>1.1200000000000001</v>
       </c>
-      <c r="S12" s="8" t="s">
+      <c r="S12" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="T12" s="8">
+      <c r="T12" s="6">
         <v>805</v>
       </c>
-      <c r="U12" s="8">
+      <c r="U12" s="6">
         <v>5</v>
       </c>
-      <c r="V12" s="8">
+      <c r="V12" s="6">
         <v>5</v>
       </c>
-      <c r="W12" s="8">
+      <c r="W12" s="6">
         <v>2000</v>
       </c>
-      <c r="X12" s="8">
+      <c r="X12" s="6">
         <v>5645</v>
       </c>
-      <c r="Y12" s="8" t="s">
+      <c r="Y12" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z12" s="8"/>
-      <c r="AA12" s="8" t="s">
+      <c r="Z12" s="6"/>
+      <c r="AA12" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="AB12" s="10" t="s">
+      <c r="AB12" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC12" s="16" t="s">
+      <c r="AC12" s="23" t="s">
         <v>298</v>
       </c>
     </row>
@@ -5037,50 +5034,50 @@
       <c r="J13" t="s">
         <v>186</v>
       </c>
-      <c r="N13" s="8" t="s">
+      <c r="N13" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="O13" s="8" t="s">
+      <c r="O13" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="P13" s="9">
+      <c r="P13" s="7">
         <v>5</v>
       </c>
-      <c r="Q13" s="15">
+      <c r="Q13" s="12">
         <v>0.14280000000000001</v>
       </c>
-      <c r="R13" s="15">
+      <c r="R13" s="12">
         <v>0.71</v>
       </c>
-      <c r="S13" s="8" t="s">
+      <c r="S13" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="T13" s="8" t="s">
+      <c r="T13" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="U13" s="8">
+      <c r="U13" s="6">
         <v>5</v>
       </c>
-      <c r="V13" s="8">
+      <c r="V13" s="6">
         <v>5</v>
       </c>
-      <c r="W13" s="8">
+      <c r="W13" s="6">
         <v>1000</v>
       </c>
-      <c r="X13" s="8">
+      <c r="X13" s="6">
         <v>1420</v>
       </c>
-      <c r="Y13" s="8" t="s">
+      <c r="Y13" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z13" s="8"/>
-      <c r="AA13" s="8" t="s">
+      <c r="Z13" s="6"/>
+      <c r="AA13" s="6" t="s">
         <v>386</v>
       </c>
-      <c r="AB13" s="11" t="s">
+      <c r="AB13" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC13" s="16" t="s">
+      <c r="AC13" s="23" t="s">
         <v>387</v>
       </c>
     </row>
@@ -5116,50 +5113,50 @@
       <c r="J14" t="s">
         <v>186</v>
       </c>
-      <c r="N14" s="8" t="s">
+      <c r="N14" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="O14" s="8" t="s">
+      <c r="O14" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="P14" s="9">
+      <c r="P14" s="7">
         <v>100</v>
       </c>
-      <c r="Q14" s="15">
+      <c r="Q14" s="12">
         <v>5.5999999999999999E-3</v>
       </c>
-      <c r="R14" s="15">
+      <c r="R14" s="12">
         <v>0.56000000000000005</v>
       </c>
-      <c r="S14" s="8" t="s">
+      <c r="S14" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="T14" s="8">
+      <c r="T14" s="6">
         <v>603</v>
       </c>
-      <c r="U14" s="8">
+      <c r="U14" s="6">
         <v>100</v>
       </c>
-      <c r="V14" s="8">
+      <c r="V14" s="6">
         <v>100</v>
       </c>
-      <c r="W14" s="8">
+      <c r="W14" s="6">
         <v>4000</v>
       </c>
-      <c r="X14" s="8">
+      <c r="X14" s="6">
         <v>189700</v>
       </c>
-      <c r="Y14" s="8" t="s">
+      <c r="Y14" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z14" s="8"/>
-      <c r="AA14" s="8" t="s">
+      <c r="Z14" s="6"/>
+      <c r="AA14" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="AB14" s="10" t="s">
+      <c r="AB14" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC14" s="16" t="s">
+      <c r="AC14" s="23" t="s">
         <v>261</v>
       </c>
     </row>
@@ -5195,50 +5192,50 @@
       <c r="J15" t="s">
         <v>186</v>
       </c>
-      <c r="N15" s="8" t="s">
+      <c r="N15" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="O15" s="8" t="s">
+      <c r="O15" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="P15" s="9">
-        <v>2</v>
-      </c>
-      <c r="Q15" s="15">
+      <c r="P15" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="12">
         <v>0.77639999999999998</v>
       </c>
-      <c r="R15" s="15">
+      <c r="R15" s="12">
         <v>1.55</v>
       </c>
-      <c r="S15" s="8" t="s">
+      <c r="S15" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="T15" s="8" t="s">
+      <c r="T15" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="U15" s="8">
-        <v>1</v>
-      </c>
-      <c r="V15" s="8">
-        <v>1</v>
-      </c>
-      <c r="W15" s="8">
+      <c r="U15" s="6">
+        <v>1</v>
+      </c>
+      <c r="V15" s="6">
+        <v>1</v>
+      </c>
+      <c r="W15" s="6">
         <v>500</v>
       </c>
-      <c r="X15" s="8">
+      <c r="X15" s="6">
         <v>4041</v>
       </c>
-      <c r="Y15" s="8" t="s">
+      <c r="Y15" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z15" s="8"/>
-      <c r="AA15" s="8" t="s">
+      <c r="Z15" s="6"/>
+      <c r="AA15" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="AB15" s="11" t="s">
+      <c r="AB15" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC15" s="16" t="s">
+      <c r="AC15" s="23" t="s">
         <v>392</v>
       </c>
     </row>
@@ -5274,50 +5271,50 @@
       <c r="J16" t="s">
         <v>186</v>
       </c>
-      <c r="N16" s="8" t="s">
+      <c r="N16" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="O16" s="8" t="s">
+      <c r="O16" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="P16" s="9">
+      <c r="P16" s="7">
         <v>10</v>
       </c>
-      <c r="Q16" s="15">
+      <c r="Q16" s="12">
         <v>6.0999999999999999E-2</v>
       </c>
-      <c r="R16" s="15">
+      <c r="R16" s="12">
         <v>0.61</v>
       </c>
-      <c r="S16" s="8" t="s">
+      <c r="S16" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="T16" s="8">
+      <c r="T16" s="6">
         <v>1206</v>
       </c>
-      <c r="U16" s="8">
+      <c r="U16" s="6">
         <v>10</v>
       </c>
-      <c r="V16" s="8">
+      <c r="V16" s="6">
         <v>10</v>
       </c>
-      <c r="W16" s="8">
+      <c r="W16" s="6">
         <v>2000</v>
       </c>
-      <c r="X16" s="8">
+      <c r="X16" s="6">
         <v>6009890</v>
       </c>
-      <c r="Y16" s="8" t="s">
+      <c r="Y16" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z16" s="8"/>
-      <c r="AA16" s="8" t="s">
+      <c r="Z16" s="6"/>
+      <c r="AA16" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="AB16" s="10" t="s">
+      <c r="AB16" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC16" s="16" t="s">
+      <c r="AC16" s="23" t="s">
         <v>265</v>
       </c>
     </row>
@@ -5353,50 +5350,50 @@
       <c r="J17" t="s">
         <v>186</v>
       </c>
-      <c r="N17" s="8" t="s">
+      <c r="N17" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="O17" s="8" t="s">
+      <c r="O17" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="P17" s="9">
+      <c r="P17" s="7">
         <v>50</v>
       </c>
-      <c r="Q17" s="15">
+      <c r="Q17" s="12">
         <v>5.5999999999999999E-3</v>
       </c>
-      <c r="R17" s="15">
+      <c r="R17" s="12">
         <v>0.28000000000000003</v>
       </c>
-      <c r="S17" s="8" t="s">
+      <c r="S17" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="T17" s="8">
+      <c r="T17" s="6">
         <v>603</v>
       </c>
-      <c r="U17" s="8">
+      <c r="U17" s="6">
         <v>50</v>
       </c>
-      <c r="V17" s="8">
+      <c r="V17" s="6">
         <v>50</v>
       </c>
-      <c r="W17" s="8">
+      <c r="W17" s="6">
         <v>4000</v>
       </c>
-      <c r="X17" s="8">
+      <c r="X17" s="6">
         <v>13333100</v>
       </c>
-      <c r="Y17" s="8" t="s">
+      <c r="Y17" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z17" s="8"/>
-      <c r="AA17" s="8" t="s">
+      <c r="Z17" s="6"/>
+      <c r="AA17" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="AB17" s="10" t="s">
+      <c r="AB17" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC17" s="16" t="s">
+      <c r="AC17" s="23" t="s">
         <v>269</v>
       </c>
     </row>
@@ -5432,50 +5429,50 @@
       <c r="J18" t="s">
         <v>186</v>
       </c>
-      <c r="N18" s="8" t="s">
+      <c r="N18" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="O18" s="8" t="s">
+      <c r="O18" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="P18" s="9">
+      <c r="P18" s="7">
         <v>20</v>
       </c>
-      <c r="Q18" s="15">
+      <c r="Q18" s="12">
         <v>5.4000000000000003E-3</v>
       </c>
-      <c r="R18" s="15">
+      <c r="R18" s="12">
         <v>0.11</v>
       </c>
-      <c r="S18" s="8" t="s">
+      <c r="S18" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="T18" s="8">
+      <c r="T18" s="6">
         <v>603</v>
       </c>
-      <c r="U18" s="8">
+      <c r="U18" s="6">
         <v>20</v>
       </c>
-      <c r="V18" s="8">
+      <c r="V18" s="6">
         <v>20</v>
       </c>
-      <c r="W18" s="8">
+      <c r="W18" s="6">
         <v>4000</v>
       </c>
-      <c r="X18" s="8">
+      <c r="X18" s="6">
         <v>61420</v>
       </c>
-      <c r="Y18" s="8" t="s">
+      <c r="Y18" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z18" s="8"/>
-      <c r="AA18" s="8" t="s">
+      <c r="Z18" s="6"/>
+      <c r="AA18" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="AB18" s="10" t="s">
+      <c r="AB18" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC18" s="16" t="s">
+      <c r="AC18" s="23" t="s">
         <v>273</v>
       </c>
     </row>
@@ -5511,50 +5508,50 @@
       <c r="J19" t="s">
         <v>186</v>
       </c>
-      <c r="N19" s="8" t="s">
+      <c r="N19" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="O19" s="8" t="s">
+      <c r="O19" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="P19" s="9">
+      <c r="P19" s="7">
         <v>20</v>
       </c>
-      <c r="Q19" s="15">
+      <c r="Q19" s="12">
         <v>8.2000000000000007E-3</v>
       </c>
-      <c r="R19" s="15">
+      <c r="R19" s="12">
         <v>0.16</v>
       </c>
-      <c r="S19" s="8" t="s">
+      <c r="S19" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="T19" s="8">
+      <c r="T19" s="6">
         <v>603</v>
       </c>
-      <c r="U19" s="8">
+      <c r="U19" s="6">
         <v>20</v>
       </c>
-      <c r="V19" s="8">
+      <c r="V19" s="6">
         <v>20</v>
       </c>
-      <c r="W19" s="8">
+      <c r="W19" s="6">
         <v>4000</v>
       </c>
-      <c r="X19" s="8">
+      <c r="X19" s="6">
         <v>39800</v>
       </c>
-      <c r="Y19" s="8" t="s">
+      <c r="Y19" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z19" s="8"/>
-      <c r="AA19" s="8" t="s">
+      <c r="Z19" s="6"/>
+      <c r="AA19" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="AB19" s="10" t="s">
+      <c r="AB19" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC19" s="16" t="s">
+      <c r="AC19" s="23" t="s">
         <v>277</v>
       </c>
     </row>
@@ -5590,50 +5587,50 @@
       <c r="J20" t="s">
         <v>186</v>
       </c>
-      <c r="N20" s="8" t="s">
+      <c r="N20" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="O20" s="8" t="s">
+      <c r="O20" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="P20" s="9">
+      <c r="P20" s="7">
         <v>50</v>
       </c>
-      <c r="Q20" s="15">
+      <c r="Q20" s="12">
         <v>5.5999999999999999E-3</v>
       </c>
-      <c r="R20" s="15">
+      <c r="R20" s="12">
         <v>0.28000000000000003</v>
       </c>
-      <c r="S20" s="8" t="s">
+      <c r="S20" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="T20" s="8">
+      <c r="T20" s="6">
         <v>603</v>
       </c>
-      <c r="U20" s="8">
+      <c r="U20" s="6">
         <v>50</v>
       </c>
-      <c r="V20" s="8">
+      <c r="V20" s="6">
         <v>50</v>
       </c>
-      <c r="W20" s="8">
+      <c r="W20" s="6">
         <v>4000</v>
       </c>
-      <c r="X20" s="8">
+      <c r="X20" s="6">
         <v>4548950</v>
       </c>
-      <c r="Y20" s="8" t="s">
+      <c r="Y20" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z20" s="8"/>
-      <c r="AA20" s="8" t="s">
+      <c r="Z20" s="6"/>
+      <c r="AA20" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="AB20" s="10" t="s">
+      <c r="AB20" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC20" s="16" t="s">
+      <c r="AC20" s="23" t="s">
         <v>281</v>
       </c>
     </row>
@@ -5669,50 +5666,50 @@
       <c r="J21" t="s">
         <v>186</v>
       </c>
-      <c r="N21" s="8" t="s">
+      <c r="N21" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="O21" s="8" t="s">
+      <c r="O21" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="P21" s="9">
+      <c r="P21" s="7">
         <v>50</v>
       </c>
-      <c r="Q21" s="15">
+      <c r="Q21" s="12">
         <v>6.4999999999999997E-3</v>
       </c>
-      <c r="R21" s="15">
+      <c r="R21" s="12">
         <v>0.33</v>
       </c>
-      <c r="S21" s="8" t="s">
+      <c r="S21" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="T21" s="8">
+      <c r="T21" s="6">
         <v>603</v>
       </c>
-      <c r="U21" s="8">
+      <c r="U21" s="6">
         <v>50</v>
       </c>
-      <c r="V21" s="8">
+      <c r="V21" s="6">
         <v>50</v>
       </c>
-      <c r="W21" s="8">
+      <c r="W21" s="6">
         <v>4000</v>
       </c>
-      <c r="X21" s="8">
+      <c r="X21" s="6">
         <v>13475400</v>
       </c>
-      <c r="Y21" s="8" t="s">
+      <c r="Y21" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z21" s="8"/>
-      <c r="AA21" s="8" t="s">
+      <c r="Z21" s="6"/>
+      <c r="AA21" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="AB21" s="10" t="s">
+      <c r="AB21" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC21" s="16" t="s">
+      <c r="AC21" s="23" t="s">
         <v>285</v>
       </c>
     </row>
@@ -5748,50 +5745,50 @@
       <c r="J22" t="s">
         <v>186</v>
       </c>
-      <c r="N22" s="8" t="s">
+      <c r="N22" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="O22" s="8" t="s">
+      <c r="O22" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="P22" s="9">
+      <c r="P22" s="7">
         <v>50</v>
       </c>
-      <c r="Q22" s="15">
+      <c r="Q22" s="12">
         <v>6.1999999999999998E-3</v>
       </c>
-      <c r="R22" s="15">
+      <c r="R22" s="12">
         <v>0.31</v>
       </c>
-      <c r="S22" s="8" t="s">
+      <c r="S22" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="T22" s="8">
+      <c r="T22" s="6">
         <v>603</v>
       </c>
-      <c r="U22" s="8">
+      <c r="U22" s="6">
         <v>50</v>
       </c>
-      <c r="V22" s="8">
+      <c r="V22" s="6">
         <v>50</v>
       </c>
-      <c r="W22" s="8">
+      <c r="W22" s="6">
         <v>4000</v>
       </c>
-      <c r="X22" s="8">
+      <c r="X22" s="6">
         <v>5941500</v>
       </c>
-      <c r="Y22" s="8" t="s">
+      <c r="Y22" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z22" s="8"/>
-      <c r="AA22" s="8" t="s">
+      <c r="Z22" s="6"/>
+      <c r="AA22" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB22" s="10" t="s">
+      <c r="AB22" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC22" s="16" t="s">
+      <c r="AC22" s="23" t="s">
         <v>289</v>
       </c>
     </row>
@@ -5827,50 +5824,50 @@
       <c r="J23" t="s">
         <v>186</v>
       </c>
-      <c r="N23" s="8" t="s">
+      <c r="N23" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="O23" s="8" t="s">
+      <c r="O23" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="P23" s="9">
+      <c r="P23" s="7">
         <v>10</v>
       </c>
-      <c r="Q23" s="15">
+      <c r="Q23" s="12">
         <v>6.2100000000000002E-2</v>
       </c>
-      <c r="R23" s="15">
+      <c r="R23" s="12">
         <v>0.62</v>
       </c>
-      <c r="S23" s="8" t="s">
+      <c r="S23" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="T23" s="8" t="s">
+      <c r="T23" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="U23" s="8">
+      <c r="U23" s="6">
         <v>10</v>
       </c>
-      <c r="V23" s="8">
+      <c r="V23" s="6">
         <v>10</v>
       </c>
-      <c r="W23" s="8">
+      <c r="W23" s="6">
         <v>3000</v>
       </c>
-      <c r="X23" s="8">
+      <c r="X23" s="6">
         <v>2600</v>
       </c>
-      <c r="Y23" s="8" t="s">
+      <c r="Y23" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z23" s="8"/>
-      <c r="AA23" s="8" t="s">
+      <c r="Z23" s="6"/>
+      <c r="AA23" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="AB23" s="10" t="s">
+      <c r="AB23" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC23" s="16" t="s">
+      <c r="AC23" s="23" t="s">
         <v>311</v>
       </c>
     </row>
@@ -5906,50 +5903,50 @@
       <c r="J24" t="s">
         <v>186</v>
       </c>
-      <c r="N24" s="8" t="s">
+      <c r="N24" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="O24" s="8" t="s">
+      <c r="O24" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="P24" s="9">
+      <c r="P24" s="7">
         <v>20</v>
       </c>
-      <c r="Q24" s="15">
+      <c r="Q24" s="12">
         <v>2.81E-2</v>
       </c>
-      <c r="R24" s="15">
+      <c r="R24" s="12">
         <v>0.56000000000000005</v>
       </c>
-      <c r="S24" s="8" t="s">
+      <c r="S24" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="T24" s="8" t="s">
+      <c r="T24" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="U24" s="8">
+      <c r="U24" s="6">
         <v>20</v>
       </c>
-      <c r="V24" s="8">
+      <c r="V24" s="6">
         <v>20</v>
       </c>
-      <c r="W24" s="8">
+      <c r="W24" s="6">
         <v>5000</v>
       </c>
-      <c r="X24" s="8">
+      <c r="X24" s="6">
         <v>202260</v>
       </c>
-      <c r="Y24" s="8" t="s">
+      <c r="Y24" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z24" s="8"/>
-      <c r="AA24" s="8" t="s">
+      <c r="Z24" s="6"/>
+      <c r="AA24" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="AB24" s="10" t="s">
+      <c r="AB24" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC24" s="16" t="s">
+      <c r="AC24" s="23" t="s">
         <v>316</v>
       </c>
     </row>
@@ -5985,50 +5982,50 @@
       <c r="J25" t="s">
         <v>186</v>
       </c>
-      <c r="N25" s="8" t="s">
+      <c r="N25" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="O25" s="8" t="s">
+      <c r="O25" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="P25" s="9">
+      <c r="P25" s="7">
         <v>5</v>
       </c>
-      <c r="Q25" s="15">
+      <c r="Q25" s="12">
         <v>3.3300000000000003E-2</v>
       </c>
-      <c r="R25" s="15">
+      <c r="R25" s="12">
         <v>0.17</v>
       </c>
-      <c r="S25" s="8" t="s">
+      <c r="S25" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="T25" s="8" t="s">
+      <c r="T25" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="U25" s="8">
+      <c r="U25" s="6">
         <v>5</v>
       </c>
-      <c r="V25" s="8">
+      <c r="V25" s="6">
         <v>5</v>
       </c>
-      <c r="W25" s="8">
+      <c r="W25" s="6">
         <v>3000</v>
       </c>
-      <c r="X25" s="8">
+      <c r="X25" s="6">
         <v>71145</v>
       </c>
-      <c r="Y25" s="8" t="s">
+      <c r="Y25" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z25" s="8"/>
-      <c r="AA25" s="8" t="s">
+      <c r="Z25" s="6"/>
+      <c r="AA25" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="AB25" s="10" t="s">
+      <c r="AB25" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC25" s="16" t="s">
+      <c r="AC25" s="23" t="s">
         <v>322</v>
       </c>
     </row>
@@ -6064,50 +6061,50 @@
       <c r="J26" t="s">
         <v>186</v>
       </c>
-      <c r="N26" s="8" t="s">
+      <c r="N26" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="O26" s="8" t="s">
+      <c r="O26" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="P26" s="9">
+      <c r="P26" s="7">
         <v>5</v>
       </c>
-      <c r="Q26" s="15">
+      <c r="Q26" s="12">
         <v>8.5199999999999998E-2</v>
       </c>
-      <c r="R26" s="15">
+      <c r="R26" s="12">
         <v>0.43</v>
       </c>
-      <c r="S26" s="8" t="s">
+      <c r="S26" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="T26" s="8" t="s">
+      <c r="T26" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="U26" s="8">
+      <c r="U26" s="6">
         <v>5</v>
       </c>
-      <c r="V26" s="8">
+      <c r="V26" s="6">
         <v>5</v>
       </c>
-      <c r="W26" s="8">
+      <c r="W26" s="6">
         <v>3000</v>
       </c>
-      <c r="X26" s="8">
+      <c r="X26" s="6">
         <v>2220</v>
       </c>
-      <c r="Y26" s="8" t="s">
+      <c r="Y26" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z26" s="8"/>
-      <c r="AA26" s="8" t="s">
+      <c r="Z26" s="6"/>
+      <c r="AA26" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="AB26" s="10" t="s">
+      <c r="AB26" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC26" s="16" t="s">
+      <c r="AC26" s="23" t="s">
         <v>327</v>
       </c>
     </row>
@@ -6143,50 +6140,50 @@
       <c r="J27" t="s">
         <v>186</v>
       </c>
-      <c r="N27" s="8" t="s">
+      <c r="N27" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="O27" s="8" t="s">
+      <c r="O27" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="P27" s="9">
+      <c r="P27" s="7">
         <v>10</v>
       </c>
-      <c r="Q27" s="15">
+      <c r="Q27" s="12">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="R27" s="15">
+      <c r="R27" s="12">
         <v>0.37</v>
       </c>
-      <c r="S27" s="8" t="s">
+      <c r="S27" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="T27" s="8" t="s">
+      <c r="T27" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="U27" s="8">
+      <c r="U27" s="6">
         <v>10</v>
       </c>
-      <c r="V27" s="8">
+      <c r="V27" s="6">
         <v>10</v>
       </c>
-      <c r="W27" s="8">
+      <c r="W27" s="6">
         <v>4000</v>
       </c>
-      <c r="X27" s="8">
+      <c r="X27" s="6">
         <v>1640</v>
       </c>
-      <c r="Y27" s="8" t="s">
+      <c r="Y27" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z27" s="8"/>
-      <c r="AA27" s="8" t="s">
+      <c r="Z27" s="6"/>
+      <c r="AA27" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="AB27" s="10" t="s">
+      <c r="AB27" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC27" s="16" t="s">
+      <c r="AC27" s="23" t="s">
         <v>333</v>
       </c>
     </row>
@@ -6222,50 +6219,50 @@
       <c r="J28" t="s">
         <v>186</v>
       </c>
-      <c r="N28" s="8" t="s">
+      <c r="N28" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="O28" s="8" t="s">
+      <c r="O28" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="P28" s="9">
+      <c r="P28" s="7">
         <v>20</v>
       </c>
-      <c r="Q28" s="15">
+      <c r="Q28" s="12">
         <v>0.15329999999999999</v>
       </c>
-      <c r="R28" s="15">
+      <c r="R28" s="12">
         <v>3.07</v>
       </c>
-      <c r="S28" s="8" t="s">
+      <c r="S28" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="T28" s="8" t="s">
+      <c r="T28" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="U28" s="8">
+      <c r="U28" s="6">
         <v>10</v>
       </c>
-      <c r="V28" s="8">
+      <c r="V28" s="6">
         <v>10</v>
       </c>
-      <c r="W28" s="8">
+      <c r="W28" s="6">
         <v>2500</v>
       </c>
-      <c r="X28" s="8">
+      <c r="X28" s="6">
         <v>4140</v>
       </c>
-      <c r="Y28" s="8" t="s">
+      <c r="Y28" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z28" s="8"/>
-      <c r="AA28" s="8" t="s">
+      <c r="Z28" s="6"/>
+      <c r="AA28" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="AB28" s="10" t="s">
+      <c r="AB28" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC28" s="16" t="s">
+      <c r="AC28" s="23" t="s">
         <v>337</v>
       </c>
     </row>
@@ -6301,26 +6298,26 @@
       <c r="K29" t="s">
         <v>186</v>
       </c>
-      <c r="N29" s="17" t="s">
+      <c r="N29" s="13" t="s">
+        <v>625</v>
+      </c>
+      <c r="O29" s="14" t="s">
         <v>626</v>
       </c>
-      <c r="O29" s="18" t="s">
-        <v>627</v>
-      </c>
-      <c r="P29" s="19">
-        <v>2</v>
-      </c>
-      <c r="Q29" s="20">
+      <c r="P29" s="15">
+        <v>2</v>
+      </c>
+      <c r="Q29" s="16">
         <v>1.54</v>
       </c>
-      <c r="R29" s="20">
+      <c r="R29" s="16">
         <v>3.08</v>
       </c>
-      <c r="S29" s="21" t="s">
-        <v>625</v>
+      <c r="S29" s="17" t="s">
+        <v>624</v>
       </c>
       <c r="AC29" s="26" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="30" spans="1:29" ht="15" customHeight="1">
@@ -6355,50 +6352,50 @@
       <c r="J30" t="s">
         <v>186</v>
       </c>
-      <c r="N30" s="8" t="s">
+      <c r="N30" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="O30" s="8" t="s">
+      <c r="O30" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="P30" s="9">
+      <c r="P30" s="7">
         <v>5</v>
       </c>
-      <c r="Q30" s="15">
+      <c r="Q30" s="12">
         <v>0.1734</v>
       </c>
-      <c r="R30" s="15">
+      <c r="R30" s="12">
         <v>0.87</v>
       </c>
-      <c r="S30" s="8" t="s">
+      <c r="S30" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="T30" s="8" t="s">
+      <c r="T30" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="U30" s="8">
+      <c r="U30" s="6">
         <v>5</v>
       </c>
-      <c r="V30" s="8">
+      <c r="V30" s="6">
         <v>5</v>
       </c>
-      <c r="W30" s="8">
+      <c r="W30" s="6">
         <v>3000</v>
       </c>
-      <c r="X30" s="8">
+      <c r="X30" s="6">
         <v>47315</v>
       </c>
-      <c r="Y30" s="8" t="s">
+      <c r="Y30" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z30" s="8"/>
-      <c r="AA30" s="8" t="s">
+      <c r="Z30" s="6"/>
+      <c r="AA30" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="AB30" s="10" t="s">
+      <c r="AB30" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC30" s="16" t="s">
+      <c r="AC30" s="23" t="s">
         <v>342</v>
       </c>
     </row>
@@ -6434,50 +6431,50 @@
       <c r="J31" t="s">
         <v>186</v>
       </c>
-      <c r="N31" s="8" t="s">
+      <c r="N31" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="O31" s="8" t="s">
+      <c r="O31" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="P31" s="9">
+      <c r="P31" s="7">
         <v>5</v>
       </c>
-      <c r="Q31" s="15">
+      <c r="Q31" s="12">
         <v>0.114</v>
       </c>
-      <c r="R31" s="15">
+      <c r="R31" s="12">
         <v>0.56999999999999995</v>
       </c>
-      <c r="S31" s="8" t="s">
+      <c r="S31" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="T31" s="8" t="s">
+      <c r="T31" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="U31" s="8">
+      <c r="U31" s="6">
         <v>5</v>
       </c>
-      <c r="V31" s="8">
+      <c r="V31" s="6">
         <v>5</v>
       </c>
-      <c r="W31" s="8">
+      <c r="W31" s="6">
         <v>220</v>
       </c>
-      <c r="X31" s="8">
+      <c r="X31" s="6">
         <v>19840</v>
       </c>
-      <c r="Y31" s="8" t="s">
+      <c r="Y31" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z31" s="8"/>
-      <c r="AA31" s="8" t="s">
+      <c r="Z31" s="6"/>
+      <c r="AA31" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="AB31" s="10" t="s">
+      <c r="AB31" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC31" s="16" t="s">
+      <c r="AC31" s="23" t="s">
         <v>348</v>
       </c>
     </row>
@@ -6513,50 +6510,50 @@
       <c r="J32" t="s">
         <v>186</v>
       </c>
-      <c r="N32" s="8" t="s">
+      <c r="N32" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="O32" s="8" t="s">
+      <c r="O32" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="P32" s="9">
+      <c r="P32" s="7">
         <v>5</v>
       </c>
-      <c r="Q32" s="15">
+      <c r="Q32" s="12">
         <v>0.1115</v>
       </c>
-      <c r="R32" s="15">
+      <c r="R32" s="12">
         <v>0.56000000000000005</v>
       </c>
-      <c r="S32" s="8" t="s">
+      <c r="S32" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="T32" s="8" t="s">
+      <c r="T32" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="U32" s="8">
+      <c r="U32" s="6">
         <v>5</v>
       </c>
-      <c r="V32" s="8">
+      <c r="V32" s="6">
         <v>5</v>
       </c>
-      <c r="W32" s="8">
+      <c r="W32" s="6">
         <v>1000</v>
       </c>
-      <c r="X32" s="8">
+      <c r="X32" s="6">
         <v>26375</v>
       </c>
-      <c r="Y32" s="8" t="s">
+      <c r="Y32" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z32" s="8"/>
-      <c r="AA32" s="8" t="s">
+      <c r="Z32" s="6"/>
+      <c r="AA32" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="AB32" s="10" t="s">
+      <c r="AB32" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC32" s="16" t="s">
+      <c r="AC32" s="23" t="s">
         <v>353</v>
       </c>
     </row>
@@ -6592,50 +6589,50 @@
       <c r="J33" t="s">
         <v>186</v>
       </c>
-      <c r="N33" s="8" t="s">
+      <c r="N33" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="O33" s="8" t="s">
+      <c r="O33" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="P33" s="9">
+      <c r="P33" s="7">
         <v>5</v>
       </c>
-      <c r="Q33" s="15">
+      <c r="Q33" s="12">
         <v>0.1681</v>
       </c>
-      <c r="R33" s="15">
+      <c r="R33" s="12">
         <v>0.84</v>
       </c>
-      <c r="S33" s="8" t="s">
+      <c r="S33" s="6" t="s">
         <v>356</v>
       </c>
-      <c r="T33" s="8" t="s">
+      <c r="T33" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="U33" s="8">
+      <c r="U33" s="6">
         <v>5</v>
       </c>
-      <c r="V33" s="8">
+      <c r="V33" s="6">
         <v>5</v>
       </c>
-      <c r="W33" s="8">
+      <c r="W33" s="6">
         <v>1000</v>
       </c>
-      <c r="X33" s="8">
+      <c r="X33" s="6">
         <v>263130</v>
       </c>
-      <c r="Y33" s="8" t="s">
+      <c r="Y33" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z33" s="8"/>
-      <c r="AA33" s="8" t="s">
+      <c r="Z33" s="6"/>
+      <c r="AA33" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="AB33" s="10" t="s">
+      <c r="AB33" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC33" s="16" t="s">
+      <c r="AC33" s="23" t="s">
         <v>358</v>
       </c>
     </row>
@@ -6671,26 +6668,26 @@
       <c r="K34" t="s">
         <v>186</v>
       </c>
-      <c r="N34" s="17" t="s">
+      <c r="N34" s="13" t="s">
+        <v>628</v>
+      </c>
+      <c r="O34" s="14" t="s">
         <v>629</v>
       </c>
-      <c r="O34" s="18" t="s">
-        <v>630</v>
-      </c>
-      <c r="P34" s="19">
-        <v>2</v>
-      </c>
-      <c r="Q34" s="20">
+      <c r="P34" s="15">
+        <v>2</v>
+      </c>
+      <c r="Q34" s="16">
         <v>6.73</v>
       </c>
-      <c r="R34" s="20">
+      <c r="R34" s="16">
         <v>13.46</v>
       </c>
-      <c r="S34" s="18" t="s">
-        <v>628</v>
+      <c r="S34" s="14" t="s">
+        <v>627</v>
       </c>
       <c r="AC34" s="26" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="35" spans="1:48" ht="15" customHeight="1">
@@ -6716,8 +6713,7 @@
         <v>11</v>
       </c>
       <c r="H35">
-        <f>2*Artnet_DMX_Converter5[[#This Row],[Quantity]]</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I35" t="s">
         <v>11</v>
@@ -6725,26 +6721,26 @@
       <c r="K35" t="s">
         <v>186</v>
       </c>
-      <c r="N35" s="17" t="s">
+      <c r="N35" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="O35" s="18" t="s">
+      <c r="O35" s="14" t="s">
+        <v>629</v>
+      </c>
+      <c r="P35" s="15">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="16">
+        <v>7.79</v>
+      </c>
+      <c r="R35" s="16">
+        <v>31.16</v>
+      </c>
+      <c r="S35" s="14" t="s">
         <v>630</v>
       </c>
-      <c r="P35" s="19">
-        <v>4</v>
-      </c>
-      <c r="Q35" s="20">
-        <v>7.79</v>
-      </c>
-      <c r="R35" s="20">
-        <v>31.16</v>
-      </c>
-      <c r="S35" s="18" t="s">
-        <v>631</v>
-      </c>
       <c r="AC35" s="26" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="36" spans="1:48" ht="15" customHeight="1">
@@ -6770,8 +6766,7 @@
         <v>11</v>
       </c>
       <c r="H36">
-        <f>2*Artnet_DMX_Converter5[[#This Row],[Quantity]]</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I36" t="s">
         <v>11</v>
@@ -6779,26 +6774,26 @@
       <c r="K36" t="s">
         <v>186</v>
       </c>
-      <c r="N36" s="17" t="s">
+      <c r="N36" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="O36" s="18" t="s">
-        <v>630</v>
-      </c>
-      <c r="P36" s="19">
+      <c r="O36" s="14" t="s">
+        <v>629</v>
+      </c>
+      <c r="P36" s="15">
         <v>4</v>
       </c>
-      <c r="Q36" s="20">
+      <c r="Q36" s="16">
         <v>4.33</v>
       </c>
-      <c r="R36" s="20">
+      <c r="R36" s="16">
         <v>17.32</v>
       </c>
-      <c r="S36" s="18" t="s">
-        <v>632</v>
+      <c r="S36" s="14" t="s">
+        <v>631</v>
       </c>
       <c r="AC36" s="26" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="37" spans="1:48" ht="15" customHeight="1">
@@ -6833,50 +6828,50 @@
       <c r="J37" t="s">
         <v>186</v>
       </c>
-      <c r="N37" s="8" t="s">
+      <c r="N37" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="O37" s="8" t="s">
+      <c r="O37" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="P37" s="9">
+      <c r="P37" s="7">
         <v>5</v>
       </c>
-      <c r="Q37" s="15">
+      <c r="Q37" s="12">
         <v>0.28739999999999999</v>
       </c>
-      <c r="R37" s="15">
+      <c r="R37" s="12">
         <v>1.44</v>
       </c>
-      <c r="S37" s="8" t="s">
+      <c r="S37" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="T37" s="8">
+      <c r="T37" s="6">
         <v>806</v>
       </c>
-      <c r="U37" s="8">
+      <c r="U37" s="6">
         <v>5</v>
       </c>
-      <c r="V37" s="8">
+      <c r="V37" s="6">
         <v>5</v>
       </c>
-      <c r="W37" s="8">
+      <c r="W37" s="6">
         <v>3000</v>
       </c>
-      <c r="X37" s="8">
+      <c r="X37" s="6">
         <v>15360</v>
       </c>
-      <c r="Y37" s="8" t="s">
+      <c r="Y37" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z37" s="8"/>
-      <c r="AA37" s="8" t="s">
+      <c r="Z37" s="6"/>
+      <c r="AA37" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="AB37" s="10" t="s">
+      <c r="AB37" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC37" s="16" t="s">
+      <c r="AC37" s="23" t="s">
         <v>363</v>
       </c>
       <c r="AG37" s="1"/>
@@ -6924,50 +6919,50 @@
       <c r="J38" t="s">
         <v>186</v>
       </c>
-      <c r="N38" s="8" t="s">
+      <c r="N38" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="O38" s="8" t="s">
+      <c r="O38" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="P38" s="9">
-        <v>2</v>
-      </c>
-      <c r="Q38" s="15">
+      <c r="P38" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q38" s="12">
         <v>1.6293</v>
       </c>
-      <c r="R38" s="15">
+      <c r="R38" s="12">
         <v>3.26</v>
       </c>
-      <c r="S38" s="8" t="s">
+      <c r="S38" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="T38" s="8">
+      <c r="T38" s="6">
         <v>1616</v>
       </c>
-      <c r="U38" s="8">
-        <v>1</v>
-      </c>
-      <c r="V38" s="8">
-        <v>1</v>
-      </c>
-      <c r="W38" s="8">
+      <c r="U38" s="6">
+        <v>1</v>
+      </c>
+      <c r="V38" s="6">
+        <v>1</v>
+      </c>
+      <c r="W38" s="6">
         <v>4000</v>
       </c>
-      <c r="X38" s="8">
+      <c r="X38" s="6">
         <v>79</v>
       </c>
-      <c r="Y38" s="8" t="s">
+      <c r="Y38" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z38" s="8"/>
-      <c r="AA38" s="8" t="s">
+      <c r="Z38" s="6"/>
+      <c r="AA38" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="AB38" s="10" t="s">
+      <c r="AB38" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC38" s="16" t="s">
+      <c r="AC38" s="23" t="s">
         <v>367</v>
       </c>
     </row>
@@ -7003,50 +6998,50 @@
       <c r="J39" t="s">
         <v>186</v>
       </c>
-      <c r="N39" s="8" t="s">
+      <c r="N39" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="O39" s="8" t="s">
+      <c r="O39" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="P39" s="9">
-        <v>2</v>
-      </c>
-      <c r="Q39" s="15">
+      <c r="P39" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q39" s="12">
         <v>0.74319999999999997</v>
       </c>
-      <c r="R39" s="15">
+      <c r="R39" s="12">
         <v>1.49</v>
       </c>
-      <c r="S39" s="8" t="s">
+      <c r="S39" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="T39" s="8" t="s">
+      <c r="T39" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="U39" s="8">
-        <v>1</v>
-      </c>
-      <c r="V39" s="8">
-        <v>1</v>
-      </c>
-      <c r="W39" s="8">
+      <c r="U39" s="6">
+        <v>1</v>
+      </c>
+      <c r="V39" s="6">
+        <v>1</v>
+      </c>
+      <c r="W39" s="6">
         <v>600</v>
       </c>
-      <c r="X39" s="8">
+      <c r="X39" s="6">
         <v>2085</v>
       </c>
-      <c r="Y39" s="8" t="s">
+      <c r="Y39" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z39" s="8"/>
-      <c r="AA39" s="8" t="s">
+      <c r="Z39" s="6"/>
+      <c r="AA39" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="AB39" s="10" t="s">
+      <c r="AB39" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC39" s="16" t="s">
+      <c r="AC39" s="23" t="s">
         <v>372</v>
       </c>
     </row>
@@ -7082,50 +7077,50 @@
       <c r="J40" t="s">
         <v>186</v>
       </c>
-      <c r="N40" s="8" t="s">
+      <c r="N40" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="O40" s="8" t="s">
+      <c r="O40" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="P40" s="9">
+      <c r="P40" s="7">
         <v>10</v>
       </c>
-      <c r="Q40" s="15">
+      <c r="Q40" s="12">
         <v>8.3500000000000005E-2</v>
       </c>
-      <c r="R40" s="15">
+      <c r="R40" s="12">
         <v>0.84</v>
       </c>
-      <c r="S40" s="8" t="s">
+      <c r="S40" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="T40" s="8">
+      <c r="T40" s="6">
         <v>805</v>
       </c>
-      <c r="U40" s="8">
+      <c r="U40" s="6">
         <v>10</v>
       </c>
-      <c r="V40" s="8">
+      <c r="V40" s="6">
         <v>10</v>
       </c>
-      <c r="W40" s="8">
+      <c r="W40" s="6">
         <v>4000</v>
       </c>
-      <c r="X40" s="8">
+      <c r="X40" s="6">
         <v>89820</v>
       </c>
-      <c r="Y40" s="8" t="s">
+      <c r="Y40" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z40" s="8"/>
-      <c r="AA40" s="8" t="s">
+      <c r="Z40" s="6"/>
+      <c r="AA40" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="AB40" s="10" t="s">
+      <c r="AB40" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AC40" s="16" t="s">
+      <c r="AC40" s="23" t="s">
         <v>376</v>
       </c>
     </row>
@@ -7161,50 +7156,50 @@
       <c r="J41" t="s">
         <v>186</v>
       </c>
-      <c r="N41" s="8" t="s">
+      <c r="N41" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="O41" s="8" t="s">
+      <c r="O41" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="P41" s="9">
+      <c r="P41" s="7">
         <v>45</v>
       </c>
-      <c r="Q41" s="15">
+      <c r="Q41" s="12">
         <v>8.9800000000000005E-2</v>
       </c>
-      <c r="R41" s="15">
+      <c r="R41" s="12">
         <v>4.04</v>
       </c>
-      <c r="S41" s="8" t="s">
+      <c r="S41" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="T41" s="8" t="s">
+      <c r="T41" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="U41" s="8">
+      <c r="U41" s="6">
         <v>5</v>
       </c>
-      <c r="V41" s="8">
+      <c r="V41" s="6">
         <v>5</v>
       </c>
-      <c r="W41" s="8">
+      <c r="W41" s="6">
         <v>4500</v>
       </c>
-      <c r="X41" s="8">
+      <c r="X41" s="6">
         <v>259070</v>
       </c>
-      <c r="Y41" s="8" t="s">
+      <c r="Y41" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z41" s="8"/>
-      <c r="AA41" s="8" t="s">
+      <c r="Z41" s="6"/>
+      <c r="AA41" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="AB41" s="11" t="s">
+      <c r="AB41" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC41" s="16" t="s">
+      <c r="AC41" s="23" t="s">
         <v>381</v>
       </c>
     </row>
@@ -7240,50 +7235,50 @@
       <c r="J42" t="s">
         <v>186</v>
       </c>
-      <c r="N42" s="8" t="s">
+      <c r="N42" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="O42" s="8" t="s">
+      <c r="O42" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="P42" s="9">
+      <c r="P42" s="7">
         <v>100</v>
       </c>
-      <c r="Q42" s="15">
+      <c r="Q42" s="12">
         <v>1.4E-3</v>
       </c>
-      <c r="R42" s="15">
+      <c r="R42" s="12">
         <v>0.14000000000000001</v>
       </c>
-      <c r="S42" s="8" t="s">
+      <c r="S42" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="T42" s="8">
+      <c r="T42" s="6">
         <v>603</v>
       </c>
-      <c r="U42" s="8">
+      <c r="U42" s="6">
         <v>100</v>
       </c>
-      <c r="V42" s="8">
+      <c r="V42" s="6">
         <v>100</v>
       </c>
-      <c r="W42" s="8">
+      <c r="W42" s="6">
         <v>5000</v>
       </c>
-      <c r="X42" s="8">
+      <c r="X42" s="6">
         <v>4596000</v>
       </c>
-      <c r="Y42" s="8" t="s">
+      <c r="Y42" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z42" s="8"/>
-      <c r="AA42" s="8" t="s">
+      <c r="Z42" s="6"/>
+      <c r="AA42" s="6" t="s">
         <v>396</v>
       </c>
-      <c r="AB42" s="11" t="s">
+      <c r="AB42" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC42" s="16" t="s">
+      <c r="AC42" s="23" t="s">
         <v>397</v>
       </c>
     </row>
@@ -7319,50 +7314,50 @@
       <c r="J43" t="s">
         <v>186</v>
       </c>
-      <c r="N43" s="8" t="s">
+      <c r="N43" s="6" t="s">
         <v>398</v>
       </c>
-      <c r="O43" s="8" t="s">
+      <c r="O43" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="P43" s="9">
+      <c r="P43" s="7">
         <v>100</v>
       </c>
-      <c r="Q43" s="15">
+      <c r="Q43" s="12">
         <v>1.4E-3</v>
       </c>
-      <c r="R43" s="15">
+      <c r="R43" s="12">
         <v>0.14000000000000001</v>
       </c>
-      <c r="S43" s="8" t="s">
+      <c r="S43" s="6" t="s">
         <v>399</v>
       </c>
-      <c r="T43" s="8">
+      <c r="T43" s="6">
         <v>603</v>
       </c>
-      <c r="U43" s="8">
+      <c r="U43" s="6">
         <v>100</v>
       </c>
-      <c r="V43" s="8">
+      <c r="V43" s="6">
         <v>100</v>
       </c>
-      <c r="W43" s="8">
+      <c r="W43" s="6">
         <v>5000</v>
       </c>
-      <c r="X43" s="8">
+      <c r="X43" s="6">
         <v>9034300</v>
       </c>
-      <c r="Y43" s="8" t="s">
+      <c r="Y43" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z43" s="8"/>
-      <c r="AA43" s="8" t="s">
+      <c r="Z43" s="6"/>
+      <c r="AA43" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="AB43" s="11" t="s">
+      <c r="AB43" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC43" s="16" t="s">
+      <c r="AC43" s="23" t="s">
         <v>401</v>
       </c>
     </row>
@@ -7398,50 +7393,50 @@
       <c r="J44" t="s">
         <v>186</v>
       </c>
-      <c r="N44" s="8" t="s">
+      <c r="N44" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="O44" s="8" t="s">
+      <c r="O44" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="P44" s="9">
+      <c r="P44" s="7">
         <v>100</v>
       </c>
-      <c r="Q44" s="15">
+      <c r="Q44" s="12">
         <v>1.5E-3</v>
       </c>
-      <c r="R44" s="15">
+      <c r="R44" s="12">
         <v>0.15</v>
       </c>
-      <c r="S44" s="8" t="s">
+      <c r="S44" s="6" t="s">
         <v>403</v>
       </c>
-      <c r="T44" s="8">
+      <c r="T44" s="6">
         <v>603</v>
       </c>
-      <c r="U44" s="8">
+      <c r="U44" s="6">
         <v>100</v>
       </c>
-      <c r="V44" s="8">
+      <c r="V44" s="6">
         <v>100</v>
       </c>
-      <c r="W44" s="8">
+      <c r="W44" s="6">
         <v>5000</v>
       </c>
-      <c r="X44" s="8">
+      <c r="X44" s="6">
         <v>1912100</v>
       </c>
-      <c r="Y44" s="8" t="s">
+      <c r="Y44" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z44" s="8"/>
-      <c r="AA44" s="8" t="s">
+      <c r="Z44" s="6"/>
+      <c r="AA44" s="6" t="s">
         <v>404</v>
       </c>
-      <c r="AB44" s="11" t="s">
+      <c r="AB44" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC44" s="16" t="s">
+      <c r="AC44" s="23" t="s">
         <v>405</v>
       </c>
     </row>
@@ -7477,50 +7472,50 @@
       <c r="J45" t="s">
         <v>186</v>
       </c>
-      <c r="N45" s="8" t="s">
+      <c r="N45" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="O45" s="8" t="s">
+      <c r="O45" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="P45" s="9">
+      <c r="P45" s="7">
         <v>100</v>
       </c>
-      <c r="Q45" s="15">
+      <c r="Q45" s="12">
         <v>1.5E-3</v>
       </c>
-      <c r="R45" s="15">
+      <c r="R45" s="12">
         <v>0.15</v>
       </c>
-      <c r="S45" s="8" t="s">
+      <c r="S45" s="6" t="s">
         <v>407</v>
       </c>
-      <c r="T45" s="8">
+      <c r="T45" s="6">
         <v>603</v>
       </c>
-      <c r="U45" s="8">
+      <c r="U45" s="6">
         <v>100</v>
       </c>
-      <c r="V45" s="8">
+      <c r="V45" s="6">
         <v>100</v>
       </c>
-      <c r="W45" s="8">
+      <c r="W45" s="6">
         <v>5000</v>
       </c>
-      <c r="X45" s="8">
+      <c r="X45" s="6">
         <v>711300</v>
       </c>
-      <c r="Y45" s="8" t="s">
+      <c r="Y45" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z45" s="8"/>
-      <c r="AA45" s="8" t="s">
+      <c r="Z45" s="6"/>
+      <c r="AA45" s="6" t="s">
         <v>408</v>
       </c>
-      <c r="AB45" s="11" t="s">
+      <c r="AB45" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC45" s="16" t="s">
+      <c r="AC45" s="23" t="s">
         <v>409</v>
       </c>
     </row>
@@ -7556,51 +7551,51 @@
       <c r="J46" t="s">
         <v>186</v>
       </c>
-      <c r="N46" s="28" t="s">
+      <c r="N46" s="21" t="s">
+        <v>646</v>
+      </c>
+      <c r="O46" s="21" t="s">
+        <v>394</v>
+      </c>
+      <c r="P46" s="21">
+        <v>100</v>
+      </c>
+      <c r="Q46" s="12">
+        <v>4.3E-3</v>
+      </c>
+      <c r="R46" s="12">
+        <v>0.43</v>
+      </c>
+      <c r="S46" s="21" t="s">
         <v>647</v>
       </c>
-      <c r="O46" s="28" t="s">
-        <v>394</v>
-      </c>
-      <c r="P46" s="29">
+      <c r="T46" s="21">
+        <v>603</v>
+      </c>
+      <c r="U46" s="21">
         <v>100</v>
       </c>
-      <c r="Q46" s="15">
-        <v>4.3E-3</v>
-      </c>
-      <c r="R46" s="15">
-        <v>0.43</v>
-      </c>
-      <c r="S46" s="28" t="s">
+      <c r="V46" s="21">
+        <v>100</v>
+      </c>
+      <c r="W46" s="21">
+        <v>5000</v>
+      </c>
+      <c r="X46" s="21">
+        <v>1937200</v>
+      </c>
+      <c r="Y46" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z46" s="21"/>
+      <c r="AA46" s="21" t="s">
         <v>648</v>
       </c>
-      <c r="T46" s="29">
-        <v>603</v>
-      </c>
-      <c r="U46" s="29">
-        <v>100</v>
-      </c>
-      <c r="V46" s="29">
-        <v>100</v>
-      </c>
-      <c r="W46" s="29">
-        <v>5000</v>
-      </c>
-      <c r="X46" s="29">
-        <v>1937200</v>
-      </c>
-      <c r="Y46" s="28" t="s">
-        <v>233</v>
-      </c>
-      <c r="Z46" s="28"/>
-      <c r="AA46" s="28" t="s">
+      <c r="AB46" t="s">
+        <v>235</v>
+      </c>
+      <c r="AC46" s="26" t="s">
         <v>649</v>
-      </c>
-      <c r="AB46" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="AC46" s="12" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="47" spans="1:48" ht="15" customHeight="1">
@@ -7635,50 +7630,50 @@
       <c r="J47" t="s">
         <v>186</v>
       </c>
-      <c r="N47" s="8" t="s">
+      <c r="N47" s="6" t="s">
         <v>410</v>
       </c>
-      <c r="O47" s="8" t="s">
+      <c r="O47" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="P47" s="9">
+      <c r="P47" s="7">
         <v>100</v>
       </c>
-      <c r="Q47" s="15">
+      <c r="Q47" s="12">
         <v>1.5E-3</v>
       </c>
-      <c r="R47" s="15">
+      <c r="R47" s="12">
         <v>0.15</v>
       </c>
-      <c r="S47" s="8" t="s">
+      <c r="S47" s="6" t="s">
         <v>411</v>
       </c>
-      <c r="T47" s="8">
+      <c r="T47" s="6">
         <v>603</v>
       </c>
-      <c r="U47" s="8">
+      <c r="U47" s="6">
         <v>100</v>
       </c>
-      <c r="V47" s="8">
+      <c r="V47" s="6">
         <v>100</v>
       </c>
-      <c r="W47" s="8">
+      <c r="W47" s="6">
         <v>5000</v>
       </c>
-      <c r="X47" s="8">
+      <c r="X47" s="6">
         <v>38200</v>
       </c>
-      <c r="Y47" s="8" t="s">
+      <c r="Y47" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z47" s="8"/>
-      <c r="AA47" s="8" t="s">
+      <c r="Z47" s="6"/>
+      <c r="AA47" s="6" t="s">
         <v>412</v>
       </c>
-      <c r="AB47" s="11" t="s">
+      <c r="AB47" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC47" s="16" t="s">
+      <c r="AC47" s="23" t="s">
         <v>413</v>
       </c>
     </row>
@@ -7714,50 +7709,50 @@
       <c r="J48" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="8" t="s">
+      <c r="N48" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="O48" s="8" t="s">
+      <c r="O48" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="P48" s="9">
+      <c r="P48" s="7">
         <v>100</v>
       </c>
-      <c r="Q48" s="15">
+      <c r="Q48" s="12">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="R48" s="15">
+      <c r="R48" s="12">
         <v>0.08</v>
       </c>
-      <c r="S48" s="8" t="s">
+      <c r="S48" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="T48" s="8">
+      <c r="T48" s="6">
         <v>402</v>
       </c>
-      <c r="U48" s="8">
+      <c r="U48" s="6">
         <v>100</v>
       </c>
-      <c r="V48" s="8">
+      <c r="V48" s="6">
         <v>100</v>
       </c>
-      <c r="W48" s="8">
+      <c r="W48" s="6">
         <v>10000</v>
       </c>
-      <c r="X48" s="8">
+      <c r="X48" s="6">
         <v>1384200</v>
       </c>
-      <c r="Y48" s="8" t="s">
+      <c r="Y48" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z48" s="8"/>
-      <c r="AA48" s="8" t="s">
+      <c r="Z48" s="6"/>
+      <c r="AA48" s="6" t="s">
         <v>453</v>
       </c>
-      <c r="AB48" s="11" t="s">
+      <c r="AB48" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC48" s="16" t="s">
+      <c r="AC48" s="23" t="s">
         <v>454</v>
       </c>
     </row>
@@ -7793,50 +7788,50 @@
       <c r="J49" t="s">
         <v>186</v>
       </c>
-      <c r="N49" s="8" t="s">
+      <c r="N49" s="6" t="s">
         <v>414</v>
       </c>
-      <c r="O49" s="8" t="s">
+      <c r="O49" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="P49" s="9">
+      <c r="P49" s="7">
         <v>100</v>
       </c>
-      <c r="Q49" s="15">
+      <c r="Q49" s="12">
         <v>1.5E-3</v>
       </c>
-      <c r="R49" s="15">
+      <c r="R49" s="12">
         <v>0.15</v>
       </c>
-      <c r="S49" s="8" t="s">
+      <c r="S49" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="T49" s="8">
+      <c r="T49" s="6">
         <v>603</v>
       </c>
-      <c r="U49" s="8">
+      <c r="U49" s="6">
         <v>100</v>
       </c>
-      <c r="V49" s="8">
+      <c r="V49" s="6">
         <v>100</v>
       </c>
-      <c r="W49" s="8">
+      <c r="W49" s="6">
         <v>5000</v>
       </c>
-      <c r="X49" s="8">
+      <c r="X49" s="6">
         <v>164800</v>
       </c>
-      <c r="Y49" s="8" t="s">
+      <c r="Y49" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z49" s="8"/>
-      <c r="AA49" s="8" t="s">
+      <c r="Z49" s="6"/>
+      <c r="AA49" s="6" t="s">
         <v>416</v>
       </c>
-      <c r="AB49" s="11" t="s">
+      <c r="AB49" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC49" s="16" t="s">
+      <c r="AC49" s="23" t="s">
         <v>417</v>
       </c>
     </row>
@@ -7872,50 +7867,50 @@
       <c r="J50" t="s">
         <v>186</v>
       </c>
-      <c r="N50" s="8" t="s">
+      <c r="N50" s="6" t="s">
         <v>418</v>
       </c>
-      <c r="O50" s="8" t="s">
+      <c r="O50" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="P50" s="9">
+      <c r="P50" s="7">
         <v>100</v>
       </c>
-      <c r="Q50" s="15">
+      <c r="Q50" s="12">
         <v>1.4E-3</v>
       </c>
-      <c r="R50" s="15">
+      <c r="R50" s="12">
         <v>0.14000000000000001</v>
       </c>
-      <c r="S50" s="8" t="s">
+      <c r="S50" s="6" t="s">
         <v>419</v>
       </c>
-      <c r="T50" s="8">
+      <c r="T50" s="6">
         <v>603</v>
       </c>
-      <c r="U50" s="8">
+      <c r="U50" s="6">
         <v>100</v>
       </c>
-      <c r="V50" s="8">
+      <c r="V50" s="6">
         <v>100</v>
       </c>
-      <c r="W50" s="8">
+      <c r="W50" s="6">
         <v>5000</v>
       </c>
-      <c r="X50" s="8">
+      <c r="X50" s="6">
         <v>7700</v>
       </c>
-      <c r="Y50" s="8" t="s">
+      <c r="Y50" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z50" s="8"/>
-      <c r="AA50" s="8" t="s">
+      <c r="Z50" s="6"/>
+      <c r="AA50" s="6" t="s">
         <v>420</v>
       </c>
-      <c r="AB50" s="11" t="s">
+      <c r="AB50" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC50" s="16" t="s">
+      <c r="AC50" s="23" t="s">
         <v>421</v>
       </c>
     </row>
@@ -7951,50 +7946,50 @@
       <c r="J51" t="s">
         <v>186</v>
       </c>
-      <c r="N51" s="8" t="s">
+      <c r="N51" s="6" t="s">
         <v>422</v>
       </c>
-      <c r="O51" s="8" t="s">
+      <c r="O51" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="P51" s="9">
+      <c r="P51" s="7">
         <v>100</v>
       </c>
-      <c r="Q51" s="15">
+      <c r="Q51" s="12">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="R51" s="15">
+      <c r="R51" s="12">
         <v>0.13</v>
       </c>
-      <c r="S51" s="8" t="s">
+      <c r="S51" s="6" t="s">
         <v>423</v>
       </c>
-      <c r="T51" s="8">
+      <c r="T51" s="6">
         <v>603</v>
       </c>
-      <c r="U51" s="8">
+      <c r="U51" s="6">
         <v>100</v>
       </c>
-      <c r="V51" s="8">
+      <c r="V51" s="6">
         <v>100</v>
       </c>
-      <c r="W51" s="8">
+      <c r="W51" s="6">
         <v>5000</v>
       </c>
-      <c r="X51" s="8">
+      <c r="X51" s="6">
         <v>2174100</v>
       </c>
-      <c r="Y51" s="8" t="s">
+      <c r="Y51" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z51" s="8"/>
-      <c r="AA51" s="8" t="s">
+      <c r="Z51" s="6"/>
+      <c r="AA51" s="6" t="s">
         <v>424</v>
       </c>
-      <c r="AB51" s="11" t="s">
+      <c r="AB51" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC51" s="16" t="s">
+      <c r="AC51" s="23" t="s">
         <v>425</v>
       </c>
     </row>
@@ -8030,50 +8025,50 @@
       <c r="J52" t="s">
         <v>186</v>
       </c>
-      <c r="N52" s="8" t="s">
+      <c r="N52" s="6" t="s">
         <v>426</v>
       </c>
-      <c r="O52" s="8" t="s">
+      <c r="O52" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="P52" s="9">
+      <c r="P52" s="7">
         <v>100</v>
       </c>
-      <c r="Q52" s="15">
+      <c r="Q52" s="12">
         <v>1.4E-3</v>
       </c>
-      <c r="R52" s="15">
+      <c r="R52" s="12">
         <v>0.14000000000000001</v>
       </c>
-      <c r="S52" s="8" t="s">
+      <c r="S52" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="T52" s="8">
+      <c r="T52" s="6">
         <v>603</v>
       </c>
-      <c r="U52" s="8">
+      <c r="U52" s="6">
         <v>100</v>
       </c>
-      <c r="V52" s="8">
+      <c r="V52" s="6">
         <v>100</v>
       </c>
-      <c r="W52" s="8">
+      <c r="W52" s="6">
         <v>5000</v>
       </c>
-      <c r="X52" s="8">
+      <c r="X52" s="6">
         <v>20500</v>
       </c>
-      <c r="Y52" s="8" t="s">
+      <c r="Y52" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z52" s="8"/>
-      <c r="AA52" s="8" t="s">
+      <c r="Z52" s="6"/>
+      <c r="AA52" s="6" t="s">
         <v>428</v>
       </c>
-      <c r="AB52" s="11" t="s">
+      <c r="AB52" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC52" s="16" t="s">
+      <c r="AC52" s="23" t="s">
         <v>429</v>
       </c>
     </row>
@@ -8109,50 +8104,50 @@
       <c r="J53" t="s">
         <v>186</v>
       </c>
-      <c r="N53" s="8" t="s">
+      <c r="N53" s="6" t="s">
         <v>430</v>
       </c>
-      <c r="O53" s="8" t="s">
+      <c r="O53" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="P53" s="9">
+      <c r="P53" s="7">
         <v>100</v>
       </c>
-      <c r="Q53" s="15">
+      <c r="Q53" s="12">
         <v>1.8E-3</v>
       </c>
-      <c r="R53" s="15">
+      <c r="R53" s="12">
         <v>0.18</v>
       </c>
-      <c r="S53" s="8" t="s">
+      <c r="S53" s="6" t="s">
         <v>431</v>
       </c>
-      <c r="T53" s="8">
+      <c r="T53" s="6">
         <v>603</v>
       </c>
-      <c r="U53" s="8">
+      <c r="U53" s="6">
         <v>100</v>
       </c>
-      <c r="V53" s="8">
+      <c r="V53" s="6">
         <v>100</v>
       </c>
-      <c r="W53" s="8">
+      <c r="W53" s="6">
         <v>5000</v>
       </c>
-      <c r="X53" s="8">
+      <c r="X53" s="6">
         <v>0</v>
       </c>
-      <c r="Y53" s="8" t="s">
+      <c r="Y53" s="6" t="s">
         <v>432</v>
       </c>
-      <c r="Z53" s="8"/>
-      <c r="AA53" s="8" t="s">
+      <c r="Z53" s="6"/>
+      <c r="AA53" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="AB53" s="11" t="s">
+      <c r="AB53" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC53" s="16" t="s">
+      <c r="AC53" s="23" t="s">
         <v>434</v>
       </c>
     </row>
@@ -8188,50 +8183,50 @@
       <c r="J54" t="s">
         <v>186</v>
       </c>
-      <c r="N54" s="8" t="s">
+      <c r="N54" s="6" t="s">
         <v>435</v>
       </c>
-      <c r="O54" s="8" t="s">
+      <c r="O54" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="P54" s="9">
+      <c r="P54" s="7">
         <v>100</v>
       </c>
-      <c r="Q54" s="15">
+      <c r="Q54" s="12">
         <v>1.5E-3</v>
       </c>
-      <c r="R54" s="15">
+      <c r="R54" s="12">
         <v>0.15</v>
       </c>
-      <c r="S54" s="8" t="s">
+      <c r="S54" s="6" t="s">
         <v>436</v>
       </c>
-      <c r="T54" s="8">
+      <c r="T54" s="6">
         <v>603</v>
       </c>
-      <c r="U54" s="8">
+      <c r="U54" s="6">
         <v>100</v>
       </c>
-      <c r="V54" s="8">
+      <c r="V54" s="6">
         <v>100</v>
       </c>
-      <c r="W54" s="8">
+      <c r="W54" s="6">
         <v>5000</v>
       </c>
-      <c r="X54" s="8">
+      <c r="X54" s="6">
         <v>0</v>
       </c>
-      <c r="Y54" s="8" t="s">
+      <c r="Y54" s="6" t="s">
         <v>432</v>
       </c>
-      <c r="Z54" s="8"/>
-      <c r="AA54" s="8" t="s">
+      <c r="Z54" s="6"/>
+      <c r="AA54" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="AB54" s="11" t="s">
+      <c r="AB54" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC54" s="16" t="s">
+      <c r="AC54" s="23" t="s">
         <v>438</v>
       </c>
     </row>
@@ -8267,50 +8262,50 @@
       <c r="J55" t="s">
         <v>186</v>
       </c>
-      <c r="N55" s="8" t="s">
+      <c r="N55" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="O55" s="8" t="s">
+      <c r="O55" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="P55" s="9">
+      <c r="P55" s="7">
         <v>100</v>
       </c>
-      <c r="Q55" s="15">
+      <c r="Q55" s="12">
         <v>1.4E-3</v>
       </c>
-      <c r="R55" s="15">
+      <c r="R55" s="12">
         <v>0.14000000000000001</v>
       </c>
-      <c r="S55" s="8" t="s">
+      <c r="S55" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="T55" s="8">
+      <c r="T55" s="6">
         <v>603</v>
       </c>
-      <c r="U55" s="8">
+      <c r="U55" s="6">
         <v>100</v>
       </c>
-      <c r="V55" s="8">
+      <c r="V55" s="6">
         <v>100</v>
       </c>
-      <c r="W55" s="8">
+      <c r="W55" s="6">
         <v>5000</v>
       </c>
-      <c r="X55" s="8">
+      <c r="X55" s="6">
         <v>6700</v>
       </c>
-      <c r="Y55" s="8" t="s">
+      <c r="Y55" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z55" s="8"/>
-      <c r="AA55" s="8" t="s">
+      <c r="Z55" s="6"/>
+      <c r="AA55" s="6" t="s">
         <v>441</v>
       </c>
-      <c r="AB55" s="11" t="s">
+      <c r="AB55" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC55" s="16" t="s">
+      <c r="AC55" s="23" t="s">
         <v>442</v>
       </c>
     </row>
@@ -8346,50 +8341,50 @@
       <c r="J56" t="s">
         <v>186</v>
       </c>
-      <c r="N56" s="8" t="s">
+      <c r="N56" s="6" t="s">
         <v>443</v>
       </c>
-      <c r="O56" s="8" t="s">
+      <c r="O56" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="P56" s="9">
+      <c r="P56" s="7">
         <v>100</v>
       </c>
-      <c r="Q56" s="15">
+      <c r="Q56" s="12">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="R56" s="15">
+      <c r="R56" s="12">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="S56" s="8" t="s">
+      <c r="S56" s="6" t="s">
         <v>444</v>
       </c>
-      <c r="T56" s="8">
+      <c r="T56" s="6">
         <v>603</v>
       </c>
-      <c r="U56" s="8">
+      <c r="U56" s="6">
         <v>100</v>
       </c>
-      <c r="V56" s="8">
+      <c r="V56" s="6">
         <v>100</v>
       </c>
-      <c r="W56" s="8">
+      <c r="W56" s="6">
         <v>5000</v>
       </c>
-      <c r="X56" s="8">
+      <c r="X56" s="6">
         <v>0</v>
       </c>
-      <c r="Y56" s="8" t="s">
+      <c r="Y56" s="6" t="s">
         <v>432</v>
       </c>
-      <c r="Z56" s="8"/>
-      <c r="AA56" s="8" t="s">
+      <c r="Z56" s="6"/>
+      <c r="AA56" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="AB56" s="11" t="s">
+      <c r="AB56" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC56" s="16" t="s">
+      <c r="AC56" s="23" t="s">
         <v>446</v>
       </c>
     </row>
@@ -8425,50 +8420,50 @@
       <c r="J57" t="s">
         <v>186</v>
       </c>
-      <c r="N57" s="8" t="s">
+      <c r="N57" s="6" t="s">
         <v>447</v>
       </c>
-      <c r="O57" s="8" t="s">
+      <c r="O57" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="P57" s="9">
+      <c r="P57" s="7">
         <v>100</v>
       </c>
-      <c r="Q57" s="15">
+      <c r="Q57" s="12">
         <v>1.5E-3</v>
       </c>
-      <c r="R57" s="15">
+      <c r="R57" s="12">
         <v>0.15</v>
       </c>
-      <c r="S57" s="8" t="s">
+      <c r="S57" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="T57" s="8">
+      <c r="T57" s="6">
         <v>603</v>
       </c>
-      <c r="U57" s="8">
+      <c r="U57" s="6">
         <v>100</v>
       </c>
-      <c r="V57" s="8">
+      <c r="V57" s="6">
         <v>100</v>
       </c>
-      <c r="W57" s="8">
+      <c r="W57" s="6">
         <v>5000</v>
       </c>
-      <c r="X57" s="8">
+      <c r="X57" s="6">
         <v>30900</v>
       </c>
-      <c r="Y57" s="8" t="s">
+      <c r="Y57" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z57" s="8"/>
-      <c r="AA57" s="8" t="s">
+      <c r="Z57" s="6"/>
+      <c r="AA57" s="6" t="s">
         <v>449</v>
       </c>
-      <c r="AB57" s="11" t="s">
+      <c r="AB57" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC57" s="16" t="s">
+      <c r="AC57" s="23" t="s">
         <v>450</v>
       </c>
     </row>
@@ -8504,50 +8499,50 @@
       <c r="J58" t="s">
         <v>186</v>
       </c>
-      <c r="N58" s="8" t="s">
+      <c r="N58" s="6" t="s">
         <v>455</v>
       </c>
-      <c r="O58" s="8" t="s">
+      <c r="O58" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="P58" s="9">
+      <c r="P58" s="7">
         <v>100</v>
       </c>
-      <c r="Q58" s="15">
+      <c r="Q58" s="12">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="R58" s="15">
+      <c r="R58" s="12">
         <v>0.09</v>
       </c>
-      <c r="S58" s="8" t="s">
+      <c r="S58" s="6" t="s">
         <v>456</v>
       </c>
-      <c r="T58" s="8">
+      <c r="T58" s="6">
         <v>402</v>
       </c>
-      <c r="U58" s="8">
+      <c r="U58" s="6">
         <v>100</v>
       </c>
-      <c r="V58" s="8">
+      <c r="V58" s="6">
         <v>100</v>
       </c>
-      <c r="W58" s="8">
+      <c r="W58" s="6">
         <v>10000</v>
       </c>
-      <c r="X58" s="8">
+      <c r="X58" s="6">
         <v>134000</v>
       </c>
-      <c r="Y58" s="8" t="s">
+      <c r="Y58" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z58" s="8"/>
-      <c r="AA58" s="8" t="s">
+      <c r="Z58" s="6"/>
+      <c r="AA58" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="AB58" s="11" t="s">
+      <c r="AB58" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC58" s="16" t="s">
+      <c r="AC58" s="23" t="s">
         <v>458</v>
       </c>
       <c r="AN58" s="4"/>
@@ -8584,50 +8579,50 @@
       <c r="J59" t="s">
         <v>186</v>
       </c>
-      <c r="N59" s="8" t="s">
+      <c r="N59" s="6" t="s">
         <v>459</v>
       </c>
-      <c r="O59" s="8" t="s">
+      <c r="O59" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="P59" s="9">
+      <c r="P59" s="7">
         <v>100</v>
       </c>
-      <c r="Q59" s="15">
+      <c r="Q59" s="12">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="R59" s="15">
+      <c r="R59" s="12">
         <v>0.08</v>
       </c>
-      <c r="S59" s="8" t="s">
+      <c r="S59" s="6" t="s">
         <v>460</v>
       </c>
-      <c r="T59" s="8">
+      <c r="T59" s="6">
         <v>402</v>
       </c>
-      <c r="U59" s="8">
+      <c r="U59" s="6">
         <v>100</v>
       </c>
-      <c r="V59" s="8">
+      <c r="V59" s="6">
         <v>100</v>
       </c>
-      <c r="W59" s="8">
+      <c r="W59" s="6">
         <v>10000</v>
       </c>
-      <c r="X59" s="8">
+      <c r="X59" s="6">
         <v>5619500</v>
       </c>
-      <c r="Y59" s="8" t="s">
+      <c r="Y59" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z59" s="8"/>
-      <c r="AA59" s="8" t="s">
+      <c r="Z59" s="6"/>
+      <c r="AA59" s="6" t="s">
         <v>461</v>
       </c>
-      <c r="AB59" s="11" t="s">
+      <c r="AB59" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC59" s="16" t="s">
+      <c r="AC59" s="23" t="s">
         <v>462</v>
       </c>
       <c r="AN59" s="4"/>
@@ -8664,26 +8659,26 @@
       <c r="K60" t="s">
         <v>186</v>
       </c>
-      <c r="N60" s="17" t="s">
+      <c r="N60" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="O60" s="18" t="s">
-        <v>630</v>
-      </c>
-      <c r="P60" s="19">
+      <c r="O60" s="14" t="s">
+        <v>629</v>
+      </c>
+      <c r="P60" s="15">
         <v>6</v>
       </c>
-      <c r="Q60" s="20">
+      <c r="Q60" s="16">
         <v>1.01</v>
       </c>
-      <c r="R60" s="20">
+      <c r="R60" s="16">
         <v>6.06</v>
       </c>
-      <c r="S60" s="18" t="s">
-        <v>633</v>
+      <c r="S60" s="14" t="s">
+        <v>632</v>
       </c>
       <c r="AC60" s="26" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="AN60" s="4"/>
     </row>
@@ -8719,50 +8714,50 @@
       <c r="J61" t="s">
         <v>186</v>
       </c>
-      <c r="N61" s="8" t="s">
+      <c r="N61" s="6" t="s">
         <v>463</v>
       </c>
-      <c r="O61" s="8" t="s">
+      <c r="O61" s="6" t="s">
         <v>464</v>
       </c>
-      <c r="P61" s="9">
+      <c r="P61" s="7">
         <v>100</v>
       </c>
-      <c r="Q61" s="15">
+      <c r="Q61" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="R61" s="15">
+      <c r="R61" s="12">
         <v>0.5</v>
       </c>
-      <c r="S61" s="8" t="s">
+      <c r="S61" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="T61" s="8" t="s">
+      <c r="T61" s="6" t="s">
         <v>466</v>
       </c>
-      <c r="U61" s="8">
+      <c r="U61" s="6">
         <v>100</v>
       </c>
-      <c r="V61" s="8">
+      <c r="V61" s="6">
         <v>100</v>
       </c>
-      <c r="W61" s="8">
+      <c r="W61" s="6">
         <v>5000</v>
       </c>
-      <c r="X61" s="8">
+      <c r="X61" s="6">
         <v>584400</v>
       </c>
-      <c r="Y61" s="8" t="s">
+      <c r="Y61" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z61" s="8"/>
-      <c r="AA61" s="8" t="s">
+      <c r="Z61" s="6"/>
+      <c r="AA61" s="6" t="s">
         <v>467</v>
       </c>
-      <c r="AB61" s="11" t="s">
+      <c r="AB61" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC61" s="16" t="s">
+      <c r="AC61" s="23" t="s">
         <v>468</v>
       </c>
       <c r="AN61" s="4"/>
@@ -8799,50 +8794,50 @@
       <c r="J62" t="s">
         <v>186</v>
       </c>
-      <c r="N62" s="8" t="s">
+      <c r="N62" s="6" t="s">
         <v>469</v>
       </c>
-      <c r="O62" s="8" t="s">
+      <c r="O62" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="P62" s="9">
+      <c r="P62" s="7">
         <v>50</v>
       </c>
-      <c r="Q62" s="15">
+      <c r="Q62" s="12">
         <v>9.2999999999999992E-3</v>
       </c>
-      <c r="R62" s="15">
+      <c r="R62" s="12">
         <v>0.47</v>
       </c>
-      <c r="S62" s="8" t="s">
+      <c r="S62" s="6" t="s">
         <v>470</v>
       </c>
-      <c r="T62" s="8" t="s">
+      <c r="T62" s="6" t="s">
         <v>466</v>
       </c>
-      <c r="U62" s="8">
+      <c r="U62" s="6">
         <v>50</v>
       </c>
-      <c r="V62" s="8">
+      <c r="V62" s="6">
         <v>50</v>
       </c>
-      <c r="W62" s="8">
+      <c r="W62" s="6">
         <v>5000</v>
       </c>
-      <c r="X62" s="8">
+      <c r="X62" s="6">
         <v>15400</v>
       </c>
-      <c r="Y62" s="8" t="s">
+      <c r="Y62" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z62" s="8"/>
-      <c r="AA62" s="8" t="s">
+      <c r="Z62" s="6"/>
+      <c r="AA62" s="6" t="s">
         <v>471</v>
       </c>
-      <c r="AB62" s="11" t="s">
+      <c r="AB62" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC62" s="16" t="s">
+      <c r="AC62" s="23" t="s">
         <v>472</v>
       </c>
       <c r="AN62" s="4"/>
@@ -8879,50 +8874,50 @@
       <c r="J63" t="s">
         <v>186</v>
       </c>
-      <c r="N63" s="8" t="s">
+      <c r="N63" s="6" t="s">
         <v>473</v>
       </c>
-      <c r="O63" s="8" t="s">
+      <c r="O63" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="P63" s="9">
+      <c r="P63" s="7">
         <v>5</v>
       </c>
-      <c r="Q63" s="15">
+      <c r="Q63" s="12">
         <v>0.21879999999999999</v>
       </c>
-      <c r="R63" s="15">
+      <c r="R63" s="12">
         <v>1.0900000000000001</v>
       </c>
-      <c r="S63" s="8" t="s">
+      <c r="S63" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="T63" s="8" t="s">
+      <c r="T63" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="U63" s="8">
+      <c r="U63" s="6">
         <v>5</v>
       </c>
-      <c r="V63" s="8">
+      <c r="V63" s="6">
         <v>5</v>
       </c>
-      <c r="W63" s="8">
+      <c r="W63" s="6">
         <v>3500</v>
       </c>
-      <c r="X63" s="8">
+      <c r="X63" s="6">
         <v>107795</v>
       </c>
-      <c r="Y63" s="8" t="s">
+      <c r="Y63" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z63" s="8"/>
-      <c r="AA63" s="8" t="s">
+      <c r="Z63" s="6"/>
+      <c r="AA63" s="6" t="s">
         <v>477</v>
       </c>
-      <c r="AB63" s="11" t="s">
+      <c r="AB63" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC63" s="16" t="s">
+      <c r="AC63" s="23" t="s">
         <v>478</v>
       </c>
       <c r="AN63" s="4"/>
@@ -8959,26 +8954,26 @@
       <c r="K64" t="s">
         <v>186</v>
       </c>
-      <c r="N64" s="17" t="s">
+      <c r="N64" s="13" t="s">
+        <v>634</v>
+      </c>
+      <c r="O64" s="14" t="s">
         <v>635</v>
       </c>
-      <c r="O64" s="18" t="s">
-        <v>636</v>
-      </c>
-      <c r="P64" s="19">
-        <v>2</v>
-      </c>
-      <c r="Q64" s="20">
+      <c r="P64" s="15">
+        <v>2</v>
+      </c>
+      <c r="Q64" s="16">
         <v>4.9400000000000004</v>
       </c>
-      <c r="R64" s="20">
+      <c r="R64" s="16">
         <v>9.8800000000000008</v>
       </c>
-      <c r="S64" s="18" t="s">
-        <v>634</v>
+      <c r="S64" s="14" t="s">
+        <v>633</v>
       </c>
       <c r="AC64" s="26" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="AN64" s="4"/>
     </row>
@@ -9014,26 +9009,26 @@
       <c r="K65" t="s">
         <v>186</v>
       </c>
-      <c r="N65" s="17" t="s">
+      <c r="N65" s="13" t="s">
+        <v>637</v>
+      </c>
+      <c r="O65" s="14" t="s">
         <v>638</v>
       </c>
-      <c r="O65" s="18" t="s">
-        <v>639</v>
-      </c>
-      <c r="P65" s="19">
-        <v>2</v>
-      </c>
-      <c r="Q65" s="20">
+      <c r="P65" s="15">
+        <v>2</v>
+      </c>
+      <c r="Q65" s="16">
         <v>0.89600000000000002</v>
       </c>
-      <c r="R65" s="20">
+      <c r="R65" s="16">
         <v>1.79</v>
       </c>
-      <c r="S65" s="18" t="s">
-        <v>637</v>
+      <c r="S65" s="14" t="s">
+        <v>636</v>
       </c>
       <c r="AC65" s="26" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="66" spans="1:29" ht="15" customHeight="1">
@@ -9068,50 +9063,50 @@
       <c r="J66" t="s">
         <v>186</v>
       </c>
-      <c r="N66" s="8" t="s">
+      <c r="N66" s="6" t="s">
         <v>518</v>
       </c>
-      <c r="O66" s="8" t="s">
+      <c r="O66" s="6" t="s">
         <v>519</v>
       </c>
-      <c r="P66" s="9">
+      <c r="P66" s="7">
         <v>8</v>
       </c>
-      <c r="Q66" s="15">
+      <c r="Q66" s="12">
         <v>2.2972000000000001</v>
       </c>
-      <c r="R66" s="15">
+      <c r="R66" s="12">
         <v>18.38</v>
       </c>
-      <c r="S66" s="8" t="s">
+      <c r="S66" s="6" t="s">
         <v>520</v>
       </c>
-      <c r="T66" s="8" t="s">
+      <c r="T66" s="6" t="s">
         <v>521</v>
       </c>
-      <c r="U66" s="8">
-        <v>1</v>
-      </c>
-      <c r="V66" s="8">
-        <v>1</v>
-      </c>
-      <c r="W66" s="8">
+      <c r="U66" s="6">
+        <v>1</v>
+      </c>
+      <c r="V66" s="6">
+        <v>1</v>
+      </c>
+      <c r="W66" s="6">
         <v>2500</v>
       </c>
-      <c r="X66" s="8">
+      <c r="X66" s="6">
         <v>12603</v>
       </c>
-      <c r="Y66" s="8" t="s">
+      <c r="Y66" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z66" s="8"/>
-      <c r="AA66" s="8" t="s">
+      <c r="Z66" s="6"/>
+      <c r="AA66" s="6" t="s">
         <v>522</v>
       </c>
-      <c r="AB66" s="11" t="s">
+      <c r="AB66" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC66" s="16" t="s">
+      <c r="AC66" s="23" t="s">
         <v>523</v>
       </c>
     </row>
@@ -9147,50 +9142,50 @@
       <c r="J67" t="s">
         <v>186</v>
       </c>
-      <c r="N67" s="8" t="s">
+      <c r="N67" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="O67" s="8" t="s">
+      <c r="O67" s="6" t="s">
         <v>480</v>
       </c>
-      <c r="P67" s="9">
-        <v>2</v>
-      </c>
-      <c r="Q67" s="15">
+      <c r="P67" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q67" s="12">
         <v>0.52080000000000004</v>
       </c>
-      <c r="R67" s="15">
+      <c r="R67" s="12">
         <v>1.04</v>
       </c>
-      <c r="S67" s="8" t="s">
+      <c r="S67" s="6" t="s">
         <v>481</v>
       </c>
-      <c r="T67" s="8" t="s">
+      <c r="T67" s="6" t="s">
         <v>482</v>
       </c>
-      <c r="U67" s="8">
-        <v>1</v>
-      </c>
-      <c r="V67" s="8">
-        <v>1</v>
-      </c>
-      <c r="W67" s="8">
+      <c r="U67" s="6">
+        <v>1</v>
+      </c>
+      <c r="V67" s="6">
+        <v>1</v>
+      </c>
+      <c r="W67" s="6">
         <v>3000</v>
       </c>
-      <c r="X67" s="8">
+      <c r="X67" s="6">
         <v>660</v>
       </c>
-      <c r="Y67" s="8" t="s">
+      <c r="Y67" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z67" s="8"/>
-      <c r="AA67" s="8" t="s">
+      <c r="Z67" s="6"/>
+      <c r="AA67" s="6" t="s">
         <v>483</v>
       </c>
-      <c r="AB67" s="11" t="s">
+      <c r="AB67" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC67" s="16" t="s">
+      <c r="AC67" s="23" t="s">
         <v>484</v>
       </c>
     </row>
@@ -9226,50 +9221,50 @@
       <c r="J68" t="s">
         <v>186</v>
       </c>
-      <c r="N68" s="8" t="s">
+      <c r="N68" s="6" t="s">
         <v>485</v>
       </c>
-      <c r="O68" s="8" t="s">
+      <c r="O68" s="6" t="s">
         <v>486</v>
       </c>
-      <c r="P68" s="9">
+      <c r="P68" s="7">
         <v>5</v>
       </c>
-      <c r="Q68" s="15">
+      <c r="Q68" s="12">
         <v>2.3386999999999998</v>
       </c>
-      <c r="R68" s="15">
+      <c r="R68" s="12">
         <v>11.69</v>
       </c>
-      <c r="S68" s="8" t="s">
+      <c r="S68" s="6" t="s">
         <v>487</v>
       </c>
-      <c r="T68" s="8" t="s">
+      <c r="T68" s="6" t="s">
         <v>488</v>
       </c>
-      <c r="U68" s="8">
+      <c r="U68" s="6">
         <v>5</v>
       </c>
-      <c r="V68" s="8">
+      <c r="V68" s="6">
         <v>5</v>
       </c>
-      <c r="W68" s="8">
+      <c r="W68" s="6">
         <v>2000</v>
       </c>
-      <c r="X68" s="8">
+      <c r="X68" s="6">
         <v>59900</v>
       </c>
-      <c r="Y68" s="8" t="s">
+      <c r="Y68" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z68" s="8"/>
-      <c r="AA68" s="8" t="s">
+      <c r="Z68" s="6"/>
+      <c r="AA68" s="6" t="s">
         <v>489</v>
       </c>
-      <c r="AB68" s="11" t="s">
+      <c r="AB68" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC68" s="16" t="s">
+      <c r="AC68" s="23" t="s">
         <v>490</v>
       </c>
     </row>
@@ -9305,50 +9300,50 @@
       <c r="J69" t="s">
         <v>186</v>
       </c>
-      <c r="N69" s="8" t="s">
+      <c r="N69" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="O69" s="8" t="s">
+      <c r="O69" s="6" t="s">
         <v>491</v>
       </c>
-      <c r="P69" s="9">
+      <c r="P69" s="7">
         <v>5</v>
       </c>
-      <c r="Q69" s="15">
+      <c r="Q69" s="12">
         <v>0.13800000000000001</v>
       </c>
-      <c r="R69" s="15">
+      <c r="R69" s="12">
         <v>0.69</v>
       </c>
-      <c r="S69" s="8" t="s">
+      <c r="S69" s="6" t="s">
         <v>492</v>
       </c>
-      <c r="T69" s="8" t="s">
+      <c r="T69" s="6" t="s">
         <v>493</v>
       </c>
-      <c r="U69" s="8">
+      <c r="U69" s="6">
         <v>5</v>
       </c>
-      <c r="V69" s="8">
+      <c r="V69" s="6">
         <v>5</v>
       </c>
-      <c r="W69" s="8">
+      <c r="W69" s="6">
         <v>3000</v>
       </c>
-      <c r="X69" s="8">
+      <c r="X69" s="6">
         <v>29740</v>
       </c>
-      <c r="Y69" s="8" t="s">
+      <c r="Y69" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z69" s="8"/>
-      <c r="AA69" s="8" t="s">
+      <c r="Z69" s="6"/>
+      <c r="AA69" s="6" t="s">
         <v>494</v>
       </c>
-      <c r="AB69" s="11" t="s">
+      <c r="AB69" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC69" s="16" t="s">
+      <c r="AC69" s="23" t="s">
         <v>495</v>
       </c>
     </row>
@@ -9384,50 +9379,50 @@
       <c r="J70" t="s">
         <v>186</v>
       </c>
-      <c r="N70" s="8" t="s">
+      <c r="N70" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="O70" s="8" t="s">
+      <c r="O70" s="6" t="s">
         <v>496</v>
       </c>
-      <c r="P70" s="9">
-        <v>2</v>
-      </c>
-      <c r="Q70" s="15">
+      <c r="P70" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q70" s="12">
         <v>2.7793000000000001</v>
       </c>
-      <c r="R70" s="15">
+      <c r="R70" s="12">
         <v>5.56</v>
       </c>
-      <c r="S70" s="8" t="s">
+      <c r="S70" s="6" t="s">
         <v>497</v>
       </c>
-      <c r="T70" s="8" t="s">
+      <c r="T70" s="6" t="s">
         <v>498</v>
       </c>
-      <c r="U70" s="8">
-        <v>1</v>
-      </c>
-      <c r="V70" s="8">
-        <v>1</v>
-      </c>
-      <c r="W70" s="8">
+      <c r="U70" s="6">
+        <v>1</v>
+      </c>
+      <c r="V70" s="6">
+        <v>1</v>
+      </c>
+      <c r="W70" s="6">
         <v>2500</v>
       </c>
-      <c r="X70" s="8">
+      <c r="X70" s="6">
         <v>40852</v>
       </c>
-      <c r="Y70" s="8" t="s">
+      <c r="Y70" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z70" s="8"/>
-      <c r="AA70" s="8" t="s">
+      <c r="Z70" s="6"/>
+      <c r="AA70" s="6" t="s">
         <v>499</v>
       </c>
-      <c r="AB70" s="11" t="s">
+      <c r="AB70" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC70" s="16" t="s">
+      <c r="AC70" s="23" t="s">
         <v>500</v>
       </c>
     </row>
@@ -9463,50 +9458,50 @@
       <c r="J71" t="s">
         <v>186</v>
       </c>
-      <c r="N71" s="8" t="s">
+      <c r="N71" s="6" t="s">
         <v>530</v>
       </c>
-      <c r="O71" s="8" t="s">
+      <c r="O71" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="P71" s="9">
+      <c r="P71" s="7">
         <v>5</v>
       </c>
-      <c r="Q71" s="15">
+      <c r="Q71" s="12">
         <v>0.378</v>
       </c>
-      <c r="R71" s="15">
+      <c r="R71" s="12">
         <v>1.89</v>
       </c>
-      <c r="S71" s="8" t="s">
+      <c r="S71" s="6" t="s">
         <v>531</v>
       </c>
-      <c r="T71" s="8" t="s">
+      <c r="T71" s="6" t="s">
         <v>532</v>
       </c>
-      <c r="U71" s="8">
+      <c r="U71" s="6">
         <v>5</v>
       </c>
-      <c r="V71" s="8">
+      <c r="V71" s="6">
         <v>5</v>
       </c>
-      <c r="W71" s="8">
+      <c r="W71" s="6">
         <v>1000</v>
       </c>
-      <c r="X71" s="8">
+      <c r="X71" s="6">
         <v>4355</v>
       </c>
-      <c r="Y71" s="8" t="s">
+      <c r="Y71" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z71" s="8"/>
-      <c r="AA71" s="8" t="s">
+      <c r="Z71" s="6"/>
+      <c r="AA71" s="6" t="s">
         <v>533</v>
       </c>
-      <c r="AB71" s="11" t="s">
+      <c r="AB71" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC71" s="16" t="s">
+      <c r="AC71" s="23" t="s">
         <v>534</v>
       </c>
     </row>
@@ -9542,50 +9537,50 @@
       <c r="J72" t="s">
         <v>186</v>
       </c>
-      <c r="N72" s="8" t="s">
+      <c r="N72" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="O72" s="8" t="s">
+      <c r="O72" s="6" t="s">
         <v>501</v>
       </c>
-      <c r="P72" s="9">
-        <v>2</v>
-      </c>
-      <c r="Q72" s="15">
+      <c r="P72" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q72" s="12">
         <v>2.9626999999999999</v>
       </c>
-      <c r="R72" s="15">
+      <c r="R72" s="12">
         <v>5.93</v>
       </c>
-      <c r="S72" s="8" t="s">
+      <c r="S72" s="6" t="s">
         <v>502</v>
       </c>
-      <c r="T72" s="8" t="s">
+      <c r="T72" s="6" t="s">
         <v>503</v>
       </c>
-      <c r="U72" s="8">
-        <v>1</v>
-      </c>
-      <c r="V72" s="8">
-        <v>1</v>
-      </c>
-      <c r="W72" s="8">
+      <c r="U72" s="6">
+        <v>1</v>
+      </c>
+      <c r="V72" s="6">
+        <v>1</v>
+      </c>
+      <c r="W72" s="6">
         <v>2500</v>
       </c>
-      <c r="X72" s="8">
+      <c r="X72" s="6">
         <v>91</v>
       </c>
-      <c r="Y72" s="8" t="s">
+      <c r="Y72" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z72" s="8"/>
-      <c r="AA72" s="8" t="s">
+      <c r="Z72" s="6"/>
+      <c r="AA72" s="6" t="s">
         <v>504</v>
       </c>
-      <c r="AB72" s="11" t="s">
+      <c r="AB72" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC72" s="16" t="s">
+      <c r="AC72" s="23" t="s">
         <v>505</v>
       </c>
     </row>
@@ -9621,50 +9616,50 @@
       <c r="J73" t="s">
         <v>186</v>
       </c>
-      <c r="N73" s="8" t="s">
+      <c r="N73" s="6" t="s">
         <v>506</v>
       </c>
-      <c r="O73" s="8" t="s">
+      <c r="O73" s="6" t="s">
         <v>480</v>
       </c>
-      <c r="P73" s="9">
+      <c r="P73" s="7">
         <v>5</v>
       </c>
-      <c r="Q73" s="15">
+      <c r="Q73" s="12">
         <v>0.23280000000000001</v>
       </c>
-      <c r="R73" s="15">
+      <c r="R73" s="12">
         <v>1.1599999999999999</v>
       </c>
-      <c r="S73" s="8" t="s">
+      <c r="S73" s="6" t="s">
         <v>507</v>
       </c>
-      <c r="T73" s="8" t="s">
+      <c r="T73" s="6" t="s">
         <v>508</v>
       </c>
-      <c r="U73" s="8">
+      <c r="U73" s="6">
         <v>5</v>
       </c>
-      <c r="V73" s="8">
+      <c r="V73" s="6">
         <v>5</v>
       </c>
-      <c r="W73" s="8">
+      <c r="W73" s="6">
         <v>3000</v>
       </c>
-      <c r="X73" s="8">
+      <c r="X73" s="6">
         <v>11190</v>
       </c>
-      <c r="Y73" s="8" t="s">
+      <c r="Y73" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z73" s="8"/>
-      <c r="AA73" s="8" t="s">
+      <c r="Z73" s="6"/>
+      <c r="AA73" s="6" t="s">
         <v>509</v>
       </c>
-      <c r="AB73" s="11" t="s">
+      <c r="AB73" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC73" s="16" t="s">
+      <c r="AC73" s="23" t="s">
         <v>510</v>
       </c>
     </row>
@@ -9700,50 +9695,50 @@
       <c r="J74" t="s">
         <v>186</v>
       </c>
-      <c r="N74" s="8" t="s">
+      <c r="N74" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="O74" s="8" t="s">
+      <c r="O74" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="P74" s="9">
+      <c r="P74" s="7">
         <v>5</v>
       </c>
-      <c r="Q74" s="15">
+      <c r="Q74" s="12">
         <v>0.32719999999999999</v>
       </c>
-      <c r="R74" s="15">
+      <c r="R74" s="12">
         <v>1.64</v>
       </c>
-      <c r="S74" s="8" t="s">
+      <c r="S74" s="6" t="s">
         <v>511</v>
       </c>
-      <c r="T74" s="8" t="s">
+      <c r="T74" s="6" t="s">
         <v>512</v>
       </c>
-      <c r="U74" s="8">
+      <c r="U74" s="6">
         <v>5</v>
       </c>
-      <c r="V74" s="8">
+      <c r="V74" s="6">
         <v>5</v>
       </c>
-      <c r="W74" s="8">
+      <c r="W74" s="6">
         <v>3000</v>
       </c>
-      <c r="X74" s="8">
+      <c r="X74" s="6">
         <v>0</v>
       </c>
-      <c r="Y74" s="8" t="s">
+      <c r="Y74" s="6" t="s">
         <v>432</v>
       </c>
-      <c r="Z74" s="8"/>
-      <c r="AA74" s="8" t="s">
+      <c r="Z74" s="6"/>
+      <c r="AA74" s="6" t="s">
         <v>513</v>
       </c>
-      <c r="AB74" s="11" t="s">
+      <c r="AB74" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC74" s="16" t="s">
+      <c r="AC74" s="23" t="s">
         <v>514</v>
       </c>
     </row>
@@ -9779,71 +9774,71 @@
       <c r="J75" t="s">
         <v>186</v>
       </c>
-      <c r="N75" s="8" t="s">
+      <c r="N75" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="O75" s="8" t="s">
+      <c r="O75" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="P75" s="9">
-        <v>2</v>
-      </c>
-      <c r="Q75" s="15">
+      <c r="P75" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q75" s="12">
         <v>0.84150000000000003</v>
       </c>
-      <c r="R75" s="15">
+      <c r="R75" s="12">
         <v>1.68</v>
       </c>
-      <c r="S75" s="8" t="s">
+      <c r="S75" s="6" t="s">
         <v>515</v>
       </c>
-      <c r="T75" s="8" t="s">
+      <c r="T75" s="6" t="s">
         <v>512</v>
       </c>
-      <c r="U75" s="8">
-        <v>1</v>
-      </c>
-      <c r="V75" s="8">
-        <v>1</v>
-      </c>
-      <c r="W75" s="8">
+      <c r="U75" s="6">
+        <v>1</v>
+      </c>
+      <c r="V75" s="6">
+        <v>1</v>
+      </c>
+      <c r="W75" s="6">
         <v>1000</v>
       </c>
-      <c r="X75" s="8">
+      <c r="X75" s="6">
         <v>436</v>
       </c>
-      <c r="Y75" s="8" t="s">
+      <c r="Y75" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z75" s="8"/>
-      <c r="AA75" s="8" t="s">
+      <c r="Z75" s="6"/>
+      <c r="AA75" s="6" t="s">
         <v>516</v>
       </c>
-      <c r="AB75" s="11" t="s">
+      <c r="AB75" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC75" s="16" t="s">
+      <c r="AC75" s="23" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="76" spans="1:29" ht="15" customHeight="1"/>
     <row r="77" spans="1:29" ht="15" customHeight="1">
-      <c r="N77" s="30"/>
-      <c r="O77" s="30"/>
-      <c r="P77" s="31"/>
-      <c r="Q77" s="31"/>
-      <c r="R77" s="31"/>
-      <c r="S77" s="30"/>
-      <c r="T77" s="31"/>
-      <c r="U77" s="31"/>
-      <c r="V77" s="31"/>
-      <c r="W77" s="31"/>
-      <c r="X77" s="31"/>
-      <c r="Y77" s="30"/>
-      <c r="Z77" s="30"/>
-      <c r="AA77" s="30"/>
-      <c r="AB77" s="32"/>
-      <c r="AC77" s="3"/>
+      <c r="N77" s="22"/>
+      <c r="O77" s="22"/>
+      <c r="P77" s="22"/>
+      <c r="Q77" s="22"/>
+      <c r="R77" s="22"/>
+      <c r="S77" s="22"/>
+      <c r="T77" s="22"/>
+      <c r="U77" s="22"/>
+      <c r="V77" s="22"/>
+      <c r="W77" s="22"/>
+      <c r="X77" s="22"/>
+      <c r="Y77" s="22"/>
+      <c r="Z77" s="22"/>
+      <c r="AA77" s="22"/>
+      <c r="AB77"/>
+      <c r="AC77" s="25"/>
     </row>
     <row r="78" spans="1:29" ht="15" customHeight="1">
       <c r="A78" t="s">
@@ -9880,58 +9875,58 @@
         <v>226</v>
       </c>
       <c r="L78" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="M78" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="N78" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="N78" s="5" t="s">
         <v>600</v>
       </c>
-      <c r="O78" s="6" t="s">
+      <c r="O78" s="5" t="s">
         <v>601</v>
       </c>
-      <c r="P78" s="13" t="s">
+      <c r="P78" s="10" t="s">
         <v>602</v>
       </c>
-      <c r="Q78" s="14" t="s">
+      <c r="Q78" s="11" t="s">
         <v>603</v>
       </c>
-      <c r="R78" s="14" t="s">
+      <c r="R78" s="11" t="s">
         <v>604</v>
       </c>
-      <c r="S78" s="6" t="s">
+      <c r="S78" s="5" t="s">
+        <v>653</v>
+      </c>
+      <c r="T78" s="5" t="s">
         <v>605</v>
       </c>
-      <c r="T78" s="6" t="s">
+      <c r="U78" s="5" t="s">
         <v>606</v>
       </c>
-      <c r="U78" s="6" t="s">
+      <c r="V78" s="5" t="s">
         <v>607</v>
       </c>
-      <c r="V78" s="6" t="s">
+      <c r="W78" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="W78" s="6" t="s">
+      <c r="X78" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="X78" s="6" t="s">
+      <c r="Y78" s="5" t="s">
         <v>610</v>
       </c>
-      <c r="Y78" s="6" t="s">
+      <c r="Z78" s="5" t="s">
         <v>611</v>
       </c>
-      <c r="Z78" s="6" t="s">
+      <c r="AA78" s="5" t="s">
         <v>612</v>
       </c>
-      <c r="AA78" s="6" t="s">
+      <c r="AB78" s="5" t="s">
         <v>613</v>
       </c>
-      <c r="AB78" s="6" t="s">
+      <c r="AC78" s="5" t="s">
         <v>614</v>
-      </c>
-      <c r="AC78" s="7" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="79" spans="1:29" ht="15" customHeight="1">
@@ -9963,7 +9958,8 @@
       <c r="L79" t="s">
         <v>186</v>
       </c>
-      <c r="P79" s="22"/>
+      <c r="P79" s="18"/>
+      <c r="AC79" s="27"/>
     </row>
     <row r="80" spans="1:29" ht="15" customHeight="1">
       <c r="A80">
@@ -9994,7 +9990,8 @@
       <c r="L80" t="s">
         <v>186</v>
       </c>
-      <c r="P80" s="22"/>
+      <c r="P80" s="18"/>
+      <c r="AC80" s="27"/>
     </row>
     <row r="81" spans="1:29" ht="15" customHeight="1">
       <c r="A81">
@@ -10025,50 +10022,50 @@
       <c r="J81" t="s">
         <v>186</v>
       </c>
-      <c r="N81" s="8" t="s">
+      <c r="N81" s="6" t="s">
         <v>535</v>
       </c>
-      <c r="O81" s="8" t="s">
+      <c r="O81" s="6" t="s">
         <v>536</v>
       </c>
-      <c r="P81" s="9">
+      <c r="P81" s="7">
         <v>5</v>
       </c>
-      <c r="Q81" s="15">
+      <c r="Q81" s="12">
         <v>0.35630000000000001</v>
       </c>
-      <c r="R81" s="15">
+      <c r="R81" s="12">
         <v>1.78</v>
       </c>
-      <c r="S81" s="8" t="s">
+      <c r="S81" s="6" t="s">
         <v>537</v>
       </c>
-      <c r="T81" s="8" t="s">
+      <c r="T81" s="6" t="s">
         <v>538</v>
       </c>
-      <c r="U81" s="8">
+      <c r="U81" s="6">
         <v>5</v>
       </c>
-      <c r="V81" s="8">
+      <c r="V81" s="6">
         <v>5</v>
       </c>
-      <c r="W81" s="8">
+      <c r="W81" s="6">
         <v>3000</v>
       </c>
-      <c r="X81" s="8">
+      <c r="X81" s="6">
         <v>19735</v>
       </c>
-      <c r="Y81" s="8" t="s">
+      <c r="Y81" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z81" s="8"/>
-      <c r="AA81" s="8" t="s">
+      <c r="Z81" s="6"/>
+      <c r="AA81" s="6" t="s">
         <v>539</v>
       </c>
-      <c r="AB81" s="11" t="s">
+      <c r="AB81" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC81" s="16" t="s">
+      <c r="AC81" s="23" t="s">
         <v>540</v>
       </c>
     </row>
@@ -10101,7 +10098,8 @@
       <c r="L82" t="s">
         <v>186</v>
       </c>
-      <c r="P82" s="22"/>
+      <c r="P82" s="18"/>
+      <c r="AC82" s="27"/>
     </row>
     <row r="83" spans="1:29" ht="15" customHeight="1">
       <c r="A83">
@@ -10132,50 +10130,50 @@
       <c r="J83" t="s">
         <v>186</v>
       </c>
-      <c r="N83" s="8" t="s">
+      <c r="N83" s="6" t="s">
         <v>541</v>
       </c>
-      <c r="O83" s="8" t="s">
+      <c r="O83" s="6" t="s">
         <v>542</v>
       </c>
-      <c r="P83" s="9">
+      <c r="P83" s="7">
         <v>10</v>
       </c>
-      <c r="Q83" s="15">
+      <c r="Q83" s="12">
         <v>4.07E-2</v>
       </c>
-      <c r="R83" s="15">
+      <c r="R83" s="12">
         <v>0.41</v>
       </c>
-      <c r="S83" s="8" t="s">
+      <c r="S83" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="T83" s="8" t="s">
+      <c r="T83" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="U83" s="8">
+      <c r="U83" s="6">
         <v>10</v>
       </c>
-      <c r="V83" s="8">
+      <c r="V83" s="6">
         <v>10</v>
       </c>
-      <c r="W83" s="8">
+      <c r="W83" s="6">
         <v>3000</v>
       </c>
-      <c r="X83" s="8">
+      <c r="X83" s="6">
         <v>267340</v>
       </c>
-      <c r="Y83" s="8" t="s">
+      <c r="Y83" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z83" s="8"/>
-      <c r="AA83" s="8" t="s">
+      <c r="Z83" s="6"/>
+      <c r="AA83" s="6" t="s">
         <v>544</v>
       </c>
-      <c r="AB83" s="11" t="s">
+      <c r="AB83" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC83" s="16" t="s">
+      <c r="AC83" s="23" t="s">
         <v>545</v>
       </c>
     </row>
@@ -10208,7 +10206,8 @@
       <c r="L84" t="s">
         <v>186</v>
       </c>
-      <c r="P84" s="22"/>
+      <c r="P84" s="18"/>
+      <c r="AC84" s="27"/>
     </row>
     <row r="85" spans="1:29" ht="15" customHeight="1">
       <c r="A85">
@@ -10239,7 +10238,8 @@
       <c r="L85" t="s">
         <v>186</v>
       </c>
-      <c r="P85" s="22"/>
+      <c r="P85" s="18"/>
+      <c r="AC85" s="27"/>
     </row>
     <row r="86" spans="1:29" ht="15" customHeight="1">
       <c r="A86">
@@ -10270,50 +10270,50 @@
       <c r="J86" t="s">
         <v>186</v>
       </c>
-      <c r="N86" s="8" t="s">
+      <c r="N86" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="O86" s="8" t="s">
+      <c r="O86" s="6" t="s">
         <v>546</v>
       </c>
-      <c r="P86" s="9">
-        <v>2</v>
-      </c>
-      <c r="Q86" s="15">
+      <c r="P86" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q86" s="12">
         <v>2.1164000000000001</v>
       </c>
-      <c r="R86" s="15">
+      <c r="R86" s="12">
         <v>4.2300000000000004</v>
       </c>
-      <c r="S86" s="8" t="s">
+      <c r="S86" s="6" t="s">
         <v>547</v>
       </c>
-      <c r="T86" s="8" t="s">
+      <c r="T86" s="6" t="s">
         <v>548</v>
       </c>
-      <c r="U86" s="8">
-        <v>1</v>
-      </c>
-      <c r="V86" s="8">
-        <v>1</v>
-      </c>
-      <c r="W86" s="8">
+      <c r="U86" s="6">
+        <v>1</v>
+      </c>
+      <c r="V86" s="6">
+        <v>1</v>
+      </c>
+      <c r="W86" s="6">
         <v>120</v>
       </c>
-      <c r="X86" s="8">
+      <c r="X86" s="6">
         <v>2382</v>
       </c>
-      <c r="Y86" s="8" t="s">
+      <c r="Y86" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z86" s="8"/>
-      <c r="AA86" s="8" t="s">
+      <c r="Z86" s="6"/>
+      <c r="AA86" s="6" t="s">
         <v>549</v>
       </c>
-      <c r="AB86" s="11" t="s">
+      <c r="AB86" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC86" s="16" t="s">
+      <c r="AC86" s="23" t="s">
         <v>550</v>
       </c>
     </row>
@@ -10346,58 +10346,58 @@
       <c r="J87" t="s">
         <v>186</v>
       </c>
-      <c r="N87" s="8" t="s">
+      <c r="N87" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="O87" s="8" t="s">
+      <c r="O87" s="6" t="s">
         <v>551</v>
       </c>
-      <c r="P87" s="9">
+      <c r="P87" s="7">
         <v>5</v>
       </c>
-      <c r="Q87" s="15">
+      <c r="Q87" s="12">
         <v>0.18090000000000001</v>
       </c>
-      <c r="R87" s="15">
+      <c r="R87" s="12">
         <v>0.9</v>
       </c>
-      <c r="S87" s="8" t="s">
+      <c r="S87" s="6" t="s">
         <v>552</v>
       </c>
-      <c r="T87" s="8" t="s">
+      <c r="T87" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="U87" s="8">
+      <c r="U87" s="6">
         <v>5</v>
       </c>
-      <c r="V87" s="8">
+      <c r="V87" s="6">
         <v>5</v>
       </c>
-      <c r="W87" s="8">
+      <c r="W87" s="6">
         <v>3000</v>
       </c>
-      <c r="X87" s="8">
+      <c r="X87" s="6">
         <v>4525</v>
       </c>
-      <c r="Y87" s="8" t="s">
+      <c r="Y87" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z87" s="8"/>
-      <c r="AA87" s="8" t="s">
+      <c r="Z87" s="6"/>
+      <c r="AA87" s="6" t="s">
         <v>553</v>
       </c>
-      <c r="AB87" s="11" t="s">
+      <c r="AB87" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC87" s="16" t="s">
+      <c r="AC87" s="23" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="88" spans="1:29" ht="15" customHeight="1">
-      <c r="P88" s="22"/>
+      <c r="P88" s="18"/>
     </row>
     <row r="89" spans="1:29" ht="15" customHeight="1">
-      <c r="P89" s="22"/>
+      <c r="P89" s="18"/>
     </row>
     <row r="90" spans="1:29" ht="15" customHeight="1">
       <c r="A90" t="s">
@@ -10434,58 +10434,58 @@
         <v>226</v>
       </c>
       <c r="L90" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="M90" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="N90" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="N90" s="5" t="s">
         <v>600</v>
       </c>
-      <c r="O90" s="6" t="s">
+      <c r="O90" s="5" t="s">
         <v>601</v>
       </c>
-      <c r="P90" s="13" t="s">
+      <c r="P90" s="10" t="s">
         <v>602</v>
       </c>
-      <c r="Q90" s="14" t="s">
+      <c r="Q90" s="11" t="s">
         <v>603</v>
       </c>
-      <c r="R90" s="14" t="s">
+      <c r="R90" s="11" t="s">
         <v>604</v>
       </c>
-      <c r="S90" s="6" t="s">
+      <c r="S90" s="5" t="s">
+        <v>653</v>
+      </c>
+      <c r="T90" s="5" t="s">
         <v>605</v>
       </c>
-      <c r="T90" s="6" t="s">
+      <c r="U90" s="5" t="s">
         <v>606</v>
       </c>
-      <c r="U90" s="6" t="s">
+      <c r="V90" s="5" t="s">
         <v>607</v>
       </c>
-      <c r="V90" s="6" t="s">
+      <c r="W90" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="W90" s="6" t="s">
+      <c r="X90" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="X90" s="6" t="s">
+      <c r="Y90" s="5" t="s">
         <v>610</v>
       </c>
-      <c r="Y90" s="6" t="s">
+      <c r="Z90" s="5" t="s">
         <v>611</v>
       </c>
-      <c r="Z90" s="6" t="s">
+      <c r="AA90" s="5" t="s">
         <v>612</v>
       </c>
-      <c r="AA90" s="6" t="s">
+      <c r="AB90" s="5" t="s">
         <v>613</v>
       </c>
-      <c r="AB90" s="6" t="s">
+      <c r="AC90" s="5" t="s">
         <v>614</v>
-      </c>
-      <c r="AC90" s="7" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="91" spans="1:29" ht="15" customHeight="1">
@@ -10517,50 +10517,50 @@
       <c r="J91" t="s">
         <v>186</v>
       </c>
-      <c r="N91" s="8" t="s">
+      <c r="N91" s="6" t="s">
         <v>572</v>
       </c>
-      <c r="O91" s="8" t="s">
+      <c r="O91" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="P91" s="9">
-        <v>2</v>
-      </c>
-      <c r="Q91" s="15">
+      <c r="P91" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q91" s="12">
         <v>7.6600000000000001E-2</v>
       </c>
-      <c r="R91" s="15">
+      <c r="R91" s="12">
         <v>0.15</v>
       </c>
-      <c r="S91" s="8" t="s">
+      <c r="S91" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="T91" s="8">
+      <c r="T91" s="6">
         <v>603</v>
       </c>
-      <c r="U91" s="8">
-        <v>2</v>
-      </c>
-      <c r="V91" s="8">
-        <v>2</v>
-      </c>
-      <c r="W91" s="8">
+      <c r="U91" s="6">
+        <v>2</v>
+      </c>
+      <c r="V91" s="6">
+        <v>2</v>
+      </c>
+      <c r="W91" s="6">
         <v>4000</v>
       </c>
-      <c r="X91" s="8">
+      <c r="X91" s="6">
         <v>25412</v>
       </c>
-      <c r="Y91" s="8" t="s">
+      <c r="Y91" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z91" s="8"/>
-      <c r="AA91" s="8" t="s">
+      <c r="Z91" s="6"/>
+      <c r="AA91" s="6" t="s">
         <v>574</v>
       </c>
-      <c r="AB91" s="11" t="s">
+      <c r="AB91" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC91" s="16" t="s">
+      <c r="AC91" s="23" t="s">
         <v>575</v>
       </c>
     </row>
@@ -10593,50 +10593,50 @@
       <c r="J92" t="s">
         <v>186</v>
       </c>
-      <c r="N92" s="8" t="s">
+      <c r="N92" s="6" t="s">
         <v>567</v>
       </c>
-      <c r="O92" s="8" t="s">
+      <c r="O92" s="6" t="s">
         <v>568</v>
       </c>
-      <c r="P92" s="9">
+      <c r="P92" s="7">
         <v>100</v>
       </c>
-      <c r="Q92" s="15">
+      <c r="Q92" s="12">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="R92" s="15">
+      <c r="R92" s="12">
         <v>0.16</v>
       </c>
-      <c r="S92" s="8" t="s">
+      <c r="S92" s="6" t="s">
         <v>569</v>
       </c>
-      <c r="T92" s="8">
+      <c r="T92" s="6">
         <v>402</v>
       </c>
-      <c r="U92" s="8">
+      <c r="U92" s="6">
         <v>100</v>
       </c>
-      <c r="V92" s="8">
+      <c r="V92" s="6">
         <v>100</v>
       </c>
-      <c r="W92" s="8">
+      <c r="W92" s="6">
         <v>10000</v>
       </c>
-      <c r="X92" s="8">
+      <c r="X92" s="6">
         <v>41300</v>
       </c>
-      <c r="Y92" s="8" t="s">
+      <c r="Y92" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z92" s="8"/>
-      <c r="AA92" s="8" t="s">
+      <c r="Z92" s="6"/>
+      <c r="AA92" s="6" t="s">
         <v>570</v>
       </c>
-      <c r="AB92" s="11" t="s">
+      <c r="AB92" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC92" s="16" t="s">
+      <c r="AC92" s="23" t="s">
         <v>571</v>
       </c>
     </row>
@@ -10669,7 +10669,8 @@
       <c r="L93" t="s">
         <v>186</v>
       </c>
-      <c r="P93" s="22"/>
+      <c r="P93" s="18"/>
+      <c r="AC93" s="27"/>
     </row>
     <row r="94" spans="1:29" ht="15" customHeight="1">
       <c r="A94">
@@ -10700,50 +10701,50 @@
       <c r="J94" t="s">
         <v>186</v>
       </c>
-      <c r="N94" s="8" t="s">
+      <c r="N94" s="6" t="s">
         <v>563</v>
       </c>
-      <c r="O94" s="8" t="s">
+      <c r="O94" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="P94" s="9">
+      <c r="P94" s="7">
         <v>100</v>
       </c>
-      <c r="Q94" s="15">
+      <c r="Q94" s="12">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="R94" s="15">
+      <c r="R94" s="12">
         <v>0.26</v>
       </c>
-      <c r="S94" s="8" t="s">
+      <c r="S94" s="6" t="s">
         <v>564</v>
       </c>
-      <c r="T94" s="8">
+      <c r="T94" s="6">
         <v>402</v>
       </c>
-      <c r="U94" s="8">
+      <c r="U94" s="6">
         <v>100</v>
       </c>
-      <c r="V94" s="8">
+      <c r="V94" s="6">
         <v>100</v>
       </c>
-      <c r="W94" s="8">
+      <c r="W94" s="6">
         <v>10000</v>
       </c>
-      <c r="X94" s="8">
+      <c r="X94" s="6">
         <v>17400</v>
       </c>
-      <c r="Y94" s="8" t="s">
+      <c r="Y94" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z94" s="8"/>
-      <c r="AA94" s="8" t="s">
+      <c r="Z94" s="6"/>
+      <c r="AA94" s="6" t="s">
         <v>565</v>
       </c>
-      <c r="AB94" s="11" t="s">
+      <c r="AB94" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC94" s="16" t="s">
+      <c r="AC94" s="23" t="s">
         <v>566</v>
       </c>
     </row>
@@ -10776,50 +10777,50 @@
       <c r="J95" t="s">
         <v>186</v>
       </c>
-      <c r="N95" s="8" t="s">
+      <c r="N95" s="6" t="s">
         <v>576</v>
       </c>
-      <c r="O95" s="8" t="s">
+      <c r="O95" s="6" t="s">
         <v>536</v>
       </c>
-      <c r="P95" s="9">
-        <v>2</v>
-      </c>
-      <c r="Q95" s="15">
+      <c r="P95" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q95" s="12">
         <v>0.62470000000000003</v>
       </c>
-      <c r="R95" s="15">
+      <c r="R95" s="12">
         <v>1.25</v>
       </c>
-      <c r="S95" s="8" t="s">
+      <c r="S95" s="6" t="s">
         <v>577</v>
       </c>
-      <c r="T95" s="8" t="s">
+      <c r="T95" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="U95" s="8">
-        <v>1</v>
-      </c>
-      <c r="V95" s="8">
-        <v>1</v>
-      </c>
-      <c r="W95" s="8">
+      <c r="U95" s="6">
+        <v>1</v>
+      </c>
+      <c r="V95" s="6">
+        <v>1</v>
+      </c>
+      <c r="W95" s="6">
         <v>5000</v>
       </c>
-      <c r="X95" s="8">
+      <c r="X95" s="6">
         <v>279</v>
       </c>
-      <c r="Y95" s="8" t="s">
+      <c r="Y95" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z95" s="8"/>
-      <c r="AA95" s="8" t="s">
+      <c r="Z95" s="6"/>
+      <c r="AA95" s="6" t="s">
         <v>578</v>
       </c>
-      <c r="AB95" s="11" t="s">
+      <c r="AB95" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC95" s="16" t="s">
+      <c r="AC95" s="23" t="s">
         <v>579</v>
       </c>
     </row>
@@ -10852,50 +10853,50 @@
       <c r="J96" t="s">
         <v>186</v>
       </c>
-      <c r="N96" s="8" t="s">
+      <c r="N96" s="6" t="s">
         <v>580</v>
       </c>
-      <c r="O96" s="8" t="s">
+      <c r="O96" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="P96" s="9">
+      <c r="P96" s="7">
         <v>10</v>
       </c>
-      <c r="Q96" s="15">
+      <c r="Q96" s="12">
         <v>4.0399999999999998E-2</v>
       </c>
-      <c r="R96" s="15">
+      <c r="R96" s="12">
         <v>0.4</v>
       </c>
-      <c r="S96" s="8" t="s">
+      <c r="S96" s="6" t="s">
         <v>581</v>
       </c>
-      <c r="T96" s="8" t="s">
+      <c r="T96" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="U96" s="8">
+      <c r="U96" s="6">
         <v>10</v>
       </c>
-      <c r="V96" s="8">
+      <c r="V96" s="6">
         <v>10</v>
       </c>
-      <c r="W96" s="8">
+      <c r="W96" s="6">
         <v>1000</v>
       </c>
-      <c r="X96" s="8">
+      <c r="X96" s="6">
         <v>148950</v>
       </c>
-      <c r="Y96" s="8" t="s">
+      <c r="Y96" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z96" s="8"/>
-      <c r="AA96" s="8" t="s">
+      <c r="Z96" s="6"/>
+      <c r="AA96" s="6" t="s">
         <v>582</v>
       </c>
-      <c r="AB96" s="11" t="s">
+      <c r="AB96" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC96" s="16" t="s">
+      <c r="AC96" s="23" t="s">
         <v>583</v>
       </c>
     </row>
@@ -10928,50 +10929,50 @@
       <c r="J97" t="s">
         <v>186</v>
       </c>
-      <c r="N97" s="8" t="s">
+      <c r="N97" s="6" t="s">
         <v>555</v>
       </c>
-      <c r="O97" s="8" t="s">
+      <c r="O97" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="P97" s="9">
+      <c r="P97" s="7">
         <v>10</v>
       </c>
-      <c r="Q97" s="15">
+      <c r="Q97" s="12">
         <v>8.6E-3</v>
       </c>
-      <c r="R97" s="15">
+      <c r="R97" s="12">
         <v>0.09</v>
       </c>
-      <c r="S97" s="8" t="s">
+      <c r="S97" s="6" t="s">
         <v>556</v>
       </c>
-      <c r="T97" s="8">
+      <c r="T97" s="6">
         <v>402</v>
       </c>
-      <c r="U97" s="8">
+      <c r="U97" s="6">
         <v>10</v>
       </c>
-      <c r="V97" s="8">
+      <c r="V97" s="6">
         <v>10</v>
       </c>
-      <c r="W97" s="8">
+      <c r="W97" s="6">
         <v>10000</v>
       </c>
-      <c r="X97" s="8">
+      <c r="X97" s="6">
         <v>67470</v>
       </c>
-      <c r="Y97" s="8" t="s">
+      <c r="Y97" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z97" s="8"/>
-      <c r="AA97" s="8" t="s">
+      <c r="Z97" s="6"/>
+      <c r="AA97" s="6" t="s">
         <v>557</v>
       </c>
-      <c r="AB97" s="11" t="s">
+      <c r="AB97" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC97" s="16" t="s">
+      <c r="AC97" s="23" t="s">
         <v>558</v>
       </c>
     </row>
@@ -11004,50 +11005,50 @@
       <c r="J98" t="s">
         <v>186</v>
       </c>
-      <c r="N98" s="8" t="s">
+      <c r="N98" s="6" t="s">
         <v>559</v>
       </c>
-      <c r="O98" s="8" t="s">
+      <c r="O98" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="P98" s="9">
+      <c r="P98" s="7">
         <v>100</v>
       </c>
-      <c r="Q98" s="15">
+      <c r="Q98" s="12">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="R98" s="15">
+      <c r="R98" s="12">
         <v>0.08</v>
       </c>
-      <c r="S98" s="8" t="s">
+      <c r="S98" s="6" t="s">
         <v>560</v>
       </c>
-      <c r="T98" s="8">
+      <c r="T98" s="6">
         <v>402</v>
       </c>
-      <c r="U98" s="8">
+      <c r="U98" s="6">
         <v>100</v>
       </c>
-      <c r="V98" s="8">
+      <c r="V98" s="6">
         <v>100</v>
       </c>
-      <c r="W98" s="8">
+      <c r="W98" s="6">
         <v>10000</v>
       </c>
-      <c r="X98" s="8">
+      <c r="X98" s="6">
         <v>5173500</v>
       </c>
-      <c r="Y98" s="8" t="s">
+      <c r="Y98" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z98" s="8"/>
-      <c r="AA98" s="8" t="s">
+      <c r="Z98" s="6"/>
+      <c r="AA98" s="6" t="s">
         <v>561</v>
       </c>
-      <c r="AB98" s="11" t="s">
+      <c r="AB98" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC98" s="16" t="s">
+      <c r="AC98" s="23" t="s">
         <v>562</v>
       </c>
     </row>
@@ -11077,7 +11078,8 @@
         <f>2*WIFI_Module9[[#This Row],[Quantity]]</f>
         <v>4</v>
       </c>
-      <c r="P99" s="22"/>
+      <c r="P99" s="18"/>
+      <c r="AC99" s="27"/>
     </row>
     <row r="100" spans="1:29" ht="15" customHeight="1">
       <c r="A100">
@@ -11108,50 +11110,50 @@
       <c r="J100" t="s">
         <v>186</v>
       </c>
-      <c r="N100" s="8" t="s">
+      <c r="N100" s="6" t="s">
         <v>584</v>
       </c>
-      <c r="O100" s="8" t="s">
+      <c r="O100" s="6" t="s">
         <v>585</v>
       </c>
-      <c r="P100" s="9">
-        <v>2</v>
-      </c>
-      <c r="Q100" s="15">
+      <c r="P100" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q100" s="12">
         <v>1.5423</v>
       </c>
-      <c r="R100" s="15">
+      <c r="R100" s="12">
         <v>3.08</v>
       </c>
-      <c r="S100" s="8" t="s">
+      <c r="S100" s="6" t="s">
         <v>586</v>
       </c>
-      <c r="T100" s="8" t="s">
+      <c r="T100" s="6" t="s">
         <v>587</v>
       </c>
-      <c r="U100" s="8">
-        <v>1</v>
-      </c>
-      <c r="V100" s="8">
-        <v>1</v>
-      </c>
-      <c r="W100" s="8">
+      <c r="U100" s="6">
+        <v>1</v>
+      </c>
+      <c r="V100" s="6">
+        <v>1</v>
+      </c>
+      <c r="W100" s="6">
         <v>5000</v>
       </c>
-      <c r="X100" s="8">
+      <c r="X100" s="6">
         <v>4843</v>
       </c>
-      <c r="Y100" s="8" t="s">
+      <c r="Y100" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z100" s="8"/>
-      <c r="AA100" s="8" t="s">
+      <c r="Z100" s="6"/>
+      <c r="AA100" s="6" t="s">
         <v>588</v>
       </c>
-      <c r="AB100" s="11" t="s">
+      <c r="AB100" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC100" s="16" t="s">
+      <c r="AC100" s="23" t="s">
         <v>589</v>
       </c>
     </row>
@@ -11181,65 +11183,69 @@
         <f>2*WIFI_Module9[[#This Row],[Quantity]]</f>
         <v>2</v>
       </c>
-      <c r="N101" s="8" t="s">
+      <c r="N101" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="O101" s="8" t="s">
+      <c r="O101" s="6" t="s">
         <v>590</v>
       </c>
-      <c r="P101" s="9">
+      <c r="P101" s="7">
         <v>5</v>
       </c>
-      <c r="Q101" s="15">
+      <c r="Q101" s="12">
         <v>0.3261</v>
       </c>
-      <c r="R101" s="15">
+      <c r="R101" s="12">
         <v>1.63</v>
       </c>
-      <c r="S101" s="8" t="s">
+      <c r="S101" s="6" t="s">
         <v>591</v>
       </c>
-      <c r="T101" s="8" t="s">
+      <c r="T101" s="6" t="s">
         <v>592</v>
       </c>
-      <c r="U101" s="8">
+      <c r="U101" s="6">
         <v>5</v>
       </c>
-      <c r="V101" s="8">
+      <c r="V101" s="6">
         <v>5</v>
       </c>
-      <c r="W101" s="8">
+      <c r="W101" s="6">
         <v>3000</v>
       </c>
-      <c r="X101" s="8">
+      <c r="X101" s="6">
         <v>1585</v>
       </c>
-      <c r="Y101" s="8" t="s">
+      <c r="Y101" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z101" s="8"/>
-      <c r="AA101" s="8" t="s">
+      <c r="Z101" s="6"/>
+      <c r="AA101" s="6" t="s">
         <v>593</v>
       </c>
-      <c r="AB101" s="11" t="s">
+      <c r="AB101" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC101" s="16" t="s">
+      <c r="AC101" s="23" t="s">
         <v>594</v>
       </c>
     </row>
     <row r="102" spans="1:29" ht="15" customHeight="1">
-      <c r="P102" s="22"/>
+      <c r="P102" s="18"/>
+      <c r="AC102" s="27"/>
     </row>
     <row r="103" spans="1:29" ht="15" customHeight="1">
-      <c r="P103" s="22"/>
+      <c r="P103" s="18"/>
+      <c r="AC103" s="27"/>
     </row>
     <row r="104" spans="1:29" ht="15" customHeight="1">
-      <c r="O104" s="24"/>
-      <c r="P104" s="22"/>
+      <c r="O104" s="20"/>
+      <c r="P104" s="18"/>
+      <c r="AC104" s="27"/>
     </row>
     <row r="105" spans="1:29" ht="15" customHeight="1">
-      <c r="P105" s="22"/>
+      <c r="P105" s="18"/>
+      <c r="AC105" s="27"/>
     </row>
     <row r="106" spans="1:29" ht="15" customHeight="1">
       <c r="A106" t="s">
@@ -11264,50 +11270,50 @@
       <c r="J106" t="s">
         <v>186</v>
       </c>
-      <c r="N106" s="8" t="s">
+      <c r="N106" s="6" t="s">
         <v>524</v>
       </c>
-      <c r="O106" s="8" t="s">
+      <c r="O106" s="6" t="s">
         <v>525</v>
       </c>
-      <c r="P106" s="9">
-        <v>2</v>
-      </c>
-      <c r="Q106" s="15">
+      <c r="P106" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q106" s="12">
         <v>0.30209999999999998</v>
       </c>
-      <c r="R106" s="15">
+      <c r="R106" s="12">
         <v>0.6</v>
       </c>
-      <c r="S106" s="8" t="s">
+      <c r="S106" s="6" t="s">
         <v>526</v>
       </c>
-      <c r="T106" s="8" t="s">
+      <c r="T106" s="6" t="s">
         <v>527</v>
       </c>
-      <c r="U106" s="8">
-        <v>1</v>
-      </c>
-      <c r="V106" s="8">
-        <v>1</v>
-      </c>
-      <c r="W106" s="8">
+      <c r="U106" s="6">
+        <v>1</v>
+      </c>
+      <c r="V106" s="6">
+        <v>1</v>
+      </c>
+      <c r="W106" s="6">
         <v>250</v>
       </c>
-      <c r="X106" s="8">
+      <c r="X106" s="6">
         <v>119</v>
       </c>
-      <c r="Y106" s="8" t="s">
+      <c r="Y106" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z106" s="8"/>
-      <c r="AA106" s="8" t="s">
+      <c r="Z106" s="6"/>
+      <c r="AA106" s="6" t="s">
         <v>528</v>
       </c>
-      <c r="AB106" s="11" t="s">
+      <c r="AB106" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC106" s="25" t="s">
+      <c r="AC106" s="26" t="s">
         <v>529</v>
       </c>
     </row>
@@ -11333,89 +11339,107 @@
       <c r="J107" t="s">
         <v>186</v>
       </c>
-      <c r="N107" s="8" t="s">
+      <c r="N107" s="6" t="s">
         <v>595</v>
       </c>
-      <c r="O107" s="8" t="s">
+      <c r="O107" s="6" t="s">
         <v>596</v>
       </c>
-      <c r="P107" s="9">
-        <v>2</v>
-      </c>
-      <c r="Q107" s="15">
+      <c r="P107" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q107" s="12">
         <v>3.4649000000000001</v>
       </c>
-      <c r="R107" s="15">
+      <c r="R107" s="12">
         <v>6.93</v>
       </c>
-      <c r="S107" s="8" t="s">
+      <c r="S107" s="6" t="s">
         <v>597</v>
       </c>
-      <c r="T107" s="8" t="s">
+      <c r="T107" s="6" t="s">
         <v>527</v>
       </c>
-      <c r="U107" s="8">
-        <v>1</v>
-      </c>
-      <c r="V107" s="8">
-        <v>1</v>
-      </c>
-      <c r="W107" s="8">
-        <v>1</v>
-      </c>
-      <c r="X107" s="8">
+      <c r="U107" s="6">
+        <v>1</v>
+      </c>
+      <c r="V107" s="6">
+        <v>1</v>
+      </c>
+      <c r="W107" s="6">
+        <v>1</v>
+      </c>
+      <c r="X107" s="6">
         <v>242</v>
       </c>
-      <c r="Y107" s="8" t="s">
+      <c r="Y107" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Z107" s="8"/>
-      <c r="AA107" s="8" t="s">
+      <c r="Z107" s="6"/>
+      <c r="AA107" s="6" t="s">
         <v>598</v>
       </c>
-      <c r="AB107" s="11" t="s">
+      <c r="AB107" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="AC107" s="25" t="s">
+      <c r="AC107" s="26" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="108" spans="1:29" ht="15" customHeight="1"/>
+    <row r="108" spans="1:29" ht="15" customHeight="1">
+      <c r="E108" t="s">
+        <v>650</v>
+      </c>
+      <c r="H108">
+        <v>2</v>
+      </c>
+      <c r="N108" t="s">
+        <v>652</v>
+      </c>
+      <c r="O108" s="14" t="s">
+        <v>651</v>
+      </c>
+      <c r="P108" s="15">
+        <v>2</v>
+      </c>
+      <c r="Q108" s="19">
+        <f>R108/P108</f>
+        <v>8.6850000000000005</v>
+      </c>
+      <c r="R108" s="19">
+        <v>17.37</v>
+      </c>
+      <c r="AA108" t="s">
+        <v>652</v>
+      </c>
+      <c r="AC108" s="27" t="s">
+        <v>654</v>
+      </c>
+    </row>
     <row r="109" spans="1:29" ht="15" customHeight="1"/>
     <row r="110" spans="1:29" ht="15" customHeight="1"/>
     <row r="111" spans="1:29" ht="15" customHeight="1"/>
     <row r="112" spans="1:29" ht="15" customHeight="1"/>
     <row r="113" spans="18:18" ht="15" customHeight="1"/>
     <row r="114" spans="18:18" ht="15" customHeight="1">
-      <c r="R114" s="23">
+      <c r="R114" s="19">
         <f>SUM(Artnet_DMX_Converter5[Ext.Price(USD)],Display_panel7[Ext.Price(USD)],WIFI_Module9[Ext.Price(USD)],R104:R113)</f>
-        <v>189.15000000000003</v>
+        <v>206.52000000000004</v>
       </c>
     </row>
     <row r="115" spans="18:18" ht="15" customHeight="1"/>
     <row r="116" spans="18:18" ht="15" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="M2:M28 M30:M33 M37:M59 M61:M63 M77:M107 M66:M75">
-    <cfRule type="expression" dxfId="56" priority="1">
+  <conditionalFormatting sqref="M2:M108">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>P2&gt;H2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="2">
+    <cfRule type="expression" dxfId="13" priority="2">
       <formula>P2=H2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="3">
+    <cfRule type="expression" dxfId="12" priority="3">
       <formula>P2&lt;H2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M29 M34:M36 M60 M76 M64:M65">
-    <cfRule type="expression" dxfId="53" priority="7">
-      <formula>#REF!&gt;H29</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="52" priority="8">
-      <formula>#REF!=H29</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="51" priority="9">
-      <formula>#REF!&lt;H29</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -11508,13 +11532,14 @@
     <hyperlink ref="AC35" r:id="rId87" xr:uid="{4F190B47-A6ED-4FF5-812D-08533CD1A679}"/>
     <hyperlink ref="AC36" r:id="rId88" xr:uid="{688BDCB9-5AB2-4C75-9552-B777910C5124}"/>
     <hyperlink ref="AC46" r:id="rId89" display="url" xr:uid="{3FA38DC4-CC2E-409B-B893-09DA8C87D6DD}"/>
+    <hyperlink ref="AC108" r:id="rId90" xr:uid="{8D405697-7667-4420-84D8-6CC76D0BE29D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId90"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId91"/>
   <tableParts count="3">
-    <tablePart r:id="rId91"/>
     <tablePart r:id="rId92"/>
     <tablePart r:id="rId93"/>
+    <tablePart r:id="rId94"/>
   </tableParts>
 </worksheet>
 </file>

--- a/BOMs/BOM_ORDER.xlsx
+++ b/BOMs/BOM_ORDER.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon\Documents\KiCad\desings\4_DMX node\BOMs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon\Documents\KiCad\desings\DMXion 4port node\BOMs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1372D22A-C904-4495-93E3-8CAF3AB35CBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6DB3CE-F99C-4213-9FE7-B49A87125824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{9B84EF14-36DD-40E4-AAD2-543AD15C4A8A}"/>
   </bookViews>
@@ -11408,6 +11408,10 @@
       <c r="R111" s="19">
         <v>14.11</v>
       </c>
+      <c r="S111" s="28">
+        <f>R111+7.9</f>
+        <v>22.009999999999998</v>
+      </c>
     </row>
     <row r="112" spans="1:29" ht="15" customHeight="1">
       <c r="N112" s="14" t="s">
